--- a/web/public/forms/chg-tonghap.xlsx
+++ b/web/public/forms/chg-tonghap.xlsx
@@ -20,7 +20,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'제출서식'!$A$1:$F$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'제출서식'!$A$1:$F$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -93,12 +93,12 @@
     <font>
       <b val="1"/>
       <color rgb="001F4E79"/>
-      <sz val="12"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="001F4E79"/>
-      <sz val="10"/>
+      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
@@ -254,7 +254,7 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -291,7 +291,7 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="11" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="12" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="13" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -800,7 +800,7 @@
       <c r="C4" s="6" t="n"/>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>내역서 Σ(수량 × 재료비단가)</t>
+          <t>당초 Σ(수량 × 재료비단가) · 변경 = 당초 + 증감대비표(제65조)</t>
         </is>
       </c>
       <c r="E4" s="8">
@@ -808,7 +808,7 @@
         <v/>
       </c>
       <c r="F4" s="8">
-        <f>SUMPRODUCT(N(내역서!$N$4:$N$203),N(내역서!$O$4:$O$203))</f>
+        <f>E4+SUM(증감대비표!$U$4:$U$203)</f>
         <v/>
       </c>
       <c r="G4" s="8">
@@ -916,7 +916,7 @@
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>내역서 Σ(수량 × 노무비단가)</t>
+          <t>당초 Σ(수량 × 노무비단가) · 변경 = 당초 + 증감대비표(제65조)</t>
         </is>
       </c>
       <c r="E8" s="8">
@@ -924,7 +924,7 @@
         <v/>
       </c>
       <c r="F8" s="8">
-        <f>SUMPRODUCT(N(내역서!$N$4:$N$203),N(내역서!$P$4:$P$203))</f>
+        <f>E8+SUM(증감대비표!$V$4:$V$203)</f>
         <v/>
       </c>
       <c r="G8" s="8">
@@ -1009,7 +1009,7 @@
       <c r="C11" s="6" t="n"/>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>내역서 Σ(수량 × 경비단가)</t>
+          <t>당초 Σ(수량 × 경비단가) · 변경 = 당초 + 증감대비표(제65조)</t>
         </is>
       </c>
       <c r="E11" s="8">
@@ -1017,7 +1017,7 @@
         <v/>
       </c>
       <c r="F11" s="8">
-        <f>SUMPRODUCT(N(내역서!$N$4:$N$203),N(내역서!$Q$4:$Q$203))</f>
+        <f>E11+SUM(증감대비표!$W$4:$W$203)</f>
         <v/>
       </c>
       <c r="G11" s="8">
@@ -1790,7 +1790,7 @@
     <row r="37">
       <c r="A37" s="17" t="inlineStr">
         <is>
-          <t>조달청 설계내역서 110장을 열어 줄 차례·요율·산출근거를 세어 그대로 맞춘 것입니다. 노랑 칸만 사람이 넣습니다(간접재료비·작업설·공사이행보증·폐기물·관급자재대). ⚠️ 요율은 해마다·공사 규모마다 바뀝니다 — «설정» 시트에 발주처 설계서의 요율을 넣고 쓰십시오. 이윤은 (B+C+E)에만 곱합니다 — 재료비(A)는 넣지 않습니다. 산업안전보건관리비는 관급자재대(K)를 1.1로 나눠 더한 값에 곱합니다.</t>
+          <t>조달청 설계내역서 110장을 열어 줄 차례·요율·산출근거를 세어 그대로 맞춘 것입니다. 노랑 칸만 사람이 넣습니다(간접재료비·작업설·공사이행보증·폐기물·관급자재대). ⚠️ 요율은 해마다·공사 규모마다 바뀝니다 — «설정» 시트에 발주처 설계서의 요율을 넣고 쓰십시오. 이윤은 (B+C+E)에만 곱합니다 — 재료비(A)는 넣지 않습니다. 산업안전보건관리비는 관급자재대(K)를 1.1로 나눠 더한 값에 곱합니다. «변경 후» 직접비는 당초 + 증감대비표의 제65조 증감(증가 = 계약단가 · 신규 = 당시단가 × 낙찰률)입니다 — 증감 열의 «도급액» 증감이 곧 계약금액 조정액입니다(제비율 · 부가세 포함).</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="C12" s="61" t="inlineStr">
         <is>
-          <t>당초 / 변경 후를 나란히 냅니다. 요율은 설정에서 한 번만 고칩니다.</t>
+          <t>당초 / 변경 후를 나란히 냅니다. 변경 후 = 당초 + 증감대비표의 제65조 증감. «도급액» 증감이 곧 계약금액 조정액입니다. 요율은 설정에서 한 번만 고칩니다.</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q210"/>
+  <dimension ref="A1:W212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2529,6 +2529,12 @@
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="15" customWidth="1" min="16" max="16"/>
     <col width="34" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2631,6 +2637,36 @@
           <t>단가 근거</t>
         </is>
       </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>적용 재료비</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>적용 노무비</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>적용 경비</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>증감 재료비</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>증감 노무비</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>증감 경비</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="18">
@@ -2695,6 +2731,30 @@
         <f>IF($B4="","",IF($L4="감소","감소분 → 계약단가",IF(AND($M4="Y",OR($L4="증가",$L4="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L4="증가",IF(AND($N4&lt;&gt;"",$G4&gt;$N4),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L4="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R4" s="20">
+        <f>IF($B4="","",IF(N($O4)=0,0,IF(OR($L4="감소",AND($L4="증가",$M4&lt;&gt;"Y")),IF(N($G4)=0,0,ROUND(N(내역서!$G4)*$O4/$G4,0)),IF(N($J4)=0,0,ROUND(N(내역서!$O4)*$O4/$J4,0)))))</f>
+        <v/>
+      </c>
+      <c r="S4" s="20">
+        <f>IF($B4="","",IF(N($O4)=0,0,IF(OR($L4="감소",AND($L4="증가",$M4&lt;&gt;"Y")),IF(N($G4)=0,0,ROUND(N(내역서!$H4)*$O4/$G4,0)),IF(N($J4)=0,0,ROUND(N(내역서!$P4)*$O4/$J4,0)))))</f>
+        <v/>
+      </c>
+      <c r="T4" s="20">
+        <f>IF($B4="","",N($O4)-N($R4)-N($S4))</f>
+        <v/>
+      </c>
+      <c r="U4" s="20">
+        <f>IF($B4="","",ROUND(N($K4)*N($R4),0))</f>
+        <v/>
+      </c>
+      <c r="V4" s="20">
+        <f>IF($B4="","",ROUND(N($K4)*N($S4),0))</f>
+        <v/>
+      </c>
+      <c r="W4" s="20">
+        <f>IF($B4="","",N($P4)-N($U4)-N($V4))</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="18">
@@ -2759,6 +2819,30 @@
         <f>IF($B5="","",IF($L5="감소","감소분 → 계약단가",IF(AND($M5="Y",OR($L5="증가",$L5="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L5="증가",IF(AND($N5&lt;&gt;"",$G5&gt;$N5),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L5="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R5" s="20">
+        <f>IF($B5="","",IF(N($O5)=0,0,IF(OR($L5="감소",AND($L5="증가",$M5&lt;&gt;"Y")),IF(N($G5)=0,0,ROUND(N(내역서!$G5)*$O5/$G5,0)),IF(N($J5)=0,0,ROUND(N(내역서!$O5)*$O5/$J5,0)))))</f>
+        <v/>
+      </c>
+      <c r="S5" s="20">
+        <f>IF($B5="","",IF(N($O5)=0,0,IF(OR($L5="감소",AND($L5="증가",$M5&lt;&gt;"Y")),IF(N($G5)=0,0,ROUND(N(내역서!$H5)*$O5/$G5,0)),IF(N($J5)=0,0,ROUND(N(내역서!$P5)*$O5/$J5,0)))))</f>
+        <v/>
+      </c>
+      <c r="T5" s="20">
+        <f>IF($B5="","",N($O5)-N($R5)-N($S5))</f>
+        <v/>
+      </c>
+      <c r="U5" s="20">
+        <f>IF($B5="","",ROUND(N($K5)*N($R5),0))</f>
+        <v/>
+      </c>
+      <c r="V5" s="20">
+        <f>IF($B5="","",ROUND(N($K5)*N($S5),0))</f>
+        <v/>
+      </c>
+      <c r="W5" s="20">
+        <f>IF($B5="","",N($P5)-N($U5)-N($V5))</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="18">
@@ -2823,6 +2907,30 @@
         <f>IF($B6="","",IF($L6="감소","감소분 → 계약단가",IF(AND($M6="Y",OR($L6="증가",$L6="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L6="증가",IF(AND($N6&lt;&gt;"",$G6&gt;$N6),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L6="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R6" s="20">
+        <f>IF($B6="","",IF(N($O6)=0,0,IF(OR($L6="감소",AND($L6="증가",$M6&lt;&gt;"Y")),IF(N($G6)=0,0,ROUND(N(내역서!$G6)*$O6/$G6,0)),IF(N($J6)=0,0,ROUND(N(내역서!$O6)*$O6/$J6,0)))))</f>
+        <v/>
+      </c>
+      <c r="S6" s="20">
+        <f>IF($B6="","",IF(N($O6)=0,0,IF(OR($L6="감소",AND($L6="증가",$M6&lt;&gt;"Y")),IF(N($G6)=0,0,ROUND(N(내역서!$H6)*$O6/$G6,0)),IF(N($J6)=0,0,ROUND(N(내역서!$P6)*$O6/$J6,0)))))</f>
+        <v/>
+      </c>
+      <c r="T6" s="20">
+        <f>IF($B6="","",N($O6)-N($R6)-N($S6))</f>
+        <v/>
+      </c>
+      <c r="U6" s="20">
+        <f>IF($B6="","",ROUND(N($K6)*N($R6),0))</f>
+        <v/>
+      </c>
+      <c r="V6" s="20">
+        <f>IF($B6="","",ROUND(N($K6)*N($S6),0))</f>
+        <v/>
+      </c>
+      <c r="W6" s="20">
+        <f>IF($B6="","",N($P6)-N($U6)-N($V6))</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="18">
@@ -2887,6 +2995,30 @@
         <f>IF($B7="","",IF($L7="감소","감소분 → 계약단가",IF(AND($M7="Y",OR($L7="증가",$L7="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L7="증가",IF(AND($N7&lt;&gt;"",$G7&gt;$N7),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L7="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R7" s="20">
+        <f>IF($B7="","",IF(N($O7)=0,0,IF(OR($L7="감소",AND($L7="증가",$M7&lt;&gt;"Y")),IF(N($G7)=0,0,ROUND(N(내역서!$G7)*$O7/$G7,0)),IF(N($J7)=0,0,ROUND(N(내역서!$O7)*$O7/$J7,0)))))</f>
+        <v/>
+      </c>
+      <c r="S7" s="20">
+        <f>IF($B7="","",IF(N($O7)=0,0,IF(OR($L7="감소",AND($L7="증가",$M7&lt;&gt;"Y")),IF(N($G7)=0,0,ROUND(N(내역서!$H7)*$O7/$G7,0)),IF(N($J7)=0,0,ROUND(N(내역서!$P7)*$O7/$J7,0)))))</f>
+        <v/>
+      </c>
+      <c r="T7" s="20">
+        <f>IF($B7="","",N($O7)-N($R7)-N($S7))</f>
+        <v/>
+      </c>
+      <c r="U7" s="20">
+        <f>IF($B7="","",ROUND(N($K7)*N($R7),0))</f>
+        <v/>
+      </c>
+      <c r="V7" s="20">
+        <f>IF($B7="","",ROUND(N($K7)*N($S7),0))</f>
+        <v/>
+      </c>
+      <c r="W7" s="20">
+        <f>IF($B7="","",N($P7)-N($U7)-N($V7))</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="18">
@@ -2951,6 +3083,30 @@
         <f>IF($B8="","",IF($L8="감소","감소분 → 계약단가",IF(AND($M8="Y",OR($L8="증가",$L8="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L8="증가",IF(AND($N8&lt;&gt;"",$G8&gt;$N8),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L8="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R8" s="20">
+        <f>IF($B8="","",IF(N($O8)=0,0,IF(OR($L8="감소",AND($L8="증가",$M8&lt;&gt;"Y")),IF(N($G8)=0,0,ROUND(N(내역서!$G8)*$O8/$G8,0)),IF(N($J8)=0,0,ROUND(N(내역서!$O8)*$O8/$J8,0)))))</f>
+        <v/>
+      </c>
+      <c r="S8" s="20">
+        <f>IF($B8="","",IF(N($O8)=0,0,IF(OR($L8="감소",AND($L8="증가",$M8&lt;&gt;"Y")),IF(N($G8)=0,0,ROUND(N(내역서!$H8)*$O8/$G8,0)),IF(N($J8)=0,0,ROUND(N(내역서!$P8)*$O8/$J8,0)))))</f>
+        <v/>
+      </c>
+      <c r="T8" s="20">
+        <f>IF($B8="","",N($O8)-N($R8)-N($S8))</f>
+        <v/>
+      </c>
+      <c r="U8" s="20">
+        <f>IF($B8="","",ROUND(N($K8)*N($R8),0))</f>
+        <v/>
+      </c>
+      <c r="V8" s="20">
+        <f>IF($B8="","",ROUND(N($K8)*N($S8),0))</f>
+        <v/>
+      </c>
+      <c r="W8" s="20">
+        <f>IF($B8="","",N($P8)-N($U8)-N($V8))</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="18">
@@ -3015,6 +3171,30 @@
         <f>IF($B9="","",IF($L9="감소","감소분 → 계약단가",IF(AND($M9="Y",OR($L9="증가",$L9="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L9="증가",IF(AND($N9&lt;&gt;"",$G9&gt;$N9),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L9="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R9" s="20">
+        <f>IF($B9="","",IF(N($O9)=0,0,IF(OR($L9="감소",AND($L9="증가",$M9&lt;&gt;"Y")),IF(N($G9)=0,0,ROUND(N(내역서!$G9)*$O9/$G9,0)),IF(N($J9)=0,0,ROUND(N(내역서!$O9)*$O9/$J9,0)))))</f>
+        <v/>
+      </c>
+      <c r="S9" s="20">
+        <f>IF($B9="","",IF(N($O9)=0,0,IF(OR($L9="감소",AND($L9="증가",$M9&lt;&gt;"Y")),IF(N($G9)=0,0,ROUND(N(내역서!$H9)*$O9/$G9,0)),IF(N($J9)=0,0,ROUND(N(내역서!$P9)*$O9/$J9,0)))))</f>
+        <v/>
+      </c>
+      <c r="T9" s="20">
+        <f>IF($B9="","",N($O9)-N($R9)-N($S9))</f>
+        <v/>
+      </c>
+      <c r="U9" s="20">
+        <f>IF($B9="","",ROUND(N($K9)*N($R9),0))</f>
+        <v/>
+      </c>
+      <c r="V9" s="20">
+        <f>IF($B9="","",ROUND(N($K9)*N($S9),0))</f>
+        <v/>
+      </c>
+      <c r="W9" s="20">
+        <f>IF($B9="","",N($P9)-N($U9)-N($V9))</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="18">
@@ -3079,6 +3259,30 @@
         <f>IF($B10="","",IF($L10="감소","감소분 → 계약단가",IF(AND($M10="Y",OR($L10="증가",$L10="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L10="증가",IF(AND($N10&lt;&gt;"",$G10&gt;$N10),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L10="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R10" s="20">
+        <f>IF($B10="","",IF(N($O10)=0,0,IF(OR($L10="감소",AND($L10="증가",$M10&lt;&gt;"Y")),IF(N($G10)=0,0,ROUND(N(내역서!$G10)*$O10/$G10,0)),IF(N($J10)=0,0,ROUND(N(내역서!$O10)*$O10/$J10,0)))))</f>
+        <v/>
+      </c>
+      <c r="S10" s="20">
+        <f>IF($B10="","",IF(N($O10)=0,0,IF(OR($L10="감소",AND($L10="증가",$M10&lt;&gt;"Y")),IF(N($G10)=0,0,ROUND(N(내역서!$H10)*$O10/$G10,0)),IF(N($J10)=0,0,ROUND(N(내역서!$P10)*$O10/$J10,0)))))</f>
+        <v/>
+      </c>
+      <c r="T10" s="20">
+        <f>IF($B10="","",N($O10)-N($R10)-N($S10))</f>
+        <v/>
+      </c>
+      <c r="U10" s="20">
+        <f>IF($B10="","",ROUND(N($K10)*N($R10),0))</f>
+        <v/>
+      </c>
+      <c r="V10" s="20">
+        <f>IF($B10="","",ROUND(N($K10)*N($S10),0))</f>
+        <v/>
+      </c>
+      <c r="W10" s="20">
+        <f>IF($B10="","",N($P10)-N($U10)-N($V10))</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="18">
@@ -3143,6 +3347,30 @@
         <f>IF($B11="","",IF($L11="감소","감소분 → 계약단가",IF(AND($M11="Y",OR($L11="증가",$L11="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L11="증가",IF(AND($N11&lt;&gt;"",$G11&gt;$N11),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L11="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R11" s="20">
+        <f>IF($B11="","",IF(N($O11)=0,0,IF(OR($L11="감소",AND($L11="증가",$M11&lt;&gt;"Y")),IF(N($G11)=0,0,ROUND(N(내역서!$G11)*$O11/$G11,0)),IF(N($J11)=0,0,ROUND(N(내역서!$O11)*$O11/$J11,0)))))</f>
+        <v/>
+      </c>
+      <c r="S11" s="20">
+        <f>IF($B11="","",IF(N($O11)=0,0,IF(OR($L11="감소",AND($L11="증가",$M11&lt;&gt;"Y")),IF(N($G11)=0,0,ROUND(N(내역서!$H11)*$O11/$G11,0)),IF(N($J11)=0,0,ROUND(N(내역서!$P11)*$O11/$J11,0)))))</f>
+        <v/>
+      </c>
+      <c r="T11" s="20">
+        <f>IF($B11="","",N($O11)-N($R11)-N($S11))</f>
+        <v/>
+      </c>
+      <c r="U11" s="20">
+        <f>IF($B11="","",ROUND(N($K11)*N($R11),0))</f>
+        <v/>
+      </c>
+      <c r="V11" s="20">
+        <f>IF($B11="","",ROUND(N($K11)*N($S11),0))</f>
+        <v/>
+      </c>
+      <c r="W11" s="20">
+        <f>IF($B11="","",N($P11)-N($U11)-N($V11))</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="18">
@@ -3207,6 +3435,30 @@
         <f>IF($B12="","",IF($L12="감소","감소분 → 계약단가",IF(AND($M12="Y",OR($L12="증가",$L12="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L12="증가",IF(AND($N12&lt;&gt;"",$G12&gt;$N12),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L12="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R12" s="20">
+        <f>IF($B12="","",IF(N($O12)=0,0,IF(OR($L12="감소",AND($L12="증가",$M12&lt;&gt;"Y")),IF(N($G12)=0,0,ROUND(N(내역서!$G12)*$O12/$G12,0)),IF(N($J12)=0,0,ROUND(N(내역서!$O12)*$O12/$J12,0)))))</f>
+        <v/>
+      </c>
+      <c r="S12" s="20">
+        <f>IF($B12="","",IF(N($O12)=0,0,IF(OR($L12="감소",AND($L12="증가",$M12&lt;&gt;"Y")),IF(N($G12)=0,0,ROUND(N(내역서!$H12)*$O12/$G12,0)),IF(N($J12)=0,0,ROUND(N(내역서!$P12)*$O12/$J12,0)))))</f>
+        <v/>
+      </c>
+      <c r="T12" s="20">
+        <f>IF($B12="","",N($O12)-N($R12)-N($S12))</f>
+        <v/>
+      </c>
+      <c r="U12" s="20">
+        <f>IF($B12="","",ROUND(N($K12)*N($R12),0))</f>
+        <v/>
+      </c>
+      <c r="V12" s="20">
+        <f>IF($B12="","",ROUND(N($K12)*N($S12),0))</f>
+        <v/>
+      </c>
+      <c r="W12" s="20">
+        <f>IF($B12="","",N($P12)-N($U12)-N($V12))</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="18">
@@ -3271,6 +3523,30 @@
         <f>IF($B13="","",IF($L13="감소","감소분 → 계약단가",IF(AND($M13="Y",OR($L13="증가",$L13="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L13="증가",IF(AND($N13&lt;&gt;"",$G13&gt;$N13),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L13="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R13" s="20">
+        <f>IF($B13="","",IF(N($O13)=0,0,IF(OR($L13="감소",AND($L13="증가",$M13&lt;&gt;"Y")),IF(N($G13)=0,0,ROUND(N(내역서!$G13)*$O13/$G13,0)),IF(N($J13)=0,0,ROUND(N(내역서!$O13)*$O13/$J13,0)))))</f>
+        <v/>
+      </c>
+      <c r="S13" s="20">
+        <f>IF($B13="","",IF(N($O13)=0,0,IF(OR($L13="감소",AND($L13="증가",$M13&lt;&gt;"Y")),IF(N($G13)=0,0,ROUND(N(내역서!$H13)*$O13/$G13,0)),IF(N($J13)=0,0,ROUND(N(내역서!$P13)*$O13/$J13,0)))))</f>
+        <v/>
+      </c>
+      <c r="T13" s="20">
+        <f>IF($B13="","",N($O13)-N($R13)-N($S13))</f>
+        <v/>
+      </c>
+      <c r="U13" s="20">
+        <f>IF($B13="","",ROUND(N($K13)*N($R13),0))</f>
+        <v/>
+      </c>
+      <c r="V13" s="20">
+        <f>IF($B13="","",ROUND(N($K13)*N($S13),0))</f>
+        <v/>
+      </c>
+      <c r="W13" s="20">
+        <f>IF($B13="","",N($P13)-N($U13)-N($V13))</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="18">
@@ -3335,6 +3611,30 @@
         <f>IF($B14="","",IF($L14="감소","감소분 → 계약단가",IF(AND($M14="Y",OR($L14="증가",$L14="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L14="증가",IF(AND($N14&lt;&gt;"",$G14&gt;$N14),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L14="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R14" s="20">
+        <f>IF($B14="","",IF(N($O14)=0,0,IF(OR($L14="감소",AND($L14="증가",$M14&lt;&gt;"Y")),IF(N($G14)=0,0,ROUND(N(내역서!$G14)*$O14/$G14,0)),IF(N($J14)=0,0,ROUND(N(내역서!$O14)*$O14/$J14,0)))))</f>
+        <v/>
+      </c>
+      <c r="S14" s="20">
+        <f>IF($B14="","",IF(N($O14)=0,0,IF(OR($L14="감소",AND($L14="증가",$M14&lt;&gt;"Y")),IF(N($G14)=0,0,ROUND(N(내역서!$H14)*$O14/$G14,0)),IF(N($J14)=0,0,ROUND(N(내역서!$P14)*$O14/$J14,0)))))</f>
+        <v/>
+      </c>
+      <c r="T14" s="20">
+        <f>IF($B14="","",N($O14)-N($R14)-N($S14))</f>
+        <v/>
+      </c>
+      <c r="U14" s="20">
+        <f>IF($B14="","",ROUND(N($K14)*N($R14),0))</f>
+        <v/>
+      </c>
+      <c r="V14" s="20">
+        <f>IF($B14="","",ROUND(N($K14)*N($S14),0))</f>
+        <v/>
+      </c>
+      <c r="W14" s="20">
+        <f>IF($B14="","",N($P14)-N($U14)-N($V14))</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="18">
@@ -3399,6 +3699,30 @@
         <f>IF($B15="","",IF($L15="감소","감소분 → 계약단가",IF(AND($M15="Y",OR($L15="증가",$L15="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L15="증가",IF(AND($N15&lt;&gt;"",$G15&gt;$N15),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L15="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R15" s="20">
+        <f>IF($B15="","",IF(N($O15)=0,0,IF(OR($L15="감소",AND($L15="증가",$M15&lt;&gt;"Y")),IF(N($G15)=0,0,ROUND(N(내역서!$G15)*$O15/$G15,0)),IF(N($J15)=0,0,ROUND(N(내역서!$O15)*$O15/$J15,0)))))</f>
+        <v/>
+      </c>
+      <c r="S15" s="20">
+        <f>IF($B15="","",IF(N($O15)=0,0,IF(OR($L15="감소",AND($L15="증가",$M15&lt;&gt;"Y")),IF(N($G15)=0,0,ROUND(N(내역서!$H15)*$O15/$G15,0)),IF(N($J15)=0,0,ROUND(N(내역서!$P15)*$O15/$J15,0)))))</f>
+        <v/>
+      </c>
+      <c r="T15" s="20">
+        <f>IF($B15="","",N($O15)-N($R15)-N($S15))</f>
+        <v/>
+      </c>
+      <c r="U15" s="20">
+        <f>IF($B15="","",ROUND(N($K15)*N($R15),0))</f>
+        <v/>
+      </c>
+      <c r="V15" s="20">
+        <f>IF($B15="","",ROUND(N($K15)*N($S15),0))</f>
+        <v/>
+      </c>
+      <c r="W15" s="20">
+        <f>IF($B15="","",N($P15)-N($U15)-N($V15))</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="18">
@@ -3463,6 +3787,30 @@
         <f>IF($B16="","",IF($L16="감소","감소분 → 계약단가",IF(AND($M16="Y",OR($L16="증가",$L16="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L16="증가",IF(AND($N16&lt;&gt;"",$G16&gt;$N16),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L16="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R16" s="20">
+        <f>IF($B16="","",IF(N($O16)=0,0,IF(OR($L16="감소",AND($L16="증가",$M16&lt;&gt;"Y")),IF(N($G16)=0,0,ROUND(N(내역서!$G16)*$O16/$G16,0)),IF(N($J16)=0,0,ROUND(N(내역서!$O16)*$O16/$J16,0)))))</f>
+        <v/>
+      </c>
+      <c r="S16" s="20">
+        <f>IF($B16="","",IF(N($O16)=0,0,IF(OR($L16="감소",AND($L16="증가",$M16&lt;&gt;"Y")),IF(N($G16)=0,0,ROUND(N(내역서!$H16)*$O16/$G16,0)),IF(N($J16)=0,0,ROUND(N(내역서!$P16)*$O16/$J16,0)))))</f>
+        <v/>
+      </c>
+      <c r="T16" s="20">
+        <f>IF($B16="","",N($O16)-N($R16)-N($S16))</f>
+        <v/>
+      </c>
+      <c r="U16" s="20">
+        <f>IF($B16="","",ROUND(N($K16)*N($R16),0))</f>
+        <v/>
+      </c>
+      <c r="V16" s="20">
+        <f>IF($B16="","",ROUND(N($K16)*N($S16),0))</f>
+        <v/>
+      </c>
+      <c r="W16" s="20">
+        <f>IF($B16="","",N($P16)-N($U16)-N($V16))</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="18">
@@ -3527,6 +3875,30 @@
         <f>IF($B17="","",IF($L17="감소","감소분 → 계약단가",IF(AND($M17="Y",OR($L17="증가",$L17="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L17="증가",IF(AND($N17&lt;&gt;"",$G17&gt;$N17),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L17="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R17" s="20">
+        <f>IF($B17="","",IF(N($O17)=0,0,IF(OR($L17="감소",AND($L17="증가",$M17&lt;&gt;"Y")),IF(N($G17)=0,0,ROUND(N(내역서!$G17)*$O17/$G17,0)),IF(N($J17)=0,0,ROUND(N(내역서!$O17)*$O17/$J17,0)))))</f>
+        <v/>
+      </c>
+      <c r="S17" s="20">
+        <f>IF($B17="","",IF(N($O17)=0,0,IF(OR($L17="감소",AND($L17="증가",$M17&lt;&gt;"Y")),IF(N($G17)=0,0,ROUND(N(내역서!$H17)*$O17/$G17,0)),IF(N($J17)=0,0,ROUND(N(내역서!$P17)*$O17/$J17,0)))))</f>
+        <v/>
+      </c>
+      <c r="T17" s="20">
+        <f>IF($B17="","",N($O17)-N($R17)-N($S17))</f>
+        <v/>
+      </c>
+      <c r="U17" s="20">
+        <f>IF($B17="","",ROUND(N($K17)*N($R17),0))</f>
+        <v/>
+      </c>
+      <c r="V17" s="20">
+        <f>IF($B17="","",ROUND(N($K17)*N($S17),0))</f>
+        <v/>
+      </c>
+      <c r="W17" s="20">
+        <f>IF($B17="","",N($P17)-N($U17)-N($V17))</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="18">
@@ -3591,6 +3963,30 @@
         <f>IF($B18="","",IF($L18="감소","감소분 → 계약단가",IF(AND($M18="Y",OR($L18="증가",$L18="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L18="증가",IF(AND($N18&lt;&gt;"",$G18&gt;$N18),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L18="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R18" s="20">
+        <f>IF($B18="","",IF(N($O18)=0,0,IF(OR($L18="감소",AND($L18="증가",$M18&lt;&gt;"Y")),IF(N($G18)=0,0,ROUND(N(내역서!$G18)*$O18/$G18,0)),IF(N($J18)=0,0,ROUND(N(내역서!$O18)*$O18/$J18,0)))))</f>
+        <v/>
+      </c>
+      <c r="S18" s="20">
+        <f>IF($B18="","",IF(N($O18)=0,0,IF(OR($L18="감소",AND($L18="증가",$M18&lt;&gt;"Y")),IF(N($G18)=0,0,ROUND(N(내역서!$H18)*$O18/$G18,0)),IF(N($J18)=0,0,ROUND(N(내역서!$P18)*$O18/$J18,0)))))</f>
+        <v/>
+      </c>
+      <c r="T18" s="20">
+        <f>IF($B18="","",N($O18)-N($R18)-N($S18))</f>
+        <v/>
+      </c>
+      <c r="U18" s="20">
+        <f>IF($B18="","",ROUND(N($K18)*N($R18),0))</f>
+        <v/>
+      </c>
+      <c r="V18" s="20">
+        <f>IF($B18="","",ROUND(N($K18)*N($S18),0))</f>
+        <v/>
+      </c>
+      <c r="W18" s="20">
+        <f>IF($B18="","",N($P18)-N($U18)-N($V18))</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="18">
@@ -3655,6 +4051,30 @@
         <f>IF($B19="","",IF($L19="감소","감소분 → 계약단가",IF(AND($M19="Y",OR($L19="증가",$L19="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L19="증가",IF(AND($N19&lt;&gt;"",$G19&gt;$N19),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L19="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R19" s="20">
+        <f>IF($B19="","",IF(N($O19)=0,0,IF(OR($L19="감소",AND($L19="증가",$M19&lt;&gt;"Y")),IF(N($G19)=0,0,ROUND(N(내역서!$G19)*$O19/$G19,0)),IF(N($J19)=0,0,ROUND(N(내역서!$O19)*$O19/$J19,0)))))</f>
+        <v/>
+      </c>
+      <c r="S19" s="20">
+        <f>IF($B19="","",IF(N($O19)=0,0,IF(OR($L19="감소",AND($L19="증가",$M19&lt;&gt;"Y")),IF(N($G19)=0,0,ROUND(N(내역서!$H19)*$O19/$G19,0)),IF(N($J19)=0,0,ROUND(N(내역서!$P19)*$O19/$J19,0)))))</f>
+        <v/>
+      </c>
+      <c r="T19" s="20">
+        <f>IF($B19="","",N($O19)-N($R19)-N($S19))</f>
+        <v/>
+      </c>
+      <c r="U19" s="20">
+        <f>IF($B19="","",ROUND(N($K19)*N($R19),0))</f>
+        <v/>
+      </c>
+      <c r="V19" s="20">
+        <f>IF($B19="","",ROUND(N($K19)*N($S19),0))</f>
+        <v/>
+      </c>
+      <c r="W19" s="20">
+        <f>IF($B19="","",N($P19)-N($U19)-N($V19))</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="18">
@@ -3719,6 +4139,30 @@
         <f>IF($B20="","",IF($L20="감소","감소분 → 계약단가",IF(AND($M20="Y",OR($L20="증가",$L20="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L20="증가",IF(AND($N20&lt;&gt;"",$G20&gt;$N20),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L20="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R20" s="20">
+        <f>IF($B20="","",IF(N($O20)=0,0,IF(OR($L20="감소",AND($L20="증가",$M20&lt;&gt;"Y")),IF(N($G20)=0,0,ROUND(N(내역서!$G20)*$O20/$G20,0)),IF(N($J20)=0,0,ROUND(N(내역서!$O20)*$O20/$J20,0)))))</f>
+        <v/>
+      </c>
+      <c r="S20" s="20">
+        <f>IF($B20="","",IF(N($O20)=0,0,IF(OR($L20="감소",AND($L20="증가",$M20&lt;&gt;"Y")),IF(N($G20)=0,0,ROUND(N(내역서!$H20)*$O20/$G20,0)),IF(N($J20)=0,0,ROUND(N(내역서!$P20)*$O20/$J20,0)))))</f>
+        <v/>
+      </c>
+      <c r="T20" s="20">
+        <f>IF($B20="","",N($O20)-N($R20)-N($S20))</f>
+        <v/>
+      </c>
+      <c r="U20" s="20">
+        <f>IF($B20="","",ROUND(N($K20)*N($R20),0))</f>
+        <v/>
+      </c>
+      <c r="V20" s="20">
+        <f>IF($B20="","",ROUND(N($K20)*N($S20),0))</f>
+        <v/>
+      </c>
+      <c r="W20" s="20">
+        <f>IF($B20="","",N($P20)-N($U20)-N($V20))</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="18">
@@ -3783,6 +4227,30 @@
         <f>IF($B21="","",IF($L21="감소","감소분 → 계약단가",IF(AND($M21="Y",OR($L21="증가",$L21="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L21="증가",IF(AND($N21&lt;&gt;"",$G21&gt;$N21),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L21="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R21" s="20">
+        <f>IF($B21="","",IF(N($O21)=0,0,IF(OR($L21="감소",AND($L21="증가",$M21&lt;&gt;"Y")),IF(N($G21)=0,0,ROUND(N(내역서!$G21)*$O21/$G21,0)),IF(N($J21)=0,0,ROUND(N(내역서!$O21)*$O21/$J21,0)))))</f>
+        <v/>
+      </c>
+      <c r="S21" s="20">
+        <f>IF($B21="","",IF(N($O21)=0,0,IF(OR($L21="감소",AND($L21="증가",$M21&lt;&gt;"Y")),IF(N($G21)=0,0,ROUND(N(내역서!$H21)*$O21/$G21,0)),IF(N($J21)=0,0,ROUND(N(내역서!$P21)*$O21/$J21,0)))))</f>
+        <v/>
+      </c>
+      <c r="T21" s="20">
+        <f>IF($B21="","",N($O21)-N($R21)-N($S21))</f>
+        <v/>
+      </c>
+      <c r="U21" s="20">
+        <f>IF($B21="","",ROUND(N($K21)*N($R21),0))</f>
+        <v/>
+      </c>
+      <c r="V21" s="20">
+        <f>IF($B21="","",ROUND(N($K21)*N($S21),0))</f>
+        <v/>
+      </c>
+      <c r="W21" s="20">
+        <f>IF($B21="","",N($P21)-N($U21)-N($V21))</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="18">
@@ -3847,6 +4315,30 @@
         <f>IF($B22="","",IF($L22="감소","감소분 → 계약단가",IF(AND($M22="Y",OR($L22="증가",$L22="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L22="증가",IF(AND($N22&lt;&gt;"",$G22&gt;$N22),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L22="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R22" s="20">
+        <f>IF($B22="","",IF(N($O22)=0,0,IF(OR($L22="감소",AND($L22="증가",$M22&lt;&gt;"Y")),IF(N($G22)=0,0,ROUND(N(내역서!$G22)*$O22/$G22,0)),IF(N($J22)=0,0,ROUND(N(내역서!$O22)*$O22/$J22,0)))))</f>
+        <v/>
+      </c>
+      <c r="S22" s="20">
+        <f>IF($B22="","",IF(N($O22)=0,0,IF(OR($L22="감소",AND($L22="증가",$M22&lt;&gt;"Y")),IF(N($G22)=0,0,ROUND(N(내역서!$H22)*$O22/$G22,0)),IF(N($J22)=0,0,ROUND(N(내역서!$P22)*$O22/$J22,0)))))</f>
+        <v/>
+      </c>
+      <c r="T22" s="20">
+        <f>IF($B22="","",N($O22)-N($R22)-N($S22))</f>
+        <v/>
+      </c>
+      <c r="U22" s="20">
+        <f>IF($B22="","",ROUND(N($K22)*N($R22),0))</f>
+        <v/>
+      </c>
+      <c r="V22" s="20">
+        <f>IF($B22="","",ROUND(N($K22)*N($S22),0))</f>
+        <v/>
+      </c>
+      <c r="W22" s="20">
+        <f>IF($B22="","",N($P22)-N($U22)-N($V22))</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="18">
@@ -3911,6 +4403,30 @@
         <f>IF($B23="","",IF($L23="감소","감소분 → 계약단가",IF(AND($M23="Y",OR($L23="증가",$L23="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L23="증가",IF(AND($N23&lt;&gt;"",$G23&gt;$N23),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L23="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R23" s="20">
+        <f>IF($B23="","",IF(N($O23)=0,0,IF(OR($L23="감소",AND($L23="증가",$M23&lt;&gt;"Y")),IF(N($G23)=0,0,ROUND(N(내역서!$G23)*$O23/$G23,0)),IF(N($J23)=0,0,ROUND(N(내역서!$O23)*$O23/$J23,0)))))</f>
+        <v/>
+      </c>
+      <c r="S23" s="20">
+        <f>IF($B23="","",IF(N($O23)=0,0,IF(OR($L23="감소",AND($L23="증가",$M23&lt;&gt;"Y")),IF(N($G23)=0,0,ROUND(N(내역서!$H23)*$O23/$G23,0)),IF(N($J23)=0,0,ROUND(N(내역서!$P23)*$O23/$J23,0)))))</f>
+        <v/>
+      </c>
+      <c r="T23" s="20">
+        <f>IF($B23="","",N($O23)-N($R23)-N($S23))</f>
+        <v/>
+      </c>
+      <c r="U23" s="20">
+        <f>IF($B23="","",ROUND(N($K23)*N($R23),0))</f>
+        <v/>
+      </c>
+      <c r="V23" s="20">
+        <f>IF($B23="","",ROUND(N($K23)*N($S23),0))</f>
+        <v/>
+      </c>
+      <c r="W23" s="20">
+        <f>IF($B23="","",N($P23)-N($U23)-N($V23))</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="18">
@@ -3975,6 +4491,30 @@
         <f>IF($B24="","",IF($L24="감소","감소분 → 계약단가",IF(AND($M24="Y",OR($L24="증가",$L24="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L24="증가",IF(AND($N24&lt;&gt;"",$G24&gt;$N24),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L24="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R24" s="20">
+        <f>IF($B24="","",IF(N($O24)=0,0,IF(OR($L24="감소",AND($L24="증가",$M24&lt;&gt;"Y")),IF(N($G24)=0,0,ROUND(N(내역서!$G24)*$O24/$G24,0)),IF(N($J24)=0,0,ROUND(N(내역서!$O24)*$O24/$J24,0)))))</f>
+        <v/>
+      </c>
+      <c r="S24" s="20">
+        <f>IF($B24="","",IF(N($O24)=0,0,IF(OR($L24="감소",AND($L24="증가",$M24&lt;&gt;"Y")),IF(N($G24)=0,0,ROUND(N(내역서!$H24)*$O24/$G24,0)),IF(N($J24)=0,0,ROUND(N(내역서!$P24)*$O24/$J24,0)))))</f>
+        <v/>
+      </c>
+      <c r="T24" s="20">
+        <f>IF($B24="","",N($O24)-N($R24)-N($S24))</f>
+        <v/>
+      </c>
+      <c r="U24" s="20">
+        <f>IF($B24="","",ROUND(N($K24)*N($R24),0))</f>
+        <v/>
+      </c>
+      <c r="V24" s="20">
+        <f>IF($B24="","",ROUND(N($K24)*N($S24),0))</f>
+        <v/>
+      </c>
+      <c r="W24" s="20">
+        <f>IF($B24="","",N($P24)-N($U24)-N($V24))</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="18">
@@ -4039,6 +4579,30 @@
         <f>IF($B25="","",IF($L25="감소","감소분 → 계약단가",IF(AND($M25="Y",OR($L25="증가",$L25="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L25="증가",IF(AND($N25&lt;&gt;"",$G25&gt;$N25),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L25="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R25" s="20">
+        <f>IF($B25="","",IF(N($O25)=0,0,IF(OR($L25="감소",AND($L25="증가",$M25&lt;&gt;"Y")),IF(N($G25)=0,0,ROUND(N(내역서!$G25)*$O25/$G25,0)),IF(N($J25)=0,0,ROUND(N(내역서!$O25)*$O25/$J25,0)))))</f>
+        <v/>
+      </c>
+      <c r="S25" s="20">
+        <f>IF($B25="","",IF(N($O25)=0,0,IF(OR($L25="감소",AND($L25="증가",$M25&lt;&gt;"Y")),IF(N($G25)=0,0,ROUND(N(내역서!$H25)*$O25/$G25,0)),IF(N($J25)=0,0,ROUND(N(내역서!$P25)*$O25/$J25,0)))))</f>
+        <v/>
+      </c>
+      <c r="T25" s="20">
+        <f>IF($B25="","",N($O25)-N($R25)-N($S25))</f>
+        <v/>
+      </c>
+      <c r="U25" s="20">
+        <f>IF($B25="","",ROUND(N($K25)*N($R25),0))</f>
+        <v/>
+      </c>
+      <c r="V25" s="20">
+        <f>IF($B25="","",ROUND(N($K25)*N($S25),0))</f>
+        <v/>
+      </c>
+      <c r="W25" s="20">
+        <f>IF($B25="","",N($P25)-N($U25)-N($V25))</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="18">
@@ -4103,6 +4667,30 @@
         <f>IF($B26="","",IF($L26="감소","감소분 → 계약단가",IF(AND($M26="Y",OR($L26="증가",$L26="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L26="증가",IF(AND($N26&lt;&gt;"",$G26&gt;$N26),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L26="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R26" s="20">
+        <f>IF($B26="","",IF(N($O26)=0,0,IF(OR($L26="감소",AND($L26="증가",$M26&lt;&gt;"Y")),IF(N($G26)=0,0,ROUND(N(내역서!$G26)*$O26/$G26,0)),IF(N($J26)=0,0,ROUND(N(내역서!$O26)*$O26/$J26,0)))))</f>
+        <v/>
+      </c>
+      <c r="S26" s="20">
+        <f>IF($B26="","",IF(N($O26)=0,0,IF(OR($L26="감소",AND($L26="증가",$M26&lt;&gt;"Y")),IF(N($G26)=0,0,ROUND(N(내역서!$H26)*$O26/$G26,0)),IF(N($J26)=0,0,ROUND(N(내역서!$P26)*$O26/$J26,0)))))</f>
+        <v/>
+      </c>
+      <c r="T26" s="20">
+        <f>IF($B26="","",N($O26)-N($R26)-N($S26))</f>
+        <v/>
+      </c>
+      <c r="U26" s="20">
+        <f>IF($B26="","",ROUND(N($K26)*N($R26),0))</f>
+        <v/>
+      </c>
+      <c r="V26" s="20">
+        <f>IF($B26="","",ROUND(N($K26)*N($S26),0))</f>
+        <v/>
+      </c>
+      <c r="W26" s="20">
+        <f>IF($B26="","",N($P26)-N($U26)-N($V26))</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="18">
@@ -4167,6 +4755,30 @@
         <f>IF($B27="","",IF($L27="감소","감소분 → 계약단가",IF(AND($M27="Y",OR($L27="증가",$L27="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L27="증가",IF(AND($N27&lt;&gt;"",$G27&gt;$N27),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L27="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R27" s="20">
+        <f>IF($B27="","",IF(N($O27)=0,0,IF(OR($L27="감소",AND($L27="증가",$M27&lt;&gt;"Y")),IF(N($G27)=0,0,ROUND(N(내역서!$G27)*$O27/$G27,0)),IF(N($J27)=0,0,ROUND(N(내역서!$O27)*$O27/$J27,0)))))</f>
+        <v/>
+      </c>
+      <c r="S27" s="20">
+        <f>IF($B27="","",IF(N($O27)=0,0,IF(OR($L27="감소",AND($L27="증가",$M27&lt;&gt;"Y")),IF(N($G27)=0,0,ROUND(N(내역서!$H27)*$O27/$G27,0)),IF(N($J27)=0,0,ROUND(N(내역서!$P27)*$O27/$J27,0)))))</f>
+        <v/>
+      </c>
+      <c r="T27" s="20">
+        <f>IF($B27="","",N($O27)-N($R27)-N($S27))</f>
+        <v/>
+      </c>
+      <c r="U27" s="20">
+        <f>IF($B27="","",ROUND(N($K27)*N($R27),0))</f>
+        <v/>
+      </c>
+      <c r="V27" s="20">
+        <f>IF($B27="","",ROUND(N($K27)*N($S27),0))</f>
+        <v/>
+      </c>
+      <c r="W27" s="20">
+        <f>IF($B27="","",N($P27)-N($U27)-N($V27))</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="18">
@@ -4231,6 +4843,30 @@
         <f>IF($B28="","",IF($L28="감소","감소분 → 계약단가",IF(AND($M28="Y",OR($L28="증가",$L28="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L28="증가",IF(AND($N28&lt;&gt;"",$G28&gt;$N28),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L28="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R28" s="20">
+        <f>IF($B28="","",IF(N($O28)=0,0,IF(OR($L28="감소",AND($L28="증가",$M28&lt;&gt;"Y")),IF(N($G28)=0,0,ROUND(N(내역서!$G28)*$O28/$G28,0)),IF(N($J28)=0,0,ROUND(N(내역서!$O28)*$O28/$J28,0)))))</f>
+        <v/>
+      </c>
+      <c r="S28" s="20">
+        <f>IF($B28="","",IF(N($O28)=0,0,IF(OR($L28="감소",AND($L28="증가",$M28&lt;&gt;"Y")),IF(N($G28)=0,0,ROUND(N(내역서!$H28)*$O28/$G28,0)),IF(N($J28)=0,0,ROUND(N(내역서!$P28)*$O28/$J28,0)))))</f>
+        <v/>
+      </c>
+      <c r="T28" s="20">
+        <f>IF($B28="","",N($O28)-N($R28)-N($S28))</f>
+        <v/>
+      </c>
+      <c r="U28" s="20">
+        <f>IF($B28="","",ROUND(N($K28)*N($R28),0))</f>
+        <v/>
+      </c>
+      <c r="V28" s="20">
+        <f>IF($B28="","",ROUND(N($K28)*N($S28),0))</f>
+        <v/>
+      </c>
+      <c r="W28" s="20">
+        <f>IF($B28="","",N($P28)-N($U28)-N($V28))</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="18">
@@ -4295,6 +4931,30 @@
         <f>IF($B29="","",IF($L29="감소","감소분 → 계약단가",IF(AND($M29="Y",OR($L29="증가",$L29="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L29="증가",IF(AND($N29&lt;&gt;"",$G29&gt;$N29),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L29="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R29" s="20">
+        <f>IF($B29="","",IF(N($O29)=0,0,IF(OR($L29="감소",AND($L29="증가",$M29&lt;&gt;"Y")),IF(N($G29)=0,0,ROUND(N(내역서!$G29)*$O29/$G29,0)),IF(N($J29)=0,0,ROUND(N(내역서!$O29)*$O29/$J29,0)))))</f>
+        <v/>
+      </c>
+      <c r="S29" s="20">
+        <f>IF($B29="","",IF(N($O29)=0,0,IF(OR($L29="감소",AND($L29="증가",$M29&lt;&gt;"Y")),IF(N($G29)=0,0,ROUND(N(내역서!$H29)*$O29/$G29,0)),IF(N($J29)=0,0,ROUND(N(내역서!$P29)*$O29/$J29,0)))))</f>
+        <v/>
+      </c>
+      <c r="T29" s="20">
+        <f>IF($B29="","",N($O29)-N($R29)-N($S29))</f>
+        <v/>
+      </c>
+      <c r="U29" s="20">
+        <f>IF($B29="","",ROUND(N($K29)*N($R29),0))</f>
+        <v/>
+      </c>
+      <c r="V29" s="20">
+        <f>IF($B29="","",ROUND(N($K29)*N($S29),0))</f>
+        <v/>
+      </c>
+      <c r="W29" s="20">
+        <f>IF($B29="","",N($P29)-N($U29)-N($V29))</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="18">
@@ -4359,6 +5019,30 @@
         <f>IF($B30="","",IF($L30="감소","감소분 → 계약단가",IF(AND($M30="Y",OR($L30="증가",$L30="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L30="증가",IF(AND($N30&lt;&gt;"",$G30&gt;$N30),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L30="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R30" s="20">
+        <f>IF($B30="","",IF(N($O30)=0,0,IF(OR($L30="감소",AND($L30="증가",$M30&lt;&gt;"Y")),IF(N($G30)=0,0,ROUND(N(내역서!$G30)*$O30/$G30,0)),IF(N($J30)=0,0,ROUND(N(내역서!$O30)*$O30/$J30,0)))))</f>
+        <v/>
+      </c>
+      <c r="S30" s="20">
+        <f>IF($B30="","",IF(N($O30)=0,0,IF(OR($L30="감소",AND($L30="증가",$M30&lt;&gt;"Y")),IF(N($G30)=0,0,ROUND(N(내역서!$H30)*$O30/$G30,0)),IF(N($J30)=0,0,ROUND(N(내역서!$P30)*$O30/$J30,0)))))</f>
+        <v/>
+      </c>
+      <c r="T30" s="20">
+        <f>IF($B30="","",N($O30)-N($R30)-N($S30))</f>
+        <v/>
+      </c>
+      <c r="U30" s="20">
+        <f>IF($B30="","",ROUND(N($K30)*N($R30),0))</f>
+        <v/>
+      </c>
+      <c r="V30" s="20">
+        <f>IF($B30="","",ROUND(N($K30)*N($S30),0))</f>
+        <v/>
+      </c>
+      <c r="W30" s="20">
+        <f>IF($B30="","",N($P30)-N($U30)-N($V30))</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="18">
@@ -4423,6 +5107,30 @@
         <f>IF($B31="","",IF($L31="감소","감소분 → 계약단가",IF(AND($M31="Y",OR($L31="증가",$L31="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L31="증가",IF(AND($N31&lt;&gt;"",$G31&gt;$N31),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L31="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R31" s="20">
+        <f>IF($B31="","",IF(N($O31)=0,0,IF(OR($L31="감소",AND($L31="증가",$M31&lt;&gt;"Y")),IF(N($G31)=0,0,ROUND(N(내역서!$G31)*$O31/$G31,0)),IF(N($J31)=0,0,ROUND(N(내역서!$O31)*$O31/$J31,0)))))</f>
+        <v/>
+      </c>
+      <c r="S31" s="20">
+        <f>IF($B31="","",IF(N($O31)=0,0,IF(OR($L31="감소",AND($L31="증가",$M31&lt;&gt;"Y")),IF(N($G31)=0,0,ROUND(N(내역서!$H31)*$O31/$G31,0)),IF(N($J31)=0,0,ROUND(N(내역서!$P31)*$O31/$J31,0)))))</f>
+        <v/>
+      </c>
+      <c r="T31" s="20">
+        <f>IF($B31="","",N($O31)-N($R31)-N($S31))</f>
+        <v/>
+      </c>
+      <c r="U31" s="20">
+        <f>IF($B31="","",ROUND(N($K31)*N($R31),0))</f>
+        <v/>
+      </c>
+      <c r="V31" s="20">
+        <f>IF($B31="","",ROUND(N($K31)*N($S31),0))</f>
+        <v/>
+      </c>
+      <c r="W31" s="20">
+        <f>IF($B31="","",N($P31)-N($U31)-N($V31))</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="18">
@@ -4487,6 +5195,30 @@
         <f>IF($B32="","",IF($L32="감소","감소분 → 계약단가",IF(AND($M32="Y",OR($L32="증가",$L32="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L32="증가",IF(AND($N32&lt;&gt;"",$G32&gt;$N32),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L32="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R32" s="20">
+        <f>IF($B32="","",IF(N($O32)=0,0,IF(OR($L32="감소",AND($L32="증가",$M32&lt;&gt;"Y")),IF(N($G32)=0,0,ROUND(N(내역서!$G32)*$O32/$G32,0)),IF(N($J32)=0,0,ROUND(N(내역서!$O32)*$O32/$J32,0)))))</f>
+        <v/>
+      </c>
+      <c r="S32" s="20">
+        <f>IF($B32="","",IF(N($O32)=0,0,IF(OR($L32="감소",AND($L32="증가",$M32&lt;&gt;"Y")),IF(N($G32)=0,0,ROUND(N(내역서!$H32)*$O32/$G32,0)),IF(N($J32)=0,0,ROUND(N(내역서!$P32)*$O32/$J32,0)))))</f>
+        <v/>
+      </c>
+      <c r="T32" s="20">
+        <f>IF($B32="","",N($O32)-N($R32)-N($S32))</f>
+        <v/>
+      </c>
+      <c r="U32" s="20">
+        <f>IF($B32="","",ROUND(N($K32)*N($R32),0))</f>
+        <v/>
+      </c>
+      <c r="V32" s="20">
+        <f>IF($B32="","",ROUND(N($K32)*N($S32),0))</f>
+        <v/>
+      </c>
+      <c r="W32" s="20">
+        <f>IF($B32="","",N($P32)-N($U32)-N($V32))</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="18">
@@ -4551,6 +5283,30 @@
         <f>IF($B33="","",IF($L33="감소","감소분 → 계약단가",IF(AND($M33="Y",OR($L33="증가",$L33="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L33="증가",IF(AND($N33&lt;&gt;"",$G33&gt;$N33),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L33="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R33" s="20">
+        <f>IF($B33="","",IF(N($O33)=0,0,IF(OR($L33="감소",AND($L33="증가",$M33&lt;&gt;"Y")),IF(N($G33)=0,0,ROUND(N(내역서!$G33)*$O33/$G33,0)),IF(N($J33)=0,0,ROUND(N(내역서!$O33)*$O33/$J33,0)))))</f>
+        <v/>
+      </c>
+      <c r="S33" s="20">
+        <f>IF($B33="","",IF(N($O33)=0,0,IF(OR($L33="감소",AND($L33="증가",$M33&lt;&gt;"Y")),IF(N($G33)=0,0,ROUND(N(내역서!$H33)*$O33/$G33,0)),IF(N($J33)=0,0,ROUND(N(내역서!$P33)*$O33/$J33,0)))))</f>
+        <v/>
+      </c>
+      <c r="T33" s="20">
+        <f>IF($B33="","",N($O33)-N($R33)-N($S33))</f>
+        <v/>
+      </c>
+      <c r="U33" s="20">
+        <f>IF($B33="","",ROUND(N($K33)*N($R33),0))</f>
+        <v/>
+      </c>
+      <c r="V33" s="20">
+        <f>IF($B33="","",ROUND(N($K33)*N($S33),0))</f>
+        <v/>
+      </c>
+      <c r="W33" s="20">
+        <f>IF($B33="","",N($P33)-N($U33)-N($V33))</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="18">
@@ -4615,6 +5371,30 @@
         <f>IF($B34="","",IF($L34="감소","감소분 → 계약단가",IF(AND($M34="Y",OR($L34="증가",$L34="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L34="증가",IF(AND($N34&lt;&gt;"",$G34&gt;$N34),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L34="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R34" s="20">
+        <f>IF($B34="","",IF(N($O34)=0,0,IF(OR($L34="감소",AND($L34="증가",$M34&lt;&gt;"Y")),IF(N($G34)=0,0,ROUND(N(내역서!$G34)*$O34/$G34,0)),IF(N($J34)=0,0,ROUND(N(내역서!$O34)*$O34/$J34,0)))))</f>
+        <v/>
+      </c>
+      <c r="S34" s="20">
+        <f>IF($B34="","",IF(N($O34)=0,0,IF(OR($L34="감소",AND($L34="증가",$M34&lt;&gt;"Y")),IF(N($G34)=0,0,ROUND(N(내역서!$H34)*$O34/$G34,0)),IF(N($J34)=0,0,ROUND(N(내역서!$P34)*$O34/$J34,0)))))</f>
+        <v/>
+      </c>
+      <c r="T34" s="20">
+        <f>IF($B34="","",N($O34)-N($R34)-N($S34))</f>
+        <v/>
+      </c>
+      <c r="U34" s="20">
+        <f>IF($B34="","",ROUND(N($K34)*N($R34),0))</f>
+        <v/>
+      </c>
+      <c r="V34" s="20">
+        <f>IF($B34="","",ROUND(N($K34)*N($S34),0))</f>
+        <v/>
+      </c>
+      <c r="W34" s="20">
+        <f>IF($B34="","",N($P34)-N($U34)-N($V34))</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="18">
@@ -4679,6 +5459,30 @@
         <f>IF($B35="","",IF($L35="감소","감소분 → 계약단가",IF(AND($M35="Y",OR($L35="증가",$L35="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L35="증가",IF(AND($N35&lt;&gt;"",$G35&gt;$N35),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L35="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R35" s="20">
+        <f>IF($B35="","",IF(N($O35)=0,0,IF(OR($L35="감소",AND($L35="증가",$M35&lt;&gt;"Y")),IF(N($G35)=0,0,ROUND(N(내역서!$G35)*$O35/$G35,0)),IF(N($J35)=0,0,ROUND(N(내역서!$O35)*$O35/$J35,0)))))</f>
+        <v/>
+      </c>
+      <c r="S35" s="20">
+        <f>IF($B35="","",IF(N($O35)=0,0,IF(OR($L35="감소",AND($L35="증가",$M35&lt;&gt;"Y")),IF(N($G35)=0,0,ROUND(N(내역서!$H35)*$O35/$G35,0)),IF(N($J35)=0,0,ROUND(N(내역서!$P35)*$O35/$J35,0)))))</f>
+        <v/>
+      </c>
+      <c r="T35" s="20">
+        <f>IF($B35="","",N($O35)-N($R35)-N($S35))</f>
+        <v/>
+      </c>
+      <c r="U35" s="20">
+        <f>IF($B35="","",ROUND(N($K35)*N($R35),0))</f>
+        <v/>
+      </c>
+      <c r="V35" s="20">
+        <f>IF($B35="","",ROUND(N($K35)*N($S35),0))</f>
+        <v/>
+      </c>
+      <c r="W35" s="20">
+        <f>IF($B35="","",N($P35)-N($U35)-N($V35))</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="18">
@@ -4743,6 +5547,30 @@
         <f>IF($B36="","",IF($L36="감소","감소분 → 계약단가",IF(AND($M36="Y",OR($L36="증가",$L36="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L36="증가",IF(AND($N36&lt;&gt;"",$G36&gt;$N36),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L36="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R36" s="20">
+        <f>IF($B36="","",IF(N($O36)=0,0,IF(OR($L36="감소",AND($L36="증가",$M36&lt;&gt;"Y")),IF(N($G36)=0,0,ROUND(N(내역서!$G36)*$O36/$G36,0)),IF(N($J36)=0,0,ROUND(N(내역서!$O36)*$O36/$J36,0)))))</f>
+        <v/>
+      </c>
+      <c r="S36" s="20">
+        <f>IF($B36="","",IF(N($O36)=0,0,IF(OR($L36="감소",AND($L36="증가",$M36&lt;&gt;"Y")),IF(N($G36)=0,0,ROUND(N(내역서!$H36)*$O36/$G36,0)),IF(N($J36)=0,0,ROUND(N(내역서!$P36)*$O36/$J36,0)))))</f>
+        <v/>
+      </c>
+      <c r="T36" s="20">
+        <f>IF($B36="","",N($O36)-N($R36)-N($S36))</f>
+        <v/>
+      </c>
+      <c r="U36" s="20">
+        <f>IF($B36="","",ROUND(N($K36)*N($R36),0))</f>
+        <v/>
+      </c>
+      <c r="V36" s="20">
+        <f>IF($B36="","",ROUND(N($K36)*N($S36),0))</f>
+        <v/>
+      </c>
+      <c r="W36" s="20">
+        <f>IF($B36="","",N($P36)-N($U36)-N($V36))</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="18">
@@ -4807,6 +5635,30 @@
         <f>IF($B37="","",IF($L37="감소","감소분 → 계약단가",IF(AND($M37="Y",OR($L37="증가",$L37="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L37="증가",IF(AND($N37&lt;&gt;"",$G37&gt;$N37),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L37="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R37" s="20">
+        <f>IF($B37="","",IF(N($O37)=0,0,IF(OR($L37="감소",AND($L37="증가",$M37&lt;&gt;"Y")),IF(N($G37)=0,0,ROUND(N(내역서!$G37)*$O37/$G37,0)),IF(N($J37)=0,0,ROUND(N(내역서!$O37)*$O37/$J37,0)))))</f>
+        <v/>
+      </c>
+      <c r="S37" s="20">
+        <f>IF($B37="","",IF(N($O37)=0,0,IF(OR($L37="감소",AND($L37="증가",$M37&lt;&gt;"Y")),IF(N($G37)=0,0,ROUND(N(내역서!$H37)*$O37/$G37,0)),IF(N($J37)=0,0,ROUND(N(내역서!$P37)*$O37/$J37,0)))))</f>
+        <v/>
+      </c>
+      <c r="T37" s="20">
+        <f>IF($B37="","",N($O37)-N($R37)-N($S37))</f>
+        <v/>
+      </c>
+      <c r="U37" s="20">
+        <f>IF($B37="","",ROUND(N($K37)*N($R37),0))</f>
+        <v/>
+      </c>
+      <c r="V37" s="20">
+        <f>IF($B37="","",ROUND(N($K37)*N($S37),0))</f>
+        <v/>
+      </c>
+      <c r="W37" s="20">
+        <f>IF($B37="","",N($P37)-N($U37)-N($V37))</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="18">
@@ -4871,6 +5723,30 @@
         <f>IF($B38="","",IF($L38="감소","감소분 → 계약단가",IF(AND($M38="Y",OR($L38="증가",$L38="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L38="증가",IF(AND($N38&lt;&gt;"",$G38&gt;$N38),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L38="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R38" s="20">
+        <f>IF($B38="","",IF(N($O38)=0,0,IF(OR($L38="감소",AND($L38="증가",$M38&lt;&gt;"Y")),IF(N($G38)=0,0,ROUND(N(내역서!$G38)*$O38/$G38,0)),IF(N($J38)=0,0,ROUND(N(내역서!$O38)*$O38/$J38,0)))))</f>
+        <v/>
+      </c>
+      <c r="S38" s="20">
+        <f>IF($B38="","",IF(N($O38)=0,0,IF(OR($L38="감소",AND($L38="증가",$M38&lt;&gt;"Y")),IF(N($G38)=0,0,ROUND(N(내역서!$H38)*$O38/$G38,0)),IF(N($J38)=0,0,ROUND(N(내역서!$P38)*$O38/$J38,0)))))</f>
+        <v/>
+      </c>
+      <c r="T38" s="20">
+        <f>IF($B38="","",N($O38)-N($R38)-N($S38))</f>
+        <v/>
+      </c>
+      <c r="U38" s="20">
+        <f>IF($B38="","",ROUND(N($K38)*N($R38),0))</f>
+        <v/>
+      </c>
+      <c r="V38" s="20">
+        <f>IF($B38="","",ROUND(N($K38)*N($S38),0))</f>
+        <v/>
+      </c>
+      <c r="W38" s="20">
+        <f>IF($B38="","",N($P38)-N($U38)-N($V38))</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="18">
@@ -4935,6 +5811,30 @@
         <f>IF($B39="","",IF($L39="감소","감소분 → 계약단가",IF(AND($M39="Y",OR($L39="증가",$L39="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L39="증가",IF(AND($N39&lt;&gt;"",$G39&gt;$N39),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L39="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R39" s="20">
+        <f>IF($B39="","",IF(N($O39)=0,0,IF(OR($L39="감소",AND($L39="증가",$M39&lt;&gt;"Y")),IF(N($G39)=0,0,ROUND(N(내역서!$G39)*$O39/$G39,0)),IF(N($J39)=0,0,ROUND(N(내역서!$O39)*$O39/$J39,0)))))</f>
+        <v/>
+      </c>
+      <c r="S39" s="20">
+        <f>IF($B39="","",IF(N($O39)=0,0,IF(OR($L39="감소",AND($L39="증가",$M39&lt;&gt;"Y")),IF(N($G39)=0,0,ROUND(N(내역서!$H39)*$O39/$G39,0)),IF(N($J39)=0,0,ROUND(N(내역서!$P39)*$O39/$J39,0)))))</f>
+        <v/>
+      </c>
+      <c r="T39" s="20">
+        <f>IF($B39="","",N($O39)-N($R39)-N($S39))</f>
+        <v/>
+      </c>
+      <c r="U39" s="20">
+        <f>IF($B39="","",ROUND(N($K39)*N($R39),0))</f>
+        <v/>
+      </c>
+      <c r="V39" s="20">
+        <f>IF($B39="","",ROUND(N($K39)*N($S39),0))</f>
+        <v/>
+      </c>
+      <c r="W39" s="20">
+        <f>IF($B39="","",N($P39)-N($U39)-N($V39))</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="18">
@@ -4999,6 +5899,30 @@
         <f>IF($B40="","",IF($L40="감소","감소분 → 계약단가",IF(AND($M40="Y",OR($L40="증가",$L40="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L40="증가",IF(AND($N40&lt;&gt;"",$G40&gt;$N40),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L40="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R40" s="20">
+        <f>IF($B40="","",IF(N($O40)=0,0,IF(OR($L40="감소",AND($L40="증가",$M40&lt;&gt;"Y")),IF(N($G40)=0,0,ROUND(N(내역서!$G40)*$O40/$G40,0)),IF(N($J40)=0,0,ROUND(N(내역서!$O40)*$O40/$J40,0)))))</f>
+        <v/>
+      </c>
+      <c r="S40" s="20">
+        <f>IF($B40="","",IF(N($O40)=0,0,IF(OR($L40="감소",AND($L40="증가",$M40&lt;&gt;"Y")),IF(N($G40)=0,0,ROUND(N(내역서!$H40)*$O40/$G40,0)),IF(N($J40)=0,0,ROUND(N(내역서!$P40)*$O40/$J40,0)))))</f>
+        <v/>
+      </c>
+      <c r="T40" s="20">
+        <f>IF($B40="","",N($O40)-N($R40)-N($S40))</f>
+        <v/>
+      </c>
+      <c r="U40" s="20">
+        <f>IF($B40="","",ROUND(N($K40)*N($R40),0))</f>
+        <v/>
+      </c>
+      <c r="V40" s="20">
+        <f>IF($B40="","",ROUND(N($K40)*N($S40),0))</f>
+        <v/>
+      </c>
+      <c r="W40" s="20">
+        <f>IF($B40="","",N($P40)-N($U40)-N($V40))</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="18">
@@ -5063,6 +5987,30 @@
         <f>IF($B41="","",IF($L41="감소","감소분 → 계약단가",IF(AND($M41="Y",OR($L41="증가",$L41="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L41="증가",IF(AND($N41&lt;&gt;"",$G41&gt;$N41),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L41="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R41" s="20">
+        <f>IF($B41="","",IF(N($O41)=0,0,IF(OR($L41="감소",AND($L41="증가",$M41&lt;&gt;"Y")),IF(N($G41)=0,0,ROUND(N(내역서!$G41)*$O41/$G41,0)),IF(N($J41)=0,0,ROUND(N(내역서!$O41)*$O41/$J41,0)))))</f>
+        <v/>
+      </c>
+      <c r="S41" s="20">
+        <f>IF($B41="","",IF(N($O41)=0,0,IF(OR($L41="감소",AND($L41="증가",$M41&lt;&gt;"Y")),IF(N($G41)=0,0,ROUND(N(내역서!$H41)*$O41/$G41,0)),IF(N($J41)=0,0,ROUND(N(내역서!$P41)*$O41/$J41,0)))))</f>
+        <v/>
+      </c>
+      <c r="T41" s="20">
+        <f>IF($B41="","",N($O41)-N($R41)-N($S41))</f>
+        <v/>
+      </c>
+      <c r="U41" s="20">
+        <f>IF($B41="","",ROUND(N($K41)*N($R41),0))</f>
+        <v/>
+      </c>
+      <c r="V41" s="20">
+        <f>IF($B41="","",ROUND(N($K41)*N($S41),0))</f>
+        <v/>
+      </c>
+      <c r="W41" s="20">
+        <f>IF($B41="","",N($P41)-N($U41)-N($V41))</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="18">
@@ -5127,6 +6075,30 @@
         <f>IF($B42="","",IF($L42="감소","감소분 → 계약단가",IF(AND($M42="Y",OR($L42="증가",$L42="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L42="증가",IF(AND($N42&lt;&gt;"",$G42&gt;$N42),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L42="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R42" s="20">
+        <f>IF($B42="","",IF(N($O42)=0,0,IF(OR($L42="감소",AND($L42="증가",$M42&lt;&gt;"Y")),IF(N($G42)=0,0,ROUND(N(내역서!$G42)*$O42/$G42,0)),IF(N($J42)=0,0,ROUND(N(내역서!$O42)*$O42/$J42,0)))))</f>
+        <v/>
+      </c>
+      <c r="S42" s="20">
+        <f>IF($B42="","",IF(N($O42)=0,0,IF(OR($L42="감소",AND($L42="증가",$M42&lt;&gt;"Y")),IF(N($G42)=0,0,ROUND(N(내역서!$H42)*$O42/$G42,0)),IF(N($J42)=0,0,ROUND(N(내역서!$P42)*$O42/$J42,0)))))</f>
+        <v/>
+      </c>
+      <c r="T42" s="20">
+        <f>IF($B42="","",N($O42)-N($R42)-N($S42))</f>
+        <v/>
+      </c>
+      <c r="U42" s="20">
+        <f>IF($B42="","",ROUND(N($K42)*N($R42),0))</f>
+        <v/>
+      </c>
+      <c r="V42" s="20">
+        <f>IF($B42="","",ROUND(N($K42)*N($S42),0))</f>
+        <v/>
+      </c>
+      <c r="W42" s="20">
+        <f>IF($B42="","",N($P42)-N($U42)-N($V42))</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="18">
@@ -5191,6 +6163,30 @@
         <f>IF($B43="","",IF($L43="감소","감소분 → 계약단가",IF(AND($M43="Y",OR($L43="증가",$L43="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L43="증가",IF(AND($N43&lt;&gt;"",$G43&gt;$N43),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L43="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R43" s="20">
+        <f>IF($B43="","",IF(N($O43)=0,0,IF(OR($L43="감소",AND($L43="증가",$M43&lt;&gt;"Y")),IF(N($G43)=0,0,ROUND(N(내역서!$G43)*$O43/$G43,0)),IF(N($J43)=0,0,ROUND(N(내역서!$O43)*$O43/$J43,0)))))</f>
+        <v/>
+      </c>
+      <c r="S43" s="20">
+        <f>IF($B43="","",IF(N($O43)=0,0,IF(OR($L43="감소",AND($L43="증가",$M43&lt;&gt;"Y")),IF(N($G43)=0,0,ROUND(N(내역서!$H43)*$O43/$G43,0)),IF(N($J43)=0,0,ROUND(N(내역서!$P43)*$O43/$J43,0)))))</f>
+        <v/>
+      </c>
+      <c r="T43" s="20">
+        <f>IF($B43="","",N($O43)-N($R43)-N($S43))</f>
+        <v/>
+      </c>
+      <c r="U43" s="20">
+        <f>IF($B43="","",ROUND(N($K43)*N($R43),0))</f>
+        <v/>
+      </c>
+      <c r="V43" s="20">
+        <f>IF($B43="","",ROUND(N($K43)*N($S43),0))</f>
+        <v/>
+      </c>
+      <c r="W43" s="20">
+        <f>IF($B43="","",N($P43)-N($U43)-N($V43))</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="18">
@@ -5255,6 +6251,30 @@
         <f>IF($B44="","",IF($L44="감소","감소분 → 계약단가",IF(AND($M44="Y",OR($L44="증가",$L44="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L44="증가",IF(AND($N44&lt;&gt;"",$G44&gt;$N44),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L44="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R44" s="20">
+        <f>IF($B44="","",IF(N($O44)=0,0,IF(OR($L44="감소",AND($L44="증가",$M44&lt;&gt;"Y")),IF(N($G44)=0,0,ROUND(N(내역서!$G44)*$O44/$G44,0)),IF(N($J44)=0,0,ROUND(N(내역서!$O44)*$O44/$J44,0)))))</f>
+        <v/>
+      </c>
+      <c r="S44" s="20">
+        <f>IF($B44="","",IF(N($O44)=0,0,IF(OR($L44="감소",AND($L44="증가",$M44&lt;&gt;"Y")),IF(N($G44)=0,0,ROUND(N(내역서!$H44)*$O44/$G44,0)),IF(N($J44)=0,0,ROUND(N(내역서!$P44)*$O44/$J44,0)))))</f>
+        <v/>
+      </c>
+      <c r="T44" s="20">
+        <f>IF($B44="","",N($O44)-N($R44)-N($S44))</f>
+        <v/>
+      </c>
+      <c r="U44" s="20">
+        <f>IF($B44="","",ROUND(N($K44)*N($R44),0))</f>
+        <v/>
+      </c>
+      <c r="V44" s="20">
+        <f>IF($B44="","",ROUND(N($K44)*N($S44),0))</f>
+        <v/>
+      </c>
+      <c r="W44" s="20">
+        <f>IF($B44="","",N($P44)-N($U44)-N($V44))</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="18">
@@ -5319,6 +6339,30 @@
         <f>IF($B45="","",IF($L45="감소","감소분 → 계약단가",IF(AND($M45="Y",OR($L45="증가",$L45="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L45="증가",IF(AND($N45&lt;&gt;"",$G45&gt;$N45),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L45="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R45" s="20">
+        <f>IF($B45="","",IF(N($O45)=0,0,IF(OR($L45="감소",AND($L45="증가",$M45&lt;&gt;"Y")),IF(N($G45)=0,0,ROUND(N(내역서!$G45)*$O45/$G45,0)),IF(N($J45)=0,0,ROUND(N(내역서!$O45)*$O45/$J45,0)))))</f>
+        <v/>
+      </c>
+      <c r="S45" s="20">
+        <f>IF($B45="","",IF(N($O45)=0,0,IF(OR($L45="감소",AND($L45="증가",$M45&lt;&gt;"Y")),IF(N($G45)=0,0,ROUND(N(내역서!$H45)*$O45/$G45,0)),IF(N($J45)=0,0,ROUND(N(내역서!$P45)*$O45/$J45,0)))))</f>
+        <v/>
+      </c>
+      <c r="T45" s="20">
+        <f>IF($B45="","",N($O45)-N($R45)-N($S45))</f>
+        <v/>
+      </c>
+      <c r="U45" s="20">
+        <f>IF($B45="","",ROUND(N($K45)*N($R45),0))</f>
+        <v/>
+      </c>
+      <c r="V45" s="20">
+        <f>IF($B45="","",ROUND(N($K45)*N($S45),0))</f>
+        <v/>
+      </c>
+      <c r="W45" s="20">
+        <f>IF($B45="","",N($P45)-N($U45)-N($V45))</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="18">
@@ -5383,6 +6427,30 @@
         <f>IF($B46="","",IF($L46="감소","감소분 → 계약단가",IF(AND($M46="Y",OR($L46="증가",$L46="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L46="증가",IF(AND($N46&lt;&gt;"",$G46&gt;$N46),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L46="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R46" s="20">
+        <f>IF($B46="","",IF(N($O46)=0,0,IF(OR($L46="감소",AND($L46="증가",$M46&lt;&gt;"Y")),IF(N($G46)=0,0,ROUND(N(내역서!$G46)*$O46/$G46,0)),IF(N($J46)=0,0,ROUND(N(내역서!$O46)*$O46/$J46,0)))))</f>
+        <v/>
+      </c>
+      <c r="S46" s="20">
+        <f>IF($B46="","",IF(N($O46)=0,0,IF(OR($L46="감소",AND($L46="증가",$M46&lt;&gt;"Y")),IF(N($G46)=0,0,ROUND(N(내역서!$H46)*$O46/$G46,0)),IF(N($J46)=0,0,ROUND(N(내역서!$P46)*$O46/$J46,0)))))</f>
+        <v/>
+      </c>
+      <c r="T46" s="20">
+        <f>IF($B46="","",N($O46)-N($R46)-N($S46))</f>
+        <v/>
+      </c>
+      <c r="U46" s="20">
+        <f>IF($B46="","",ROUND(N($K46)*N($R46),0))</f>
+        <v/>
+      </c>
+      <c r="V46" s="20">
+        <f>IF($B46="","",ROUND(N($K46)*N($S46),0))</f>
+        <v/>
+      </c>
+      <c r="W46" s="20">
+        <f>IF($B46="","",N($P46)-N($U46)-N($V46))</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="18">
@@ -5447,6 +6515,30 @@
         <f>IF($B47="","",IF($L47="감소","감소분 → 계약단가",IF(AND($M47="Y",OR($L47="증가",$L47="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L47="증가",IF(AND($N47&lt;&gt;"",$G47&gt;$N47),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L47="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R47" s="20">
+        <f>IF($B47="","",IF(N($O47)=0,0,IF(OR($L47="감소",AND($L47="증가",$M47&lt;&gt;"Y")),IF(N($G47)=0,0,ROUND(N(내역서!$G47)*$O47/$G47,0)),IF(N($J47)=0,0,ROUND(N(내역서!$O47)*$O47/$J47,0)))))</f>
+        <v/>
+      </c>
+      <c r="S47" s="20">
+        <f>IF($B47="","",IF(N($O47)=0,0,IF(OR($L47="감소",AND($L47="증가",$M47&lt;&gt;"Y")),IF(N($G47)=0,0,ROUND(N(내역서!$H47)*$O47/$G47,0)),IF(N($J47)=0,0,ROUND(N(내역서!$P47)*$O47/$J47,0)))))</f>
+        <v/>
+      </c>
+      <c r="T47" s="20">
+        <f>IF($B47="","",N($O47)-N($R47)-N($S47))</f>
+        <v/>
+      </c>
+      <c r="U47" s="20">
+        <f>IF($B47="","",ROUND(N($K47)*N($R47),0))</f>
+        <v/>
+      </c>
+      <c r="V47" s="20">
+        <f>IF($B47="","",ROUND(N($K47)*N($S47),0))</f>
+        <v/>
+      </c>
+      <c r="W47" s="20">
+        <f>IF($B47="","",N($P47)-N($U47)-N($V47))</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="18">
@@ -5511,6 +6603,30 @@
         <f>IF($B48="","",IF($L48="감소","감소분 → 계약단가",IF(AND($M48="Y",OR($L48="증가",$L48="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L48="증가",IF(AND($N48&lt;&gt;"",$G48&gt;$N48),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L48="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R48" s="20">
+        <f>IF($B48="","",IF(N($O48)=0,0,IF(OR($L48="감소",AND($L48="증가",$M48&lt;&gt;"Y")),IF(N($G48)=0,0,ROUND(N(내역서!$G48)*$O48/$G48,0)),IF(N($J48)=0,0,ROUND(N(내역서!$O48)*$O48/$J48,0)))))</f>
+        <v/>
+      </c>
+      <c r="S48" s="20">
+        <f>IF($B48="","",IF(N($O48)=0,0,IF(OR($L48="감소",AND($L48="증가",$M48&lt;&gt;"Y")),IF(N($G48)=0,0,ROUND(N(내역서!$H48)*$O48/$G48,0)),IF(N($J48)=0,0,ROUND(N(내역서!$P48)*$O48/$J48,0)))))</f>
+        <v/>
+      </c>
+      <c r="T48" s="20">
+        <f>IF($B48="","",N($O48)-N($R48)-N($S48))</f>
+        <v/>
+      </c>
+      <c r="U48" s="20">
+        <f>IF($B48="","",ROUND(N($K48)*N($R48),0))</f>
+        <v/>
+      </c>
+      <c r="V48" s="20">
+        <f>IF($B48="","",ROUND(N($K48)*N($S48),0))</f>
+        <v/>
+      </c>
+      <c r="W48" s="20">
+        <f>IF($B48="","",N($P48)-N($U48)-N($V48))</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="18">
@@ -5575,6 +6691,30 @@
         <f>IF($B49="","",IF($L49="감소","감소분 → 계약단가",IF(AND($M49="Y",OR($L49="증가",$L49="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L49="증가",IF(AND($N49&lt;&gt;"",$G49&gt;$N49),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L49="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R49" s="20">
+        <f>IF($B49="","",IF(N($O49)=0,0,IF(OR($L49="감소",AND($L49="증가",$M49&lt;&gt;"Y")),IF(N($G49)=0,0,ROUND(N(내역서!$G49)*$O49/$G49,0)),IF(N($J49)=0,0,ROUND(N(내역서!$O49)*$O49/$J49,0)))))</f>
+        <v/>
+      </c>
+      <c r="S49" s="20">
+        <f>IF($B49="","",IF(N($O49)=0,0,IF(OR($L49="감소",AND($L49="증가",$M49&lt;&gt;"Y")),IF(N($G49)=0,0,ROUND(N(내역서!$H49)*$O49/$G49,0)),IF(N($J49)=0,0,ROUND(N(내역서!$P49)*$O49/$J49,0)))))</f>
+        <v/>
+      </c>
+      <c r="T49" s="20">
+        <f>IF($B49="","",N($O49)-N($R49)-N($S49))</f>
+        <v/>
+      </c>
+      <c r="U49" s="20">
+        <f>IF($B49="","",ROUND(N($K49)*N($R49),0))</f>
+        <v/>
+      </c>
+      <c r="V49" s="20">
+        <f>IF($B49="","",ROUND(N($K49)*N($S49),0))</f>
+        <v/>
+      </c>
+      <c r="W49" s="20">
+        <f>IF($B49="","",N($P49)-N($U49)-N($V49))</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="18">
@@ -5639,6 +6779,30 @@
         <f>IF($B50="","",IF($L50="감소","감소분 → 계약단가",IF(AND($M50="Y",OR($L50="증가",$L50="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L50="증가",IF(AND($N50&lt;&gt;"",$G50&gt;$N50),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L50="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R50" s="20">
+        <f>IF($B50="","",IF(N($O50)=0,0,IF(OR($L50="감소",AND($L50="증가",$M50&lt;&gt;"Y")),IF(N($G50)=0,0,ROUND(N(내역서!$G50)*$O50/$G50,0)),IF(N($J50)=0,0,ROUND(N(내역서!$O50)*$O50/$J50,0)))))</f>
+        <v/>
+      </c>
+      <c r="S50" s="20">
+        <f>IF($B50="","",IF(N($O50)=0,0,IF(OR($L50="감소",AND($L50="증가",$M50&lt;&gt;"Y")),IF(N($G50)=0,0,ROUND(N(내역서!$H50)*$O50/$G50,0)),IF(N($J50)=0,0,ROUND(N(내역서!$P50)*$O50/$J50,0)))))</f>
+        <v/>
+      </c>
+      <c r="T50" s="20">
+        <f>IF($B50="","",N($O50)-N($R50)-N($S50))</f>
+        <v/>
+      </c>
+      <c r="U50" s="20">
+        <f>IF($B50="","",ROUND(N($K50)*N($R50),0))</f>
+        <v/>
+      </c>
+      <c r="V50" s="20">
+        <f>IF($B50="","",ROUND(N($K50)*N($S50),0))</f>
+        <v/>
+      </c>
+      <c r="W50" s="20">
+        <f>IF($B50="","",N($P50)-N($U50)-N($V50))</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="18">
@@ -5703,6 +6867,30 @@
         <f>IF($B51="","",IF($L51="감소","감소분 → 계약단가",IF(AND($M51="Y",OR($L51="증가",$L51="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L51="증가",IF(AND($N51&lt;&gt;"",$G51&gt;$N51),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L51="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R51" s="20">
+        <f>IF($B51="","",IF(N($O51)=0,0,IF(OR($L51="감소",AND($L51="증가",$M51&lt;&gt;"Y")),IF(N($G51)=0,0,ROUND(N(내역서!$G51)*$O51/$G51,0)),IF(N($J51)=0,0,ROUND(N(내역서!$O51)*$O51/$J51,0)))))</f>
+        <v/>
+      </c>
+      <c r="S51" s="20">
+        <f>IF($B51="","",IF(N($O51)=0,0,IF(OR($L51="감소",AND($L51="증가",$M51&lt;&gt;"Y")),IF(N($G51)=0,0,ROUND(N(내역서!$H51)*$O51/$G51,0)),IF(N($J51)=0,0,ROUND(N(내역서!$P51)*$O51/$J51,0)))))</f>
+        <v/>
+      </c>
+      <c r="T51" s="20">
+        <f>IF($B51="","",N($O51)-N($R51)-N($S51))</f>
+        <v/>
+      </c>
+      <c r="U51" s="20">
+        <f>IF($B51="","",ROUND(N($K51)*N($R51),0))</f>
+        <v/>
+      </c>
+      <c r="V51" s="20">
+        <f>IF($B51="","",ROUND(N($K51)*N($S51),0))</f>
+        <v/>
+      </c>
+      <c r="W51" s="20">
+        <f>IF($B51="","",N($P51)-N($U51)-N($V51))</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="18">
@@ -5767,6 +6955,30 @@
         <f>IF($B52="","",IF($L52="감소","감소분 → 계약단가",IF(AND($M52="Y",OR($L52="증가",$L52="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L52="증가",IF(AND($N52&lt;&gt;"",$G52&gt;$N52),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L52="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R52" s="20">
+        <f>IF($B52="","",IF(N($O52)=0,0,IF(OR($L52="감소",AND($L52="증가",$M52&lt;&gt;"Y")),IF(N($G52)=0,0,ROUND(N(내역서!$G52)*$O52/$G52,0)),IF(N($J52)=0,0,ROUND(N(내역서!$O52)*$O52/$J52,0)))))</f>
+        <v/>
+      </c>
+      <c r="S52" s="20">
+        <f>IF($B52="","",IF(N($O52)=0,0,IF(OR($L52="감소",AND($L52="증가",$M52&lt;&gt;"Y")),IF(N($G52)=0,0,ROUND(N(내역서!$H52)*$O52/$G52,0)),IF(N($J52)=0,0,ROUND(N(내역서!$P52)*$O52/$J52,0)))))</f>
+        <v/>
+      </c>
+      <c r="T52" s="20">
+        <f>IF($B52="","",N($O52)-N($R52)-N($S52))</f>
+        <v/>
+      </c>
+      <c r="U52" s="20">
+        <f>IF($B52="","",ROUND(N($K52)*N($R52),0))</f>
+        <v/>
+      </c>
+      <c r="V52" s="20">
+        <f>IF($B52="","",ROUND(N($K52)*N($S52),0))</f>
+        <v/>
+      </c>
+      <c r="W52" s="20">
+        <f>IF($B52="","",N($P52)-N($U52)-N($V52))</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="18">
@@ -5831,6 +7043,30 @@
         <f>IF($B53="","",IF($L53="감소","감소분 → 계약단가",IF(AND($M53="Y",OR($L53="증가",$L53="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L53="증가",IF(AND($N53&lt;&gt;"",$G53&gt;$N53),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L53="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R53" s="20">
+        <f>IF($B53="","",IF(N($O53)=0,0,IF(OR($L53="감소",AND($L53="증가",$M53&lt;&gt;"Y")),IF(N($G53)=0,0,ROUND(N(내역서!$G53)*$O53/$G53,0)),IF(N($J53)=0,0,ROUND(N(내역서!$O53)*$O53/$J53,0)))))</f>
+        <v/>
+      </c>
+      <c r="S53" s="20">
+        <f>IF($B53="","",IF(N($O53)=0,0,IF(OR($L53="감소",AND($L53="증가",$M53&lt;&gt;"Y")),IF(N($G53)=0,0,ROUND(N(내역서!$H53)*$O53/$G53,0)),IF(N($J53)=0,0,ROUND(N(내역서!$P53)*$O53/$J53,0)))))</f>
+        <v/>
+      </c>
+      <c r="T53" s="20">
+        <f>IF($B53="","",N($O53)-N($R53)-N($S53))</f>
+        <v/>
+      </c>
+      <c r="U53" s="20">
+        <f>IF($B53="","",ROUND(N($K53)*N($R53),0))</f>
+        <v/>
+      </c>
+      <c r="V53" s="20">
+        <f>IF($B53="","",ROUND(N($K53)*N($S53),0))</f>
+        <v/>
+      </c>
+      <c r="W53" s="20">
+        <f>IF($B53="","",N($P53)-N($U53)-N($V53))</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="18">
@@ -5895,6 +7131,30 @@
         <f>IF($B54="","",IF($L54="감소","감소분 → 계약단가",IF(AND($M54="Y",OR($L54="증가",$L54="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L54="증가",IF(AND($N54&lt;&gt;"",$G54&gt;$N54),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L54="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R54" s="20">
+        <f>IF($B54="","",IF(N($O54)=0,0,IF(OR($L54="감소",AND($L54="증가",$M54&lt;&gt;"Y")),IF(N($G54)=0,0,ROUND(N(내역서!$G54)*$O54/$G54,0)),IF(N($J54)=0,0,ROUND(N(내역서!$O54)*$O54/$J54,0)))))</f>
+        <v/>
+      </c>
+      <c r="S54" s="20">
+        <f>IF($B54="","",IF(N($O54)=0,0,IF(OR($L54="감소",AND($L54="증가",$M54&lt;&gt;"Y")),IF(N($G54)=0,0,ROUND(N(내역서!$H54)*$O54/$G54,0)),IF(N($J54)=0,0,ROUND(N(내역서!$P54)*$O54/$J54,0)))))</f>
+        <v/>
+      </c>
+      <c r="T54" s="20">
+        <f>IF($B54="","",N($O54)-N($R54)-N($S54))</f>
+        <v/>
+      </c>
+      <c r="U54" s="20">
+        <f>IF($B54="","",ROUND(N($K54)*N($R54),0))</f>
+        <v/>
+      </c>
+      <c r="V54" s="20">
+        <f>IF($B54="","",ROUND(N($K54)*N($S54),0))</f>
+        <v/>
+      </c>
+      <c r="W54" s="20">
+        <f>IF($B54="","",N($P54)-N($U54)-N($V54))</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="18">
@@ -5959,6 +7219,30 @@
         <f>IF($B55="","",IF($L55="감소","감소분 → 계약단가",IF(AND($M55="Y",OR($L55="증가",$L55="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L55="증가",IF(AND($N55&lt;&gt;"",$G55&gt;$N55),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L55="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R55" s="20">
+        <f>IF($B55="","",IF(N($O55)=0,0,IF(OR($L55="감소",AND($L55="증가",$M55&lt;&gt;"Y")),IF(N($G55)=0,0,ROUND(N(내역서!$G55)*$O55/$G55,0)),IF(N($J55)=0,0,ROUND(N(내역서!$O55)*$O55/$J55,0)))))</f>
+        <v/>
+      </c>
+      <c r="S55" s="20">
+        <f>IF($B55="","",IF(N($O55)=0,0,IF(OR($L55="감소",AND($L55="증가",$M55&lt;&gt;"Y")),IF(N($G55)=0,0,ROUND(N(내역서!$H55)*$O55/$G55,0)),IF(N($J55)=0,0,ROUND(N(내역서!$P55)*$O55/$J55,0)))))</f>
+        <v/>
+      </c>
+      <c r="T55" s="20">
+        <f>IF($B55="","",N($O55)-N($R55)-N($S55))</f>
+        <v/>
+      </c>
+      <c r="U55" s="20">
+        <f>IF($B55="","",ROUND(N($K55)*N($R55),0))</f>
+        <v/>
+      </c>
+      <c r="V55" s="20">
+        <f>IF($B55="","",ROUND(N($K55)*N($S55),0))</f>
+        <v/>
+      </c>
+      <c r="W55" s="20">
+        <f>IF($B55="","",N($P55)-N($U55)-N($V55))</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="18">
@@ -6023,6 +7307,30 @@
         <f>IF($B56="","",IF($L56="감소","감소분 → 계약단가",IF(AND($M56="Y",OR($L56="증가",$L56="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L56="증가",IF(AND($N56&lt;&gt;"",$G56&gt;$N56),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L56="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R56" s="20">
+        <f>IF($B56="","",IF(N($O56)=0,0,IF(OR($L56="감소",AND($L56="증가",$M56&lt;&gt;"Y")),IF(N($G56)=0,0,ROUND(N(내역서!$G56)*$O56/$G56,0)),IF(N($J56)=0,0,ROUND(N(내역서!$O56)*$O56/$J56,0)))))</f>
+        <v/>
+      </c>
+      <c r="S56" s="20">
+        <f>IF($B56="","",IF(N($O56)=0,0,IF(OR($L56="감소",AND($L56="증가",$M56&lt;&gt;"Y")),IF(N($G56)=0,0,ROUND(N(내역서!$H56)*$O56/$G56,0)),IF(N($J56)=0,0,ROUND(N(내역서!$P56)*$O56/$J56,0)))))</f>
+        <v/>
+      </c>
+      <c r="T56" s="20">
+        <f>IF($B56="","",N($O56)-N($R56)-N($S56))</f>
+        <v/>
+      </c>
+      <c r="U56" s="20">
+        <f>IF($B56="","",ROUND(N($K56)*N($R56),0))</f>
+        <v/>
+      </c>
+      <c r="V56" s="20">
+        <f>IF($B56="","",ROUND(N($K56)*N($S56),0))</f>
+        <v/>
+      </c>
+      <c r="W56" s="20">
+        <f>IF($B56="","",N($P56)-N($U56)-N($V56))</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="18">
@@ -6087,6 +7395,30 @@
         <f>IF($B57="","",IF($L57="감소","감소분 → 계약단가",IF(AND($M57="Y",OR($L57="증가",$L57="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L57="증가",IF(AND($N57&lt;&gt;"",$G57&gt;$N57),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L57="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R57" s="20">
+        <f>IF($B57="","",IF(N($O57)=0,0,IF(OR($L57="감소",AND($L57="증가",$M57&lt;&gt;"Y")),IF(N($G57)=0,0,ROUND(N(내역서!$G57)*$O57/$G57,0)),IF(N($J57)=0,0,ROUND(N(내역서!$O57)*$O57/$J57,0)))))</f>
+        <v/>
+      </c>
+      <c r="S57" s="20">
+        <f>IF($B57="","",IF(N($O57)=0,0,IF(OR($L57="감소",AND($L57="증가",$M57&lt;&gt;"Y")),IF(N($G57)=0,0,ROUND(N(내역서!$H57)*$O57/$G57,0)),IF(N($J57)=0,0,ROUND(N(내역서!$P57)*$O57/$J57,0)))))</f>
+        <v/>
+      </c>
+      <c r="T57" s="20">
+        <f>IF($B57="","",N($O57)-N($R57)-N($S57))</f>
+        <v/>
+      </c>
+      <c r="U57" s="20">
+        <f>IF($B57="","",ROUND(N($K57)*N($R57),0))</f>
+        <v/>
+      </c>
+      <c r="V57" s="20">
+        <f>IF($B57="","",ROUND(N($K57)*N($S57),0))</f>
+        <v/>
+      </c>
+      <c r="W57" s="20">
+        <f>IF($B57="","",N($P57)-N($U57)-N($V57))</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="18">
@@ -6151,6 +7483,30 @@
         <f>IF($B58="","",IF($L58="감소","감소분 → 계약단가",IF(AND($M58="Y",OR($L58="증가",$L58="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L58="증가",IF(AND($N58&lt;&gt;"",$G58&gt;$N58),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L58="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R58" s="20">
+        <f>IF($B58="","",IF(N($O58)=0,0,IF(OR($L58="감소",AND($L58="증가",$M58&lt;&gt;"Y")),IF(N($G58)=0,0,ROUND(N(내역서!$G58)*$O58/$G58,0)),IF(N($J58)=0,0,ROUND(N(내역서!$O58)*$O58/$J58,0)))))</f>
+        <v/>
+      </c>
+      <c r="S58" s="20">
+        <f>IF($B58="","",IF(N($O58)=0,0,IF(OR($L58="감소",AND($L58="증가",$M58&lt;&gt;"Y")),IF(N($G58)=0,0,ROUND(N(내역서!$H58)*$O58/$G58,0)),IF(N($J58)=0,0,ROUND(N(내역서!$P58)*$O58/$J58,0)))))</f>
+        <v/>
+      </c>
+      <c r="T58" s="20">
+        <f>IF($B58="","",N($O58)-N($R58)-N($S58))</f>
+        <v/>
+      </c>
+      <c r="U58" s="20">
+        <f>IF($B58="","",ROUND(N($K58)*N($R58),0))</f>
+        <v/>
+      </c>
+      <c r="V58" s="20">
+        <f>IF($B58="","",ROUND(N($K58)*N($S58),0))</f>
+        <v/>
+      </c>
+      <c r="W58" s="20">
+        <f>IF($B58="","",N($P58)-N($U58)-N($V58))</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="18">
@@ -6215,6 +7571,30 @@
         <f>IF($B59="","",IF($L59="감소","감소분 → 계약단가",IF(AND($M59="Y",OR($L59="증가",$L59="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L59="증가",IF(AND($N59&lt;&gt;"",$G59&gt;$N59),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L59="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R59" s="20">
+        <f>IF($B59="","",IF(N($O59)=0,0,IF(OR($L59="감소",AND($L59="증가",$M59&lt;&gt;"Y")),IF(N($G59)=0,0,ROUND(N(내역서!$G59)*$O59/$G59,0)),IF(N($J59)=0,0,ROUND(N(내역서!$O59)*$O59/$J59,0)))))</f>
+        <v/>
+      </c>
+      <c r="S59" s="20">
+        <f>IF($B59="","",IF(N($O59)=0,0,IF(OR($L59="감소",AND($L59="증가",$M59&lt;&gt;"Y")),IF(N($G59)=0,0,ROUND(N(내역서!$H59)*$O59/$G59,0)),IF(N($J59)=0,0,ROUND(N(내역서!$P59)*$O59/$J59,0)))))</f>
+        <v/>
+      </c>
+      <c r="T59" s="20">
+        <f>IF($B59="","",N($O59)-N($R59)-N($S59))</f>
+        <v/>
+      </c>
+      <c r="U59" s="20">
+        <f>IF($B59="","",ROUND(N($K59)*N($R59),0))</f>
+        <v/>
+      </c>
+      <c r="V59" s="20">
+        <f>IF($B59="","",ROUND(N($K59)*N($S59),0))</f>
+        <v/>
+      </c>
+      <c r="W59" s="20">
+        <f>IF($B59="","",N($P59)-N($U59)-N($V59))</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="18">
@@ -6279,6 +7659,30 @@
         <f>IF($B60="","",IF($L60="감소","감소분 → 계약단가",IF(AND($M60="Y",OR($L60="증가",$L60="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L60="증가",IF(AND($N60&lt;&gt;"",$G60&gt;$N60),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L60="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R60" s="20">
+        <f>IF($B60="","",IF(N($O60)=0,0,IF(OR($L60="감소",AND($L60="증가",$M60&lt;&gt;"Y")),IF(N($G60)=0,0,ROUND(N(내역서!$G60)*$O60/$G60,0)),IF(N($J60)=0,0,ROUND(N(내역서!$O60)*$O60/$J60,0)))))</f>
+        <v/>
+      </c>
+      <c r="S60" s="20">
+        <f>IF($B60="","",IF(N($O60)=0,0,IF(OR($L60="감소",AND($L60="증가",$M60&lt;&gt;"Y")),IF(N($G60)=0,0,ROUND(N(내역서!$H60)*$O60/$G60,0)),IF(N($J60)=0,0,ROUND(N(내역서!$P60)*$O60/$J60,0)))))</f>
+        <v/>
+      </c>
+      <c r="T60" s="20">
+        <f>IF($B60="","",N($O60)-N($R60)-N($S60))</f>
+        <v/>
+      </c>
+      <c r="U60" s="20">
+        <f>IF($B60="","",ROUND(N($K60)*N($R60),0))</f>
+        <v/>
+      </c>
+      <c r="V60" s="20">
+        <f>IF($B60="","",ROUND(N($K60)*N($S60),0))</f>
+        <v/>
+      </c>
+      <c r="W60" s="20">
+        <f>IF($B60="","",N($P60)-N($U60)-N($V60))</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="18">
@@ -6343,6 +7747,30 @@
         <f>IF($B61="","",IF($L61="감소","감소분 → 계약단가",IF(AND($M61="Y",OR($L61="증가",$L61="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L61="증가",IF(AND($N61&lt;&gt;"",$G61&gt;$N61),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L61="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R61" s="20">
+        <f>IF($B61="","",IF(N($O61)=0,0,IF(OR($L61="감소",AND($L61="증가",$M61&lt;&gt;"Y")),IF(N($G61)=0,0,ROUND(N(내역서!$G61)*$O61/$G61,0)),IF(N($J61)=0,0,ROUND(N(내역서!$O61)*$O61/$J61,0)))))</f>
+        <v/>
+      </c>
+      <c r="S61" s="20">
+        <f>IF($B61="","",IF(N($O61)=0,0,IF(OR($L61="감소",AND($L61="증가",$M61&lt;&gt;"Y")),IF(N($G61)=0,0,ROUND(N(내역서!$H61)*$O61/$G61,0)),IF(N($J61)=0,0,ROUND(N(내역서!$P61)*$O61/$J61,0)))))</f>
+        <v/>
+      </c>
+      <c r="T61" s="20">
+        <f>IF($B61="","",N($O61)-N($R61)-N($S61))</f>
+        <v/>
+      </c>
+      <c r="U61" s="20">
+        <f>IF($B61="","",ROUND(N($K61)*N($R61),0))</f>
+        <v/>
+      </c>
+      <c r="V61" s="20">
+        <f>IF($B61="","",ROUND(N($K61)*N($S61),0))</f>
+        <v/>
+      </c>
+      <c r="W61" s="20">
+        <f>IF($B61="","",N($P61)-N($U61)-N($V61))</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="18">
@@ -6407,6 +7835,30 @@
         <f>IF($B62="","",IF($L62="감소","감소분 → 계약단가",IF(AND($M62="Y",OR($L62="증가",$L62="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L62="증가",IF(AND($N62&lt;&gt;"",$G62&gt;$N62),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L62="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R62" s="20">
+        <f>IF($B62="","",IF(N($O62)=0,0,IF(OR($L62="감소",AND($L62="증가",$M62&lt;&gt;"Y")),IF(N($G62)=0,0,ROUND(N(내역서!$G62)*$O62/$G62,0)),IF(N($J62)=0,0,ROUND(N(내역서!$O62)*$O62/$J62,0)))))</f>
+        <v/>
+      </c>
+      <c r="S62" s="20">
+        <f>IF($B62="","",IF(N($O62)=0,0,IF(OR($L62="감소",AND($L62="증가",$M62&lt;&gt;"Y")),IF(N($G62)=0,0,ROUND(N(내역서!$H62)*$O62/$G62,0)),IF(N($J62)=0,0,ROUND(N(내역서!$P62)*$O62/$J62,0)))))</f>
+        <v/>
+      </c>
+      <c r="T62" s="20">
+        <f>IF($B62="","",N($O62)-N($R62)-N($S62))</f>
+        <v/>
+      </c>
+      <c r="U62" s="20">
+        <f>IF($B62="","",ROUND(N($K62)*N($R62),0))</f>
+        <v/>
+      </c>
+      <c r="V62" s="20">
+        <f>IF($B62="","",ROUND(N($K62)*N($S62),0))</f>
+        <v/>
+      </c>
+      <c r="W62" s="20">
+        <f>IF($B62="","",N($P62)-N($U62)-N($V62))</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="18">
@@ -6471,6 +7923,30 @@
         <f>IF($B63="","",IF($L63="감소","감소분 → 계약단가",IF(AND($M63="Y",OR($L63="증가",$L63="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L63="증가",IF(AND($N63&lt;&gt;"",$G63&gt;$N63),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L63="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R63" s="20">
+        <f>IF($B63="","",IF(N($O63)=0,0,IF(OR($L63="감소",AND($L63="증가",$M63&lt;&gt;"Y")),IF(N($G63)=0,0,ROUND(N(내역서!$G63)*$O63/$G63,0)),IF(N($J63)=0,0,ROUND(N(내역서!$O63)*$O63/$J63,0)))))</f>
+        <v/>
+      </c>
+      <c r="S63" s="20">
+        <f>IF($B63="","",IF(N($O63)=0,0,IF(OR($L63="감소",AND($L63="증가",$M63&lt;&gt;"Y")),IF(N($G63)=0,0,ROUND(N(내역서!$H63)*$O63/$G63,0)),IF(N($J63)=0,0,ROUND(N(내역서!$P63)*$O63/$J63,0)))))</f>
+        <v/>
+      </c>
+      <c r="T63" s="20">
+        <f>IF($B63="","",N($O63)-N($R63)-N($S63))</f>
+        <v/>
+      </c>
+      <c r="U63" s="20">
+        <f>IF($B63="","",ROUND(N($K63)*N($R63),0))</f>
+        <v/>
+      </c>
+      <c r="V63" s="20">
+        <f>IF($B63="","",ROUND(N($K63)*N($S63),0))</f>
+        <v/>
+      </c>
+      <c r="W63" s="20">
+        <f>IF($B63="","",N($P63)-N($U63)-N($V63))</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="18">
@@ -6535,6 +8011,30 @@
         <f>IF($B64="","",IF($L64="감소","감소분 → 계약단가",IF(AND($M64="Y",OR($L64="증가",$L64="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L64="증가",IF(AND($N64&lt;&gt;"",$G64&gt;$N64),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L64="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R64" s="20">
+        <f>IF($B64="","",IF(N($O64)=0,0,IF(OR($L64="감소",AND($L64="증가",$M64&lt;&gt;"Y")),IF(N($G64)=0,0,ROUND(N(내역서!$G64)*$O64/$G64,0)),IF(N($J64)=0,0,ROUND(N(내역서!$O64)*$O64/$J64,0)))))</f>
+        <v/>
+      </c>
+      <c r="S64" s="20">
+        <f>IF($B64="","",IF(N($O64)=0,0,IF(OR($L64="감소",AND($L64="증가",$M64&lt;&gt;"Y")),IF(N($G64)=0,0,ROUND(N(내역서!$H64)*$O64/$G64,0)),IF(N($J64)=0,0,ROUND(N(내역서!$P64)*$O64/$J64,0)))))</f>
+        <v/>
+      </c>
+      <c r="T64" s="20">
+        <f>IF($B64="","",N($O64)-N($R64)-N($S64))</f>
+        <v/>
+      </c>
+      <c r="U64" s="20">
+        <f>IF($B64="","",ROUND(N($K64)*N($R64),0))</f>
+        <v/>
+      </c>
+      <c r="V64" s="20">
+        <f>IF($B64="","",ROUND(N($K64)*N($S64),0))</f>
+        <v/>
+      </c>
+      <c r="W64" s="20">
+        <f>IF($B64="","",N($P64)-N($U64)-N($V64))</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="18">
@@ -6599,6 +8099,30 @@
         <f>IF($B65="","",IF($L65="감소","감소분 → 계약단가",IF(AND($M65="Y",OR($L65="증가",$L65="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L65="증가",IF(AND($N65&lt;&gt;"",$G65&gt;$N65),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L65="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R65" s="20">
+        <f>IF($B65="","",IF(N($O65)=0,0,IF(OR($L65="감소",AND($L65="증가",$M65&lt;&gt;"Y")),IF(N($G65)=0,0,ROUND(N(내역서!$G65)*$O65/$G65,0)),IF(N($J65)=0,0,ROUND(N(내역서!$O65)*$O65/$J65,0)))))</f>
+        <v/>
+      </c>
+      <c r="S65" s="20">
+        <f>IF($B65="","",IF(N($O65)=0,0,IF(OR($L65="감소",AND($L65="증가",$M65&lt;&gt;"Y")),IF(N($G65)=0,0,ROUND(N(내역서!$H65)*$O65/$G65,0)),IF(N($J65)=0,0,ROUND(N(내역서!$P65)*$O65/$J65,0)))))</f>
+        <v/>
+      </c>
+      <c r="T65" s="20">
+        <f>IF($B65="","",N($O65)-N($R65)-N($S65))</f>
+        <v/>
+      </c>
+      <c r="U65" s="20">
+        <f>IF($B65="","",ROUND(N($K65)*N($R65),0))</f>
+        <v/>
+      </c>
+      <c r="V65" s="20">
+        <f>IF($B65="","",ROUND(N($K65)*N($S65),0))</f>
+        <v/>
+      </c>
+      <c r="W65" s="20">
+        <f>IF($B65="","",N($P65)-N($U65)-N($V65))</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="18">
@@ -6663,6 +8187,30 @@
         <f>IF($B66="","",IF($L66="감소","감소분 → 계약단가",IF(AND($M66="Y",OR($L66="증가",$L66="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L66="증가",IF(AND($N66&lt;&gt;"",$G66&gt;$N66),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L66="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R66" s="20">
+        <f>IF($B66="","",IF(N($O66)=0,0,IF(OR($L66="감소",AND($L66="증가",$M66&lt;&gt;"Y")),IF(N($G66)=0,0,ROUND(N(내역서!$G66)*$O66/$G66,0)),IF(N($J66)=0,0,ROUND(N(내역서!$O66)*$O66/$J66,0)))))</f>
+        <v/>
+      </c>
+      <c r="S66" s="20">
+        <f>IF($B66="","",IF(N($O66)=0,0,IF(OR($L66="감소",AND($L66="증가",$M66&lt;&gt;"Y")),IF(N($G66)=0,0,ROUND(N(내역서!$H66)*$O66/$G66,0)),IF(N($J66)=0,0,ROUND(N(내역서!$P66)*$O66/$J66,0)))))</f>
+        <v/>
+      </c>
+      <c r="T66" s="20">
+        <f>IF($B66="","",N($O66)-N($R66)-N($S66))</f>
+        <v/>
+      </c>
+      <c r="U66" s="20">
+        <f>IF($B66="","",ROUND(N($K66)*N($R66),0))</f>
+        <v/>
+      </c>
+      <c r="V66" s="20">
+        <f>IF($B66="","",ROUND(N($K66)*N($S66),0))</f>
+        <v/>
+      </c>
+      <c r="W66" s="20">
+        <f>IF($B66="","",N($P66)-N($U66)-N($V66))</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="18">
@@ -6727,6 +8275,30 @@
         <f>IF($B67="","",IF($L67="감소","감소분 → 계약단가",IF(AND($M67="Y",OR($L67="증가",$L67="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L67="증가",IF(AND($N67&lt;&gt;"",$G67&gt;$N67),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L67="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R67" s="20">
+        <f>IF($B67="","",IF(N($O67)=0,0,IF(OR($L67="감소",AND($L67="증가",$M67&lt;&gt;"Y")),IF(N($G67)=0,0,ROUND(N(내역서!$G67)*$O67/$G67,0)),IF(N($J67)=0,0,ROUND(N(내역서!$O67)*$O67/$J67,0)))))</f>
+        <v/>
+      </c>
+      <c r="S67" s="20">
+        <f>IF($B67="","",IF(N($O67)=0,0,IF(OR($L67="감소",AND($L67="증가",$M67&lt;&gt;"Y")),IF(N($G67)=0,0,ROUND(N(내역서!$H67)*$O67/$G67,0)),IF(N($J67)=0,0,ROUND(N(내역서!$P67)*$O67/$J67,0)))))</f>
+        <v/>
+      </c>
+      <c r="T67" s="20">
+        <f>IF($B67="","",N($O67)-N($R67)-N($S67))</f>
+        <v/>
+      </c>
+      <c r="U67" s="20">
+        <f>IF($B67="","",ROUND(N($K67)*N($R67),0))</f>
+        <v/>
+      </c>
+      <c r="V67" s="20">
+        <f>IF($B67="","",ROUND(N($K67)*N($S67),0))</f>
+        <v/>
+      </c>
+      <c r="W67" s="20">
+        <f>IF($B67="","",N($P67)-N($U67)-N($V67))</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="18">
@@ -6791,6 +8363,30 @@
         <f>IF($B68="","",IF($L68="감소","감소분 → 계약단가",IF(AND($M68="Y",OR($L68="증가",$L68="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L68="증가",IF(AND($N68&lt;&gt;"",$G68&gt;$N68),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L68="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R68" s="20">
+        <f>IF($B68="","",IF(N($O68)=0,0,IF(OR($L68="감소",AND($L68="증가",$M68&lt;&gt;"Y")),IF(N($G68)=0,0,ROUND(N(내역서!$G68)*$O68/$G68,0)),IF(N($J68)=0,0,ROUND(N(내역서!$O68)*$O68/$J68,0)))))</f>
+        <v/>
+      </c>
+      <c r="S68" s="20">
+        <f>IF($B68="","",IF(N($O68)=0,0,IF(OR($L68="감소",AND($L68="증가",$M68&lt;&gt;"Y")),IF(N($G68)=0,0,ROUND(N(내역서!$H68)*$O68/$G68,0)),IF(N($J68)=0,0,ROUND(N(내역서!$P68)*$O68/$J68,0)))))</f>
+        <v/>
+      </c>
+      <c r="T68" s="20">
+        <f>IF($B68="","",N($O68)-N($R68)-N($S68))</f>
+        <v/>
+      </c>
+      <c r="U68" s="20">
+        <f>IF($B68="","",ROUND(N($K68)*N($R68),0))</f>
+        <v/>
+      </c>
+      <c r="V68" s="20">
+        <f>IF($B68="","",ROUND(N($K68)*N($S68),0))</f>
+        <v/>
+      </c>
+      <c r="W68" s="20">
+        <f>IF($B68="","",N($P68)-N($U68)-N($V68))</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="18">
@@ -6855,6 +8451,30 @@
         <f>IF($B69="","",IF($L69="감소","감소분 → 계약단가",IF(AND($M69="Y",OR($L69="증가",$L69="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L69="증가",IF(AND($N69&lt;&gt;"",$G69&gt;$N69),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L69="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R69" s="20">
+        <f>IF($B69="","",IF(N($O69)=0,0,IF(OR($L69="감소",AND($L69="증가",$M69&lt;&gt;"Y")),IF(N($G69)=0,0,ROUND(N(내역서!$G69)*$O69/$G69,0)),IF(N($J69)=0,0,ROUND(N(내역서!$O69)*$O69/$J69,0)))))</f>
+        <v/>
+      </c>
+      <c r="S69" s="20">
+        <f>IF($B69="","",IF(N($O69)=0,0,IF(OR($L69="감소",AND($L69="증가",$M69&lt;&gt;"Y")),IF(N($G69)=0,0,ROUND(N(내역서!$H69)*$O69/$G69,0)),IF(N($J69)=0,0,ROUND(N(내역서!$P69)*$O69/$J69,0)))))</f>
+        <v/>
+      </c>
+      <c r="T69" s="20">
+        <f>IF($B69="","",N($O69)-N($R69)-N($S69))</f>
+        <v/>
+      </c>
+      <c r="U69" s="20">
+        <f>IF($B69="","",ROUND(N($K69)*N($R69),0))</f>
+        <v/>
+      </c>
+      <c r="V69" s="20">
+        <f>IF($B69="","",ROUND(N($K69)*N($S69),0))</f>
+        <v/>
+      </c>
+      <c r="W69" s="20">
+        <f>IF($B69="","",N($P69)-N($U69)-N($V69))</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="18">
@@ -6919,6 +8539,30 @@
         <f>IF($B70="","",IF($L70="감소","감소분 → 계약단가",IF(AND($M70="Y",OR($L70="증가",$L70="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L70="증가",IF(AND($N70&lt;&gt;"",$G70&gt;$N70),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L70="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R70" s="20">
+        <f>IF($B70="","",IF(N($O70)=0,0,IF(OR($L70="감소",AND($L70="증가",$M70&lt;&gt;"Y")),IF(N($G70)=0,0,ROUND(N(내역서!$G70)*$O70/$G70,0)),IF(N($J70)=0,0,ROUND(N(내역서!$O70)*$O70/$J70,0)))))</f>
+        <v/>
+      </c>
+      <c r="S70" s="20">
+        <f>IF($B70="","",IF(N($O70)=0,0,IF(OR($L70="감소",AND($L70="증가",$M70&lt;&gt;"Y")),IF(N($G70)=0,0,ROUND(N(내역서!$H70)*$O70/$G70,0)),IF(N($J70)=0,0,ROUND(N(내역서!$P70)*$O70/$J70,0)))))</f>
+        <v/>
+      </c>
+      <c r="T70" s="20">
+        <f>IF($B70="","",N($O70)-N($R70)-N($S70))</f>
+        <v/>
+      </c>
+      <c r="U70" s="20">
+        <f>IF($B70="","",ROUND(N($K70)*N($R70),0))</f>
+        <v/>
+      </c>
+      <c r="V70" s="20">
+        <f>IF($B70="","",ROUND(N($K70)*N($S70),0))</f>
+        <v/>
+      </c>
+      <c r="W70" s="20">
+        <f>IF($B70="","",N($P70)-N($U70)-N($V70))</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="18">
@@ -6983,6 +8627,30 @@
         <f>IF($B71="","",IF($L71="감소","감소분 → 계약단가",IF(AND($M71="Y",OR($L71="증가",$L71="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L71="증가",IF(AND($N71&lt;&gt;"",$G71&gt;$N71),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L71="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R71" s="20">
+        <f>IF($B71="","",IF(N($O71)=0,0,IF(OR($L71="감소",AND($L71="증가",$M71&lt;&gt;"Y")),IF(N($G71)=0,0,ROUND(N(내역서!$G71)*$O71/$G71,0)),IF(N($J71)=0,0,ROUND(N(내역서!$O71)*$O71/$J71,0)))))</f>
+        <v/>
+      </c>
+      <c r="S71" s="20">
+        <f>IF($B71="","",IF(N($O71)=0,0,IF(OR($L71="감소",AND($L71="증가",$M71&lt;&gt;"Y")),IF(N($G71)=0,0,ROUND(N(내역서!$H71)*$O71/$G71,0)),IF(N($J71)=0,0,ROUND(N(내역서!$P71)*$O71/$J71,0)))))</f>
+        <v/>
+      </c>
+      <c r="T71" s="20">
+        <f>IF($B71="","",N($O71)-N($R71)-N($S71))</f>
+        <v/>
+      </c>
+      <c r="U71" s="20">
+        <f>IF($B71="","",ROUND(N($K71)*N($R71),0))</f>
+        <v/>
+      </c>
+      <c r="V71" s="20">
+        <f>IF($B71="","",ROUND(N($K71)*N($S71),0))</f>
+        <v/>
+      </c>
+      <c r="W71" s="20">
+        <f>IF($B71="","",N($P71)-N($U71)-N($V71))</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="18">
@@ -7047,6 +8715,30 @@
         <f>IF($B72="","",IF($L72="감소","감소분 → 계약단가",IF(AND($M72="Y",OR($L72="증가",$L72="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L72="증가",IF(AND($N72&lt;&gt;"",$G72&gt;$N72),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L72="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R72" s="20">
+        <f>IF($B72="","",IF(N($O72)=0,0,IF(OR($L72="감소",AND($L72="증가",$M72&lt;&gt;"Y")),IF(N($G72)=0,0,ROUND(N(내역서!$G72)*$O72/$G72,0)),IF(N($J72)=0,0,ROUND(N(내역서!$O72)*$O72/$J72,0)))))</f>
+        <v/>
+      </c>
+      <c r="S72" s="20">
+        <f>IF($B72="","",IF(N($O72)=0,0,IF(OR($L72="감소",AND($L72="증가",$M72&lt;&gt;"Y")),IF(N($G72)=0,0,ROUND(N(내역서!$H72)*$O72/$G72,0)),IF(N($J72)=0,0,ROUND(N(내역서!$P72)*$O72/$J72,0)))))</f>
+        <v/>
+      </c>
+      <c r="T72" s="20">
+        <f>IF($B72="","",N($O72)-N($R72)-N($S72))</f>
+        <v/>
+      </c>
+      <c r="U72" s="20">
+        <f>IF($B72="","",ROUND(N($K72)*N($R72),0))</f>
+        <v/>
+      </c>
+      <c r="V72" s="20">
+        <f>IF($B72="","",ROUND(N($K72)*N($S72),0))</f>
+        <v/>
+      </c>
+      <c r="W72" s="20">
+        <f>IF($B72="","",N($P72)-N($U72)-N($V72))</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="18">
@@ -7111,6 +8803,30 @@
         <f>IF($B73="","",IF($L73="감소","감소분 → 계약단가",IF(AND($M73="Y",OR($L73="증가",$L73="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L73="증가",IF(AND($N73&lt;&gt;"",$G73&gt;$N73),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L73="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R73" s="20">
+        <f>IF($B73="","",IF(N($O73)=0,0,IF(OR($L73="감소",AND($L73="증가",$M73&lt;&gt;"Y")),IF(N($G73)=0,0,ROUND(N(내역서!$G73)*$O73/$G73,0)),IF(N($J73)=0,0,ROUND(N(내역서!$O73)*$O73/$J73,0)))))</f>
+        <v/>
+      </c>
+      <c r="S73" s="20">
+        <f>IF($B73="","",IF(N($O73)=0,0,IF(OR($L73="감소",AND($L73="증가",$M73&lt;&gt;"Y")),IF(N($G73)=0,0,ROUND(N(내역서!$H73)*$O73/$G73,0)),IF(N($J73)=0,0,ROUND(N(내역서!$P73)*$O73/$J73,0)))))</f>
+        <v/>
+      </c>
+      <c r="T73" s="20">
+        <f>IF($B73="","",N($O73)-N($R73)-N($S73))</f>
+        <v/>
+      </c>
+      <c r="U73" s="20">
+        <f>IF($B73="","",ROUND(N($K73)*N($R73),0))</f>
+        <v/>
+      </c>
+      <c r="V73" s="20">
+        <f>IF($B73="","",ROUND(N($K73)*N($S73),0))</f>
+        <v/>
+      </c>
+      <c r="W73" s="20">
+        <f>IF($B73="","",N($P73)-N($U73)-N($V73))</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="18">
@@ -7175,6 +8891,30 @@
         <f>IF($B74="","",IF($L74="감소","감소분 → 계약단가",IF(AND($M74="Y",OR($L74="증가",$L74="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L74="증가",IF(AND($N74&lt;&gt;"",$G74&gt;$N74),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L74="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R74" s="20">
+        <f>IF($B74="","",IF(N($O74)=0,0,IF(OR($L74="감소",AND($L74="증가",$M74&lt;&gt;"Y")),IF(N($G74)=0,0,ROUND(N(내역서!$G74)*$O74/$G74,0)),IF(N($J74)=0,0,ROUND(N(내역서!$O74)*$O74/$J74,0)))))</f>
+        <v/>
+      </c>
+      <c r="S74" s="20">
+        <f>IF($B74="","",IF(N($O74)=0,0,IF(OR($L74="감소",AND($L74="증가",$M74&lt;&gt;"Y")),IF(N($G74)=0,0,ROUND(N(내역서!$H74)*$O74/$G74,0)),IF(N($J74)=0,0,ROUND(N(내역서!$P74)*$O74/$J74,0)))))</f>
+        <v/>
+      </c>
+      <c r="T74" s="20">
+        <f>IF($B74="","",N($O74)-N($R74)-N($S74))</f>
+        <v/>
+      </c>
+      <c r="U74" s="20">
+        <f>IF($B74="","",ROUND(N($K74)*N($R74),0))</f>
+        <v/>
+      </c>
+      <c r="V74" s="20">
+        <f>IF($B74="","",ROUND(N($K74)*N($S74),0))</f>
+        <v/>
+      </c>
+      <c r="W74" s="20">
+        <f>IF($B74="","",N($P74)-N($U74)-N($V74))</f>
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="18">
@@ -7239,6 +8979,30 @@
         <f>IF($B75="","",IF($L75="감소","감소분 → 계약단가",IF(AND($M75="Y",OR($L75="증가",$L75="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L75="증가",IF(AND($N75&lt;&gt;"",$G75&gt;$N75),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L75="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R75" s="20">
+        <f>IF($B75="","",IF(N($O75)=0,0,IF(OR($L75="감소",AND($L75="증가",$M75&lt;&gt;"Y")),IF(N($G75)=0,0,ROUND(N(내역서!$G75)*$O75/$G75,0)),IF(N($J75)=0,0,ROUND(N(내역서!$O75)*$O75/$J75,0)))))</f>
+        <v/>
+      </c>
+      <c r="S75" s="20">
+        <f>IF($B75="","",IF(N($O75)=0,0,IF(OR($L75="감소",AND($L75="증가",$M75&lt;&gt;"Y")),IF(N($G75)=0,0,ROUND(N(내역서!$H75)*$O75/$G75,0)),IF(N($J75)=0,0,ROUND(N(내역서!$P75)*$O75/$J75,0)))))</f>
+        <v/>
+      </c>
+      <c r="T75" s="20">
+        <f>IF($B75="","",N($O75)-N($R75)-N($S75))</f>
+        <v/>
+      </c>
+      <c r="U75" s="20">
+        <f>IF($B75="","",ROUND(N($K75)*N($R75),0))</f>
+        <v/>
+      </c>
+      <c r="V75" s="20">
+        <f>IF($B75="","",ROUND(N($K75)*N($S75),0))</f>
+        <v/>
+      </c>
+      <c r="W75" s="20">
+        <f>IF($B75="","",N($P75)-N($U75)-N($V75))</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="18">
@@ -7303,6 +9067,30 @@
         <f>IF($B76="","",IF($L76="감소","감소분 → 계약단가",IF(AND($M76="Y",OR($L76="증가",$L76="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L76="증가",IF(AND($N76&lt;&gt;"",$G76&gt;$N76),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L76="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R76" s="20">
+        <f>IF($B76="","",IF(N($O76)=0,0,IF(OR($L76="감소",AND($L76="증가",$M76&lt;&gt;"Y")),IF(N($G76)=0,0,ROUND(N(내역서!$G76)*$O76/$G76,0)),IF(N($J76)=0,0,ROUND(N(내역서!$O76)*$O76/$J76,0)))))</f>
+        <v/>
+      </c>
+      <c r="S76" s="20">
+        <f>IF($B76="","",IF(N($O76)=0,0,IF(OR($L76="감소",AND($L76="증가",$M76&lt;&gt;"Y")),IF(N($G76)=0,0,ROUND(N(내역서!$H76)*$O76/$G76,0)),IF(N($J76)=0,0,ROUND(N(내역서!$P76)*$O76/$J76,0)))))</f>
+        <v/>
+      </c>
+      <c r="T76" s="20">
+        <f>IF($B76="","",N($O76)-N($R76)-N($S76))</f>
+        <v/>
+      </c>
+      <c r="U76" s="20">
+        <f>IF($B76="","",ROUND(N($K76)*N($R76),0))</f>
+        <v/>
+      </c>
+      <c r="V76" s="20">
+        <f>IF($B76="","",ROUND(N($K76)*N($S76),0))</f>
+        <v/>
+      </c>
+      <c r="W76" s="20">
+        <f>IF($B76="","",N($P76)-N($U76)-N($V76))</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="18">
@@ -7367,6 +9155,30 @@
         <f>IF($B77="","",IF($L77="감소","감소분 → 계약단가",IF(AND($M77="Y",OR($L77="증가",$L77="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L77="증가",IF(AND($N77&lt;&gt;"",$G77&gt;$N77),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L77="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R77" s="20">
+        <f>IF($B77="","",IF(N($O77)=0,0,IF(OR($L77="감소",AND($L77="증가",$M77&lt;&gt;"Y")),IF(N($G77)=0,0,ROUND(N(내역서!$G77)*$O77/$G77,0)),IF(N($J77)=0,0,ROUND(N(내역서!$O77)*$O77/$J77,0)))))</f>
+        <v/>
+      </c>
+      <c r="S77" s="20">
+        <f>IF($B77="","",IF(N($O77)=0,0,IF(OR($L77="감소",AND($L77="증가",$M77&lt;&gt;"Y")),IF(N($G77)=0,0,ROUND(N(내역서!$H77)*$O77/$G77,0)),IF(N($J77)=0,0,ROUND(N(내역서!$P77)*$O77/$J77,0)))))</f>
+        <v/>
+      </c>
+      <c r="T77" s="20">
+        <f>IF($B77="","",N($O77)-N($R77)-N($S77))</f>
+        <v/>
+      </c>
+      <c r="U77" s="20">
+        <f>IF($B77="","",ROUND(N($K77)*N($R77),0))</f>
+        <v/>
+      </c>
+      <c r="V77" s="20">
+        <f>IF($B77="","",ROUND(N($K77)*N($S77),0))</f>
+        <v/>
+      </c>
+      <c r="W77" s="20">
+        <f>IF($B77="","",N($P77)-N($U77)-N($V77))</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="18">
@@ -7431,6 +9243,30 @@
         <f>IF($B78="","",IF($L78="감소","감소분 → 계약단가",IF(AND($M78="Y",OR($L78="증가",$L78="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L78="증가",IF(AND($N78&lt;&gt;"",$G78&gt;$N78),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L78="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R78" s="20">
+        <f>IF($B78="","",IF(N($O78)=0,0,IF(OR($L78="감소",AND($L78="증가",$M78&lt;&gt;"Y")),IF(N($G78)=0,0,ROUND(N(내역서!$G78)*$O78/$G78,0)),IF(N($J78)=0,0,ROUND(N(내역서!$O78)*$O78/$J78,0)))))</f>
+        <v/>
+      </c>
+      <c r="S78" s="20">
+        <f>IF($B78="","",IF(N($O78)=0,0,IF(OR($L78="감소",AND($L78="증가",$M78&lt;&gt;"Y")),IF(N($G78)=0,0,ROUND(N(내역서!$H78)*$O78/$G78,0)),IF(N($J78)=0,0,ROUND(N(내역서!$P78)*$O78/$J78,0)))))</f>
+        <v/>
+      </c>
+      <c r="T78" s="20">
+        <f>IF($B78="","",N($O78)-N($R78)-N($S78))</f>
+        <v/>
+      </c>
+      <c r="U78" s="20">
+        <f>IF($B78="","",ROUND(N($K78)*N($R78),0))</f>
+        <v/>
+      </c>
+      <c r="V78" s="20">
+        <f>IF($B78="","",ROUND(N($K78)*N($S78),0))</f>
+        <v/>
+      </c>
+      <c r="W78" s="20">
+        <f>IF($B78="","",N($P78)-N($U78)-N($V78))</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="18">
@@ -7495,6 +9331,30 @@
         <f>IF($B79="","",IF($L79="감소","감소분 → 계약단가",IF(AND($M79="Y",OR($L79="증가",$L79="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L79="증가",IF(AND($N79&lt;&gt;"",$G79&gt;$N79),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L79="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R79" s="20">
+        <f>IF($B79="","",IF(N($O79)=0,0,IF(OR($L79="감소",AND($L79="증가",$M79&lt;&gt;"Y")),IF(N($G79)=0,0,ROUND(N(내역서!$G79)*$O79/$G79,0)),IF(N($J79)=0,0,ROUND(N(내역서!$O79)*$O79/$J79,0)))))</f>
+        <v/>
+      </c>
+      <c r="S79" s="20">
+        <f>IF($B79="","",IF(N($O79)=0,0,IF(OR($L79="감소",AND($L79="증가",$M79&lt;&gt;"Y")),IF(N($G79)=0,0,ROUND(N(내역서!$H79)*$O79/$G79,0)),IF(N($J79)=0,0,ROUND(N(내역서!$P79)*$O79/$J79,0)))))</f>
+        <v/>
+      </c>
+      <c r="T79" s="20">
+        <f>IF($B79="","",N($O79)-N($R79)-N($S79))</f>
+        <v/>
+      </c>
+      <c r="U79" s="20">
+        <f>IF($B79="","",ROUND(N($K79)*N($R79),0))</f>
+        <v/>
+      </c>
+      <c r="V79" s="20">
+        <f>IF($B79="","",ROUND(N($K79)*N($S79),0))</f>
+        <v/>
+      </c>
+      <c r="W79" s="20">
+        <f>IF($B79="","",N($P79)-N($U79)-N($V79))</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="18">
@@ -7559,6 +9419,30 @@
         <f>IF($B80="","",IF($L80="감소","감소분 → 계약단가",IF(AND($M80="Y",OR($L80="증가",$L80="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L80="증가",IF(AND($N80&lt;&gt;"",$G80&gt;$N80),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L80="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R80" s="20">
+        <f>IF($B80="","",IF(N($O80)=0,0,IF(OR($L80="감소",AND($L80="증가",$M80&lt;&gt;"Y")),IF(N($G80)=0,0,ROUND(N(내역서!$G80)*$O80/$G80,0)),IF(N($J80)=0,0,ROUND(N(내역서!$O80)*$O80/$J80,0)))))</f>
+        <v/>
+      </c>
+      <c r="S80" s="20">
+        <f>IF($B80="","",IF(N($O80)=0,0,IF(OR($L80="감소",AND($L80="증가",$M80&lt;&gt;"Y")),IF(N($G80)=0,0,ROUND(N(내역서!$H80)*$O80/$G80,0)),IF(N($J80)=0,0,ROUND(N(내역서!$P80)*$O80/$J80,0)))))</f>
+        <v/>
+      </c>
+      <c r="T80" s="20">
+        <f>IF($B80="","",N($O80)-N($R80)-N($S80))</f>
+        <v/>
+      </c>
+      <c r="U80" s="20">
+        <f>IF($B80="","",ROUND(N($K80)*N($R80),0))</f>
+        <v/>
+      </c>
+      <c r="V80" s="20">
+        <f>IF($B80="","",ROUND(N($K80)*N($S80),0))</f>
+        <v/>
+      </c>
+      <c r="W80" s="20">
+        <f>IF($B80="","",N($P80)-N($U80)-N($V80))</f>
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="18">
@@ -7623,6 +9507,30 @@
         <f>IF($B81="","",IF($L81="감소","감소분 → 계약단가",IF(AND($M81="Y",OR($L81="증가",$L81="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L81="증가",IF(AND($N81&lt;&gt;"",$G81&gt;$N81),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L81="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R81" s="20">
+        <f>IF($B81="","",IF(N($O81)=0,0,IF(OR($L81="감소",AND($L81="증가",$M81&lt;&gt;"Y")),IF(N($G81)=0,0,ROUND(N(내역서!$G81)*$O81/$G81,0)),IF(N($J81)=0,0,ROUND(N(내역서!$O81)*$O81/$J81,0)))))</f>
+        <v/>
+      </c>
+      <c r="S81" s="20">
+        <f>IF($B81="","",IF(N($O81)=0,0,IF(OR($L81="감소",AND($L81="증가",$M81&lt;&gt;"Y")),IF(N($G81)=0,0,ROUND(N(내역서!$H81)*$O81/$G81,0)),IF(N($J81)=0,0,ROUND(N(내역서!$P81)*$O81/$J81,0)))))</f>
+        <v/>
+      </c>
+      <c r="T81" s="20">
+        <f>IF($B81="","",N($O81)-N($R81)-N($S81))</f>
+        <v/>
+      </c>
+      <c r="U81" s="20">
+        <f>IF($B81="","",ROUND(N($K81)*N($R81),0))</f>
+        <v/>
+      </c>
+      <c r="V81" s="20">
+        <f>IF($B81="","",ROUND(N($K81)*N($S81),0))</f>
+        <v/>
+      </c>
+      <c r="W81" s="20">
+        <f>IF($B81="","",N($P81)-N($U81)-N($V81))</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="18">
@@ -7687,6 +9595,30 @@
         <f>IF($B82="","",IF($L82="감소","감소분 → 계약단가",IF(AND($M82="Y",OR($L82="증가",$L82="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L82="증가",IF(AND($N82&lt;&gt;"",$G82&gt;$N82),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L82="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R82" s="20">
+        <f>IF($B82="","",IF(N($O82)=0,0,IF(OR($L82="감소",AND($L82="증가",$M82&lt;&gt;"Y")),IF(N($G82)=0,0,ROUND(N(내역서!$G82)*$O82/$G82,0)),IF(N($J82)=0,0,ROUND(N(내역서!$O82)*$O82/$J82,0)))))</f>
+        <v/>
+      </c>
+      <c r="S82" s="20">
+        <f>IF($B82="","",IF(N($O82)=0,0,IF(OR($L82="감소",AND($L82="증가",$M82&lt;&gt;"Y")),IF(N($G82)=0,0,ROUND(N(내역서!$H82)*$O82/$G82,0)),IF(N($J82)=0,0,ROUND(N(내역서!$P82)*$O82/$J82,0)))))</f>
+        <v/>
+      </c>
+      <c r="T82" s="20">
+        <f>IF($B82="","",N($O82)-N($R82)-N($S82))</f>
+        <v/>
+      </c>
+      <c r="U82" s="20">
+        <f>IF($B82="","",ROUND(N($K82)*N($R82),0))</f>
+        <v/>
+      </c>
+      <c r="V82" s="20">
+        <f>IF($B82="","",ROUND(N($K82)*N($S82),0))</f>
+        <v/>
+      </c>
+      <c r="W82" s="20">
+        <f>IF($B82="","",N($P82)-N($U82)-N($V82))</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="18">
@@ -7751,6 +9683,30 @@
         <f>IF($B83="","",IF($L83="감소","감소분 → 계약단가",IF(AND($M83="Y",OR($L83="증가",$L83="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L83="증가",IF(AND($N83&lt;&gt;"",$G83&gt;$N83),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L83="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R83" s="20">
+        <f>IF($B83="","",IF(N($O83)=0,0,IF(OR($L83="감소",AND($L83="증가",$M83&lt;&gt;"Y")),IF(N($G83)=0,0,ROUND(N(내역서!$G83)*$O83/$G83,0)),IF(N($J83)=0,0,ROUND(N(내역서!$O83)*$O83/$J83,0)))))</f>
+        <v/>
+      </c>
+      <c r="S83" s="20">
+        <f>IF($B83="","",IF(N($O83)=0,0,IF(OR($L83="감소",AND($L83="증가",$M83&lt;&gt;"Y")),IF(N($G83)=0,0,ROUND(N(내역서!$H83)*$O83/$G83,0)),IF(N($J83)=0,0,ROUND(N(내역서!$P83)*$O83/$J83,0)))))</f>
+        <v/>
+      </c>
+      <c r="T83" s="20">
+        <f>IF($B83="","",N($O83)-N($R83)-N($S83))</f>
+        <v/>
+      </c>
+      <c r="U83" s="20">
+        <f>IF($B83="","",ROUND(N($K83)*N($R83),0))</f>
+        <v/>
+      </c>
+      <c r="V83" s="20">
+        <f>IF($B83="","",ROUND(N($K83)*N($S83),0))</f>
+        <v/>
+      </c>
+      <c r="W83" s="20">
+        <f>IF($B83="","",N($P83)-N($U83)-N($V83))</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="18">
@@ -7815,6 +9771,30 @@
         <f>IF($B84="","",IF($L84="감소","감소분 → 계약단가",IF(AND($M84="Y",OR($L84="증가",$L84="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L84="증가",IF(AND($N84&lt;&gt;"",$G84&gt;$N84),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L84="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R84" s="20">
+        <f>IF($B84="","",IF(N($O84)=0,0,IF(OR($L84="감소",AND($L84="증가",$M84&lt;&gt;"Y")),IF(N($G84)=0,0,ROUND(N(내역서!$G84)*$O84/$G84,0)),IF(N($J84)=0,0,ROUND(N(내역서!$O84)*$O84/$J84,0)))))</f>
+        <v/>
+      </c>
+      <c r="S84" s="20">
+        <f>IF($B84="","",IF(N($O84)=0,0,IF(OR($L84="감소",AND($L84="증가",$M84&lt;&gt;"Y")),IF(N($G84)=0,0,ROUND(N(내역서!$H84)*$O84/$G84,0)),IF(N($J84)=0,0,ROUND(N(내역서!$P84)*$O84/$J84,0)))))</f>
+        <v/>
+      </c>
+      <c r="T84" s="20">
+        <f>IF($B84="","",N($O84)-N($R84)-N($S84))</f>
+        <v/>
+      </c>
+      <c r="U84" s="20">
+        <f>IF($B84="","",ROUND(N($K84)*N($R84),0))</f>
+        <v/>
+      </c>
+      <c r="V84" s="20">
+        <f>IF($B84="","",ROUND(N($K84)*N($S84),0))</f>
+        <v/>
+      </c>
+      <c r="W84" s="20">
+        <f>IF($B84="","",N($P84)-N($U84)-N($V84))</f>
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="18">
@@ -7879,6 +9859,30 @@
         <f>IF($B85="","",IF($L85="감소","감소분 → 계약단가",IF(AND($M85="Y",OR($L85="증가",$L85="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L85="증가",IF(AND($N85&lt;&gt;"",$G85&gt;$N85),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L85="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R85" s="20">
+        <f>IF($B85="","",IF(N($O85)=0,0,IF(OR($L85="감소",AND($L85="증가",$M85&lt;&gt;"Y")),IF(N($G85)=0,0,ROUND(N(내역서!$G85)*$O85/$G85,0)),IF(N($J85)=0,0,ROUND(N(내역서!$O85)*$O85/$J85,0)))))</f>
+        <v/>
+      </c>
+      <c r="S85" s="20">
+        <f>IF($B85="","",IF(N($O85)=0,0,IF(OR($L85="감소",AND($L85="증가",$M85&lt;&gt;"Y")),IF(N($G85)=0,0,ROUND(N(내역서!$H85)*$O85/$G85,0)),IF(N($J85)=0,0,ROUND(N(내역서!$P85)*$O85/$J85,0)))))</f>
+        <v/>
+      </c>
+      <c r="T85" s="20">
+        <f>IF($B85="","",N($O85)-N($R85)-N($S85))</f>
+        <v/>
+      </c>
+      <c r="U85" s="20">
+        <f>IF($B85="","",ROUND(N($K85)*N($R85),0))</f>
+        <v/>
+      </c>
+      <c r="V85" s="20">
+        <f>IF($B85="","",ROUND(N($K85)*N($S85),0))</f>
+        <v/>
+      </c>
+      <c r="W85" s="20">
+        <f>IF($B85="","",N($P85)-N($U85)-N($V85))</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="18">
@@ -7943,6 +9947,30 @@
         <f>IF($B86="","",IF($L86="감소","감소분 → 계약단가",IF(AND($M86="Y",OR($L86="증가",$L86="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L86="증가",IF(AND($N86&lt;&gt;"",$G86&gt;$N86),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L86="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R86" s="20">
+        <f>IF($B86="","",IF(N($O86)=0,0,IF(OR($L86="감소",AND($L86="증가",$M86&lt;&gt;"Y")),IF(N($G86)=0,0,ROUND(N(내역서!$G86)*$O86/$G86,0)),IF(N($J86)=0,0,ROUND(N(내역서!$O86)*$O86/$J86,0)))))</f>
+        <v/>
+      </c>
+      <c r="S86" s="20">
+        <f>IF($B86="","",IF(N($O86)=0,0,IF(OR($L86="감소",AND($L86="증가",$M86&lt;&gt;"Y")),IF(N($G86)=0,0,ROUND(N(내역서!$H86)*$O86/$G86,0)),IF(N($J86)=0,0,ROUND(N(내역서!$P86)*$O86/$J86,0)))))</f>
+        <v/>
+      </c>
+      <c r="T86" s="20">
+        <f>IF($B86="","",N($O86)-N($R86)-N($S86))</f>
+        <v/>
+      </c>
+      <c r="U86" s="20">
+        <f>IF($B86="","",ROUND(N($K86)*N($R86),0))</f>
+        <v/>
+      </c>
+      <c r="V86" s="20">
+        <f>IF($B86="","",ROUND(N($K86)*N($S86),0))</f>
+        <v/>
+      </c>
+      <c r="W86" s="20">
+        <f>IF($B86="","",N($P86)-N($U86)-N($V86))</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="18">
@@ -8007,6 +10035,30 @@
         <f>IF($B87="","",IF($L87="감소","감소분 → 계약단가",IF(AND($M87="Y",OR($L87="증가",$L87="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L87="증가",IF(AND($N87&lt;&gt;"",$G87&gt;$N87),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L87="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R87" s="20">
+        <f>IF($B87="","",IF(N($O87)=0,0,IF(OR($L87="감소",AND($L87="증가",$M87&lt;&gt;"Y")),IF(N($G87)=0,0,ROUND(N(내역서!$G87)*$O87/$G87,0)),IF(N($J87)=0,0,ROUND(N(내역서!$O87)*$O87/$J87,0)))))</f>
+        <v/>
+      </c>
+      <c r="S87" s="20">
+        <f>IF($B87="","",IF(N($O87)=0,0,IF(OR($L87="감소",AND($L87="증가",$M87&lt;&gt;"Y")),IF(N($G87)=0,0,ROUND(N(내역서!$H87)*$O87/$G87,0)),IF(N($J87)=0,0,ROUND(N(내역서!$P87)*$O87/$J87,0)))))</f>
+        <v/>
+      </c>
+      <c r="T87" s="20">
+        <f>IF($B87="","",N($O87)-N($R87)-N($S87))</f>
+        <v/>
+      </c>
+      <c r="U87" s="20">
+        <f>IF($B87="","",ROUND(N($K87)*N($R87),0))</f>
+        <v/>
+      </c>
+      <c r="V87" s="20">
+        <f>IF($B87="","",ROUND(N($K87)*N($S87),0))</f>
+        <v/>
+      </c>
+      <c r="W87" s="20">
+        <f>IF($B87="","",N($P87)-N($U87)-N($V87))</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="18">
@@ -8071,6 +10123,30 @@
         <f>IF($B88="","",IF($L88="감소","감소분 → 계약단가",IF(AND($M88="Y",OR($L88="증가",$L88="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L88="증가",IF(AND($N88&lt;&gt;"",$G88&gt;$N88),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L88="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R88" s="20">
+        <f>IF($B88="","",IF(N($O88)=0,0,IF(OR($L88="감소",AND($L88="증가",$M88&lt;&gt;"Y")),IF(N($G88)=0,0,ROUND(N(내역서!$G88)*$O88/$G88,0)),IF(N($J88)=0,0,ROUND(N(내역서!$O88)*$O88/$J88,0)))))</f>
+        <v/>
+      </c>
+      <c r="S88" s="20">
+        <f>IF($B88="","",IF(N($O88)=0,0,IF(OR($L88="감소",AND($L88="증가",$M88&lt;&gt;"Y")),IF(N($G88)=0,0,ROUND(N(내역서!$H88)*$O88/$G88,0)),IF(N($J88)=0,0,ROUND(N(내역서!$P88)*$O88/$J88,0)))))</f>
+        <v/>
+      </c>
+      <c r="T88" s="20">
+        <f>IF($B88="","",N($O88)-N($R88)-N($S88))</f>
+        <v/>
+      </c>
+      <c r="U88" s="20">
+        <f>IF($B88="","",ROUND(N($K88)*N($R88),0))</f>
+        <v/>
+      </c>
+      <c r="V88" s="20">
+        <f>IF($B88="","",ROUND(N($K88)*N($S88),0))</f>
+        <v/>
+      </c>
+      <c r="W88" s="20">
+        <f>IF($B88="","",N($P88)-N($U88)-N($V88))</f>
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="18">
@@ -8135,6 +10211,30 @@
         <f>IF($B89="","",IF($L89="감소","감소분 → 계약단가",IF(AND($M89="Y",OR($L89="증가",$L89="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L89="증가",IF(AND($N89&lt;&gt;"",$G89&gt;$N89),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L89="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R89" s="20">
+        <f>IF($B89="","",IF(N($O89)=0,0,IF(OR($L89="감소",AND($L89="증가",$M89&lt;&gt;"Y")),IF(N($G89)=0,0,ROUND(N(내역서!$G89)*$O89/$G89,0)),IF(N($J89)=0,0,ROUND(N(내역서!$O89)*$O89/$J89,0)))))</f>
+        <v/>
+      </c>
+      <c r="S89" s="20">
+        <f>IF($B89="","",IF(N($O89)=0,0,IF(OR($L89="감소",AND($L89="증가",$M89&lt;&gt;"Y")),IF(N($G89)=0,0,ROUND(N(내역서!$H89)*$O89/$G89,0)),IF(N($J89)=0,0,ROUND(N(내역서!$P89)*$O89/$J89,0)))))</f>
+        <v/>
+      </c>
+      <c r="T89" s="20">
+        <f>IF($B89="","",N($O89)-N($R89)-N($S89))</f>
+        <v/>
+      </c>
+      <c r="U89" s="20">
+        <f>IF($B89="","",ROUND(N($K89)*N($R89),0))</f>
+        <v/>
+      </c>
+      <c r="V89" s="20">
+        <f>IF($B89="","",ROUND(N($K89)*N($S89),0))</f>
+        <v/>
+      </c>
+      <c r="W89" s="20">
+        <f>IF($B89="","",N($P89)-N($U89)-N($V89))</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="18">
@@ -8199,6 +10299,30 @@
         <f>IF($B90="","",IF($L90="감소","감소분 → 계약단가",IF(AND($M90="Y",OR($L90="증가",$L90="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L90="증가",IF(AND($N90&lt;&gt;"",$G90&gt;$N90),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L90="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R90" s="20">
+        <f>IF($B90="","",IF(N($O90)=0,0,IF(OR($L90="감소",AND($L90="증가",$M90&lt;&gt;"Y")),IF(N($G90)=0,0,ROUND(N(내역서!$G90)*$O90/$G90,0)),IF(N($J90)=0,0,ROUND(N(내역서!$O90)*$O90/$J90,0)))))</f>
+        <v/>
+      </c>
+      <c r="S90" s="20">
+        <f>IF($B90="","",IF(N($O90)=0,0,IF(OR($L90="감소",AND($L90="증가",$M90&lt;&gt;"Y")),IF(N($G90)=0,0,ROUND(N(내역서!$H90)*$O90/$G90,0)),IF(N($J90)=0,0,ROUND(N(내역서!$P90)*$O90/$J90,0)))))</f>
+        <v/>
+      </c>
+      <c r="T90" s="20">
+        <f>IF($B90="","",N($O90)-N($R90)-N($S90))</f>
+        <v/>
+      </c>
+      <c r="U90" s="20">
+        <f>IF($B90="","",ROUND(N($K90)*N($R90),0))</f>
+        <v/>
+      </c>
+      <c r="V90" s="20">
+        <f>IF($B90="","",ROUND(N($K90)*N($S90),0))</f>
+        <v/>
+      </c>
+      <c r="W90" s="20">
+        <f>IF($B90="","",N($P90)-N($U90)-N($V90))</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="18">
@@ -8263,6 +10387,30 @@
         <f>IF($B91="","",IF($L91="감소","감소분 → 계약단가",IF(AND($M91="Y",OR($L91="증가",$L91="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L91="증가",IF(AND($N91&lt;&gt;"",$G91&gt;$N91),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L91="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R91" s="20">
+        <f>IF($B91="","",IF(N($O91)=0,0,IF(OR($L91="감소",AND($L91="증가",$M91&lt;&gt;"Y")),IF(N($G91)=0,0,ROUND(N(내역서!$G91)*$O91/$G91,0)),IF(N($J91)=0,0,ROUND(N(내역서!$O91)*$O91/$J91,0)))))</f>
+        <v/>
+      </c>
+      <c r="S91" s="20">
+        <f>IF($B91="","",IF(N($O91)=0,0,IF(OR($L91="감소",AND($L91="증가",$M91&lt;&gt;"Y")),IF(N($G91)=0,0,ROUND(N(내역서!$H91)*$O91/$G91,0)),IF(N($J91)=0,0,ROUND(N(내역서!$P91)*$O91/$J91,0)))))</f>
+        <v/>
+      </c>
+      <c r="T91" s="20">
+        <f>IF($B91="","",N($O91)-N($R91)-N($S91))</f>
+        <v/>
+      </c>
+      <c r="U91" s="20">
+        <f>IF($B91="","",ROUND(N($K91)*N($R91),0))</f>
+        <v/>
+      </c>
+      <c r="V91" s="20">
+        <f>IF($B91="","",ROUND(N($K91)*N($S91),0))</f>
+        <v/>
+      </c>
+      <c r="W91" s="20">
+        <f>IF($B91="","",N($P91)-N($U91)-N($V91))</f>
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="18">
@@ -8327,6 +10475,30 @@
         <f>IF($B92="","",IF($L92="감소","감소분 → 계약단가",IF(AND($M92="Y",OR($L92="증가",$L92="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L92="증가",IF(AND($N92&lt;&gt;"",$G92&gt;$N92),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L92="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R92" s="20">
+        <f>IF($B92="","",IF(N($O92)=0,0,IF(OR($L92="감소",AND($L92="증가",$M92&lt;&gt;"Y")),IF(N($G92)=0,0,ROUND(N(내역서!$G92)*$O92/$G92,0)),IF(N($J92)=0,0,ROUND(N(내역서!$O92)*$O92/$J92,0)))))</f>
+        <v/>
+      </c>
+      <c r="S92" s="20">
+        <f>IF($B92="","",IF(N($O92)=0,0,IF(OR($L92="감소",AND($L92="증가",$M92&lt;&gt;"Y")),IF(N($G92)=0,0,ROUND(N(내역서!$H92)*$O92/$G92,0)),IF(N($J92)=0,0,ROUND(N(내역서!$P92)*$O92/$J92,0)))))</f>
+        <v/>
+      </c>
+      <c r="T92" s="20">
+        <f>IF($B92="","",N($O92)-N($R92)-N($S92))</f>
+        <v/>
+      </c>
+      <c r="U92" s="20">
+        <f>IF($B92="","",ROUND(N($K92)*N($R92),0))</f>
+        <v/>
+      </c>
+      <c r="V92" s="20">
+        <f>IF($B92="","",ROUND(N($K92)*N($S92),0))</f>
+        <v/>
+      </c>
+      <c r="W92" s="20">
+        <f>IF($B92="","",N($P92)-N($U92)-N($V92))</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="18">
@@ -8391,6 +10563,30 @@
         <f>IF($B93="","",IF($L93="감소","감소분 → 계약단가",IF(AND($M93="Y",OR($L93="증가",$L93="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L93="증가",IF(AND($N93&lt;&gt;"",$G93&gt;$N93),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L93="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R93" s="20">
+        <f>IF($B93="","",IF(N($O93)=0,0,IF(OR($L93="감소",AND($L93="증가",$M93&lt;&gt;"Y")),IF(N($G93)=0,0,ROUND(N(내역서!$G93)*$O93/$G93,0)),IF(N($J93)=0,0,ROUND(N(내역서!$O93)*$O93/$J93,0)))))</f>
+        <v/>
+      </c>
+      <c r="S93" s="20">
+        <f>IF($B93="","",IF(N($O93)=0,0,IF(OR($L93="감소",AND($L93="증가",$M93&lt;&gt;"Y")),IF(N($G93)=0,0,ROUND(N(내역서!$H93)*$O93/$G93,0)),IF(N($J93)=0,0,ROUND(N(내역서!$P93)*$O93/$J93,0)))))</f>
+        <v/>
+      </c>
+      <c r="T93" s="20">
+        <f>IF($B93="","",N($O93)-N($R93)-N($S93))</f>
+        <v/>
+      </c>
+      <c r="U93" s="20">
+        <f>IF($B93="","",ROUND(N($K93)*N($R93),0))</f>
+        <v/>
+      </c>
+      <c r="V93" s="20">
+        <f>IF($B93="","",ROUND(N($K93)*N($S93),0))</f>
+        <v/>
+      </c>
+      <c r="W93" s="20">
+        <f>IF($B93="","",N($P93)-N($U93)-N($V93))</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="18">
@@ -8455,6 +10651,30 @@
         <f>IF($B94="","",IF($L94="감소","감소분 → 계약단가",IF(AND($M94="Y",OR($L94="증가",$L94="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L94="증가",IF(AND($N94&lt;&gt;"",$G94&gt;$N94),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L94="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R94" s="20">
+        <f>IF($B94="","",IF(N($O94)=0,0,IF(OR($L94="감소",AND($L94="증가",$M94&lt;&gt;"Y")),IF(N($G94)=0,0,ROUND(N(내역서!$G94)*$O94/$G94,0)),IF(N($J94)=0,0,ROUND(N(내역서!$O94)*$O94/$J94,0)))))</f>
+        <v/>
+      </c>
+      <c r="S94" s="20">
+        <f>IF($B94="","",IF(N($O94)=0,0,IF(OR($L94="감소",AND($L94="증가",$M94&lt;&gt;"Y")),IF(N($G94)=0,0,ROUND(N(내역서!$H94)*$O94/$G94,0)),IF(N($J94)=0,0,ROUND(N(내역서!$P94)*$O94/$J94,0)))))</f>
+        <v/>
+      </c>
+      <c r="T94" s="20">
+        <f>IF($B94="","",N($O94)-N($R94)-N($S94))</f>
+        <v/>
+      </c>
+      <c r="U94" s="20">
+        <f>IF($B94="","",ROUND(N($K94)*N($R94),0))</f>
+        <v/>
+      </c>
+      <c r="V94" s="20">
+        <f>IF($B94="","",ROUND(N($K94)*N($S94),0))</f>
+        <v/>
+      </c>
+      <c r="W94" s="20">
+        <f>IF($B94="","",N($P94)-N($U94)-N($V94))</f>
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="18">
@@ -8519,6 +10739,30 @@
         <f>IF($B95="","",IF($L95="감소","감소분 → 계약단가",IF(AND($M95="Y",OR($L95="증가",$L95="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L95="증가",IF(AND($N95&lt;&gt;"",$G95&gt;$N95),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L95="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R95" s="20">
+        <f>IF($B95="","",IF(N($O95)=0,0,IF(OR($L95="감소",AND($L95="증가",$M95&lt;&gt;"Y")),IF(N($G95)=0,0,ROUND(N(내역서!$G95)*$O95/$G95,0)),IF(N($J95)=0,0,ROUND(N(내역서!$O95)*$O95/$J95,0)))))</f>
+        <v/>
+      </c>
+      <c r="S95" s="20">
+        <f>IF($B95="","",IF(N($O95)=0,0,IF(OR($L95="감소",AND($L95="증가",$M95&lt;&gt;"Y")),IF(N($G95)=0,0,ROUND(N(내역서!$H95)*$O95/$G95,0)),IF(N($J95)=0,0,ROUND(N(내역서!$P95)*$O95/$J95,0)))))</f>
+        <v/>
+      </c>
+      <c r="T95" s="20">
+        <f>IF($B95="","",N($O95)-N($R95)-N($S95))</f>
+        <v/>
+      </c>
+      <c r="U95" s="20">
+        <f>IF($B95="","",ROUND(N($K95)*N($R95),0))</f>
+        <v/>
+      </c>
+      <c r="V95" s="20">
+        <f>IF($B95="","",ROUND(N($K95)*N($S95),0))</f>
+        <v/>
+      </c>
+      <c r="W95" s="20">
+        <f>IF($B95="","",N($P95)-N($U95)-N($V95))</f>
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="18">
@@ -8583,6 +10827,30 @@
         <f>IF($B96="","",IF($L96="감소","감소분 → 계약단가",IF(AND($M96="Y",OR($L96="증가",$L96="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L96="증가",IF(AND($N96&lt;&gt;"",$G96&gt;$N96),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L96="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R96" s="20">
+        <f>IF($B96="","",IF(N($O96)=0,0,IF(OR($L96="감소",AND($L96="증가",$M96&lt;&gt;"Y")),IF(N($G96)=0,0,ROUND(N(내역서!$G96)*$O96/$G96,0)),IF(N($J96)=0,0,ROUND(N(내역서!$O96)*$O96/$J96,0)))))</f>
+        <v/>
+      </c>
+      <c r="S96" s="20">
+        <f>IF($B96="","",IF(N($O96)=0,0,IF(OR($L96="감소",AND($L96="증가",$M96&lt;&gt;"Y")),IF(N($G96)=0,0,ROUND(N(내역서!$H96)*$O96/$G96,0)),IF(N($J96)=0,0,ROUND(N(내역서!$P96)*$O96/$J96,0)))))</f>
+        <v/>
+      </c>
+      <c r="T96" s="20">
+        <f>IF($B96="","",N($O96)-N($R96)-N($S96))</f>
+        <v/>
+      </c>
+      <c r="U96" s="20">
+        <f>IF($B96="","",ROUND(N($K96)*N($R96),0))</f>
+        <v/>
+      </c>
+      <c r="V96" s="20">
+        <f>IF($B96="","",ROUND(N($K96)*N($S96),0))</f>
+        <v/>
+      </c>
+      <c r="W96" s="20">
+        <f>IF($B96="","",N($P96)-N($U96)-N($V96))</f>
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="18">
@@ -8647,6 +10915,30 @@
         <f>IF($B97="","",IF($L97="감소","감소분 → 계약단가",IF(AND($M97="Y",OR($L97="증가",$L97="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L97="증가",IF(AND($N97&lt;&gt;"",$G97&gt;$N97),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L97="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R97" s="20">
+        <f>IF($B97="","",IF(N($O97)=0,0,IF(OR($L97="감소",AND($L97="증가",$M97&lt;&gt;"Y")),IF(N($G97)=0,0,ROUND(N(내역서!$G97)*$O97/$G97,0)),IF(N($J97)=0,0,ROUND(N(내역서!$O97)*$O97/$J97,0)))))</f>
+        <v/>
+      </c>
+      <c r="S97" s="20">
+        <f>IF($B97="","",IF(N($O97)=0,0,IF(OR($L97="감소",AND($L97="증가",$M97&lt;&gt;"Y")),IF(N($G97)=0,0,ROUND(N(내역서!$H97)*$O97/$G97,0)),IF(N($J97)=0,0,ROUND(N(내역서!$P97)*$O97/$J97,0)))))</f>
+        <v/>
+      </c>
+      <c r="T97" s="20">
+        <f>IF($B97="","",N($O97)-N($R97)-N($S97))</f>
+        <v/>
+      </c>
+      <c r="U97" s="20">
+        <f>IF($B97="","",ROUND(N($K97)*N($R97),0))</f>
+        <v/>
+      </c>
+      <c r="V97" s="20">
+        <f>IF($B97="","",ROUND(N($K97)*N($S97),0))</f>
+        <v/>
+      </c>
+      <c r="W97" s="20">
+        <f>IF($B97="","",N($P97)-N($U97)-N($V97))</f>
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="18">
@@ -8711,6 +11003,30 @@
         <f>IF($B98="","",IF($L98="감소","감소분 → 계약단가",IF(AND($M98="Y",OR($L98="증가",$L98="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L98="증가",IF(AND($N98&lt;&gt;"",$G98&gt;$N98),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L98="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R98" s="20">
+        <f>IF($B98="","",IF(N($O98)=0,0,IF(OR($L98="감소",AND($L98="증가",$M98&lt;&gt;"Y")),IF(N($G98)=0,0,ROUND(N(내역서!$G98)*$O98/$G98,0)),IF(N($J98)=0,0,ROUND(N(내역서!$O98)*$O98/$J98,0)))))</f>
+        <v/>
+      </c>
+      <c r="S98" s="20">
+        <f>IF($B98="","",IF(N($O98)=0,0,IF(OR($L98="감소",AND($L98="증가",$M98&lt;&gt;"Y")),IF(N($G98)=0,0,ROUND(N(내역서!$H98)*$O98/$G98,0)),IF(N($J98)=0,0,ROUND(N(내역서!$P98)*$O98/$J98,0)))))</f>
+        <v/>
+      </c>
+      <c r="T98" s="20">
+        <f>IF($B98="","",N($O98)-N($R98)-N($S98))</f>
+        <v/>
+      </c>
+      <c r="U98" s="20">
+        <f>IF($B98="","",ROUND(N($K98)*N($R98),0))</f>
+        <v/>
+      </c>
+      <c r="V98" s="20">
+        <f>IF($B98="","",ROUND(N($K98)*N($S98),0))</f>
+        <v/>
+      </c>
+      <c r="W98" s="20">
+        <f>IF($B98="","",N($P98)-N($U98)-N($V98))</f>
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="18">
@@ -8775,6 +11091,30 @@
         <f>IF($B99="","",IF($L99="감소","감소분 → 계약단가",IF(AND($M99="Y",OR($L99="증가",$L99="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L99="증가",IF(AND($N99&lt;&gt;"",$G99&gt;$N99),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L99="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R99" s="20">
+        <f>IF($B99="","",IF(N($O99)=0,0,IF(OR($L99="감소",AND($L99="증가",$M99&lt;&gt;"Y")),IF(N($G99)=0,0,ROUND(N(내역서!$G99)*$O99/$G99,0)),IF(N($J99)=0,0,ROUND(N(내역서!$O99)*$O99/$J99,0)))))</f>
+        <v/>
+      </c>
+      <c r="S99" s="20">
+        <f>IF($B99="","",IF(N($O99)=0,0,IF(OR($L99="감소",AND($L99="증가",$M99&lt;&gt;"Y")),IF(N($G99)=0,0,ROUND(N(내역서!$H99)*$O99/$G99,0)),IF(N($J99)=0,0,ROUND(N(내역서!$P99)*$O99/$J99,0)))))</f>
+        <v/>
+      </c>
+      <c r="T99" s="20">
+        <f>IF($B99="","",N($O99)-N($R99)-N($S99))</f>
+        <v/>
+      </c>
+      <c r="U99" s="20">
+        <f>IF($B99="","",ROUND(N($K99)*N($R99),0))</f>
+        <v/>
+      </c>
+      <c r="V99" s="20">
+        <f>IF($B99="","",ROUND(N($K99)*N($S99),0))</f>
+        <v/>
+      </c>
+      <c r="W99" s="20">
+        <f>IF($B99="","",N($P99)-N($U99)-N($V99))</f>
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="18">
@@ -8839,6 +11179,30 @@
         <f>IF($B100="","",IF($L100="감소","감소분 → 계약단가",IF(AND($M100="Y",OR($L100="증가",$L100="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L100="증가",IF(AND($N100&lt;&gt;"",$G100&gt;$N100),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L100="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R100" s="20">
+        <f>IF($B100="","",IF(N($O100)=0,0,IF(OR($L100="감소",AND($L100="증가",$M100&lt;&gt;"Y")),IF(N($G100)=0,0,ROUND(N(내역서!$G100)*$O100/$G100,0)),IF(N($J100)=0,0,ROUND(N(내역서!$O100)*$O100/$J100,0)))))</f>
+        <v/>
+      </c>
+      <c r="S100" s="20">
+        <f>IF($B100="","",IF(N($O100)=0,0,IF(OR($L100="감소",AND($L100="증가",$M100&lt;&gt;"Y")),IF(N($G100)=0,0,ROUND(N(내역서!$H100)*$O100/$G100,0)),IF(N($J100)=0,0,ROUND(N(내역서!$P100)*$O100/$J100,0)))))</f>
+        <v/>
+      </c>
+      <c r="T100" s="20">
+        <f>IF($B100="","",N($O100)-N($R100)-N($S100))</f>
+        <v/>
+      </c>
+      <c r="U100" s="20">
+        <f>IF($B100="","",ROUND(N($K100)*N($R100),0))</f>
+        <v/>
+      </c>
+      <c r="V100" s="20">
+        <f>IF($B100="","",ROUND(N($K100)*N($S100),0))</f>
+        <v/>
+      </c>
+      <c r="W100" s="20">
+        <f>IF($B100="","",N($P100)-N($U100)-N($V100))</f>
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="18">
@@ -8903,6 +11267,30 @@
         <f>IF($B101="","",IF($L101="감소","감소분 → 계약단가",IF(AND($M101="Y",OR($L101="증가",$L101="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L101="증가",IF(AND($N101&lt;&gt;"",$G101&gt;$N101),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L101="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R101" s="20">
+        <f>IF($B101="","",IF(N($O101)=0,0,IF(OR($L101="감소",AND($L101="증가",$M101&lt;&gt;"Y")),IF(N($G101)=0,0,ROUND(N(내역서!$G101)*$O101/$G101,0)),IF(N($J101)=0,0,ROUND(N(내역서!$O101)*$O101/$J101,0)))))</f>
+        <v/>
+      </c>
+      <c r="S101" s="20">
+        <f>IF($B101="","",IF(N($O101)=0,0,IF(OR($L101="감소",AND($L101="증가",$M101&lt;&gt;"Y")),IF(N($G101)=0,0,ROUND(N(내역서!$H101)*$O101/$G101,0)),IF(N($J101)=0,0,ROUND(N(내역서!$P101)*$O101/$J101,0)))))</f>
+        <v/>
+      </c>
+      <c r="T101" s="20">
+        <f>IF($B101="","",N($O101)-N($R101)-N($S101))</f>
+        <v/>
+      </c>
+      <c r="U101" s="20">
+        <f>IF($B101="","",ROUND(N($K101)*N($R101),0))</f>
+        <v/>
+      </c>
+      <c r="V101" s="20">
+        <f>IF($B101="","",ROUND(N($K101)*N($S101),0))</f>
+        <v/>
+      </c>
+      <c r="W101" s="20">
+        <f>IF($B101="","",N($P101)-N($U101)-N($V101))</f>
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="18">
@@ -8967,6 +11355,30 @@
         <f>IF($B102="","",IF($L102="감소","감소분 → 계약단가",IF(AND($M102="Y",OR($L102="증가",$L102="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L102="증가",IF(AND($N102&lt;&gt;"",$G102&gt;$N102),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L102="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R102" s="20">
+        <f>IF($B102="","",IF(N($O102)=0,0,IF(OR($L102="감소",AND($L102="증가",$M102&lt;&gt;"Y")),IF(N($G102)=0,0,ROUND(N(내역서!$G102)*$O102/$G102,0)),IF(N($J102)=0,0,ROUND(N(내역서!$O102)*$O102/$J102,0)))))</f>
+        <v/>
+      </c>
+      <c r="S102" s="20">
+        <f>IF($B102="","",IF(N($O102)=0,0,IF(OR($L102="감소",AND($L102="증가",$M102&lt;&gt;"Y")),IF(N($G102)=0,0,ROUND(N(내역서!$H102)*$O102/$G102,0)),IF(N($J102)=0,0,ROUND(N(내역서!$P102)*$O102/$J102,0)))))</f>
+        <v/>
+      </c>
+      <c r="T102" s="20">
+        <f>IF($B102="","",N($O102)-N($R102)-N($S102))</f>
+        <v/>
+      </c>
+      <c r="U102" s="20">
+        <f>IF($B102="","",ROUND(N($K102)*N($R102),0))</f>
+        <v/>
+      </c>
+      <c r="V102" s="20">
+        <f>IF($B102="","",ROUND(N($K102)*N($S102),0))</f>
+        <v/>
+      </c>
+      <c r="W102" s="20">
+        <f>IF($B102="","",N($P102)-N($U102)-N($V102))</f>
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="18">
@@ -9031,6 +11443,30 @@
         <f>IF($B103="","",IF($L103="감소","감소분 → 계약단가",IF(AND($M103="Y",OR($L103="증가",$L103="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L103="증가",IF(AND($N103&lt;&gt;"",$G103&gt;$N103),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L103="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R103" s="20">
+        <f>IF($B103="","",IF(N($O103)=0,0,IF(OR($L103="감소",AND($L103="증가",$M103&lt;&gt;"Y")),IF(N($G103)=0,0,ROUND(N(내역서!$G103)*$O103/$G103,0)),IF(N($J103)=0,0,ROUND(N(내역서!$O103)*$O103/$J103,0)))))</f>
+        <v/>
+      </c>
+      <c r="S103" s="20">
+        <f>IF($B103="","",IF(N($O103)=0,0,IF(OR($L103="감소",AND($L103="증가",$M103&lt;&gt;"Y")),IF(N($G103)=0,0,ROUND(N(내역서!$H103)*$O103/$G103,0)),IF(N($J103)=0,0,ROUND(N(내역서!$P103)*$O103/$J103,0)))))</f>
+        <v/>
+      </c>
+      <c r="T103" s="20">
+        <f>IF($B103="","",N($O103)-N($R103)-N($S103))</f>
+        <v/>
+      </c>
+      <c r="U103" s="20">
+        <f>IF($B103="","",ROUND(N($K103)*N($R103),0))</f>
+        <v/>
+      </c>
+      <c r="V103" s="20">
+        <f>IF($B103="","",ROUND(N($K103)*N($S103),0))</f>
+        <v/>
+      </c>
+      <c r="W103" s="20">
+        <f>IF($B103="","",N($P103)-N($U103)-N($V103))</f>
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="18">
@@ -9095,6 +11531,30 @@
         <f>IF($B104="","",IF($L104="감소","감소분 → 계약단가",IF(AND($M104="Y",OR($L104="증가",$L104="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L104="증가",IF(AND($N104&lt;&gt;"",$G104&gt;$N104),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L104="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R104" s="20">
+        <f>IF($B104="","",IF(N($O104)=0,0,IF(OR($L104="감소",AND($L104="증가",$M104&lt;&gt;"Y")),IF(N($G104)=0,0,ROUND(N(내역서!$G104)*$O104/$G104,0)),IF(N($J104)=0,0,ROUND(N(내역서!$O104)*$O104/$J104,0)))))</f>
+        <v/>
+      </c>
+      <c r="S104" s="20">
+        <f>IF($B104="","",IF(N($O104)=0,0,IF(OR($L104="감소",AND($L104="증가",$M104&lt;&gt;"Y")),IF(N($G104)=0,0,ROUND(N(내역서!$H104)*$O104/$G104,0)),IF(N($J104)=0,0,ROUND(N(내역서!$P104)*$O104/$J104,0)))))</f>
+        <v/>
+      </c>
+      <c r="T104" s="20">
+        <f>IF($B104="","",N($O104)-N($R104)-N($S104))</f>
+        <v/>
+      </c>
+      <c r="U104" s="20">
+        <f>IF($B104="","",ROUND(N($K104)*N($R104),0))</f>
+        <v/>
+      </c>
+      <c r="V104" s="20">
+        <f>IF($B104="","",ROUND(N($K104)*N($S104),0))</f>
+        <v/>
+      </c>
+      <c r="W104" s="20">
+        <f>IF($B104="","",N($P104)-N($U104)-N($V104))</f>
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="18">
@@ -9159,6 +11619,30 @@
         <f>IF($B105="","",IF($L105="감소","감소분 → 계약단가",IF(AND($M105="Y",OR($L105="증가",$L105="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L105="증가",IF(AND($N105&lt;&gt;"",$G105&gt;$N105),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L105="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R105" s="20">
+        <f>IF($B105="","",IF(N($O105)=0,0,IF(OR($L105="감소",AND($L105="증가",$M105&lt;&gt;"Y")),IF(N($G105)=0,0,ROUND(N(내역서!$G105)*$O105/$G105,0)),IF(N($J105)=0,0,ROUND(N(내역서!$O105)*$O105/$J105,0)))))</f>
+        <v/>
+      </c>
+      <c r="S105" s="20">
+        <f>IF($B105="","",IF(N($O105)=0,0,IF(OR($L105="감소",AND($L105="증가",$M105&lt;&gt;"Y")),IF(N($G105)=0,0,ROUND(N(내역서!$H105)*$O105/$G105,0)),IF(N($J105)=0,0,ROUND(N(내역서!$P105)*$O105/$J105,0)))))</f>
+        <v/>
+      </c>
+      <c r="T105" s="20">
+        <f>IF($B105="","",N($O105)-N($R105)-N($S105))</f>
+        <v/>
+      </c>
+      <c r="U105" s="20">
+        <f>IF($B105="","",ROUND(N($K105)*N($R105),0))</f>
+        <v/>
+      </c>
+      <c r="V105" s="20">
+        <f>IF($B105="","",ROUND(N($K105)*N($S105),0))</f>
+        <v/>
+      </c>
+      <c r="W105" s="20">
+        <f>IF($B105="","",N($P105)-N($U105)-N($V105))</f>
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="18">
@@ -9223,6 +11707,30 @@
         <f>IF($B106="","",IF($L106="감소","감소분 → 계약단가",IF(AND($M106="Y",OR($L106="증가",$L106="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L106="증가",IF(AND($N106&lt;&gt;"",$G106&gt;$N106),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L106="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R106" s="20">
+        <f>IF($B106="","",IF(N($O106)=0,0,IF(OR($L106="감소",AND($L106="증가",$M106&lt;&gt;"Y")),IF(N($G106)=0,0,ROUND(N(내역서!$G106)*$O106/$G106,0)),IF(N($J106)=0,0,ROUND(N(내역서!$O106)*$O106/$J106,0)))))</f>
+        <v/>
+      </c>
+      <c r="S106" s="20">
+        <f>IF($B106="","",IF(N($O106)=0,0,IF(OR($L106="감소",AND($L106="증가",$M106&lt;&gt;"Y")),IF(N($G106)=0,0,ROUND(N(내역서!$H106)*$O106/$G106,0)),IF(N($J106)=0,0,ROUND(N(내역서!$P106)*$O106/$J106,0)))))</f>
+        <v/>
+      </c>
+      <c r="T106" s="20">
+        <f>IF($B106="","",N($O106)-N($R106)-N($S106))</f>
+        <v/>
+      </c>
+      <c r="U106" s="20">
+        <f>IF($B106="","",ROUND(N($K106)*N($R106),0))</f>
+        <v/>
+      </c>
+      <c r="V106" s="20">
+        <f>IF($B106="","",ROUND(N($K106)*N($S106),0))</f>
+        <v/>
+      </c>
+      <c r="W106" s="20">
+        <f>IF($B106="","",N($P106)-N($U106)-N($V106))</f>
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="18">
@@ -9287,6 +11795,30 @@
         <f>IF($B107="","",IF($L107="감소","감소분 → 계약단가",IF(AND($M107="Y",OR($L107="증가",$L107="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L107="증가",IF(AND($N107&lt;&gt;"",$G107&gt;$N107),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L107="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R107" s="20">
+        <f>IF($B107="","",IF(N($O107)=0,0,IF(OR($L107="감소",AND($L107="증가",$M107&lt;&gt;"Y")),IF(N($G107)=0,0,ROUND(N(내역서!$G107)*$O107/$G107,0)),IF(N($J107)=0,0,ROUND(N(내역서!$O107)*$O107/$J107,0)))))</f>
+        <v/>
+      </c>
+      <c r="S107" s="20">
+        <f>IF($B107="","",IF(N($O107)=0,0,IF(OR($L107="감소",AND($L107="증가",$M107&lt;&gt;"Y")),IF(N($G107)=0,0,ROUND(N(내역서!$H107)*$O107/$G107,0)),IF(N($J107)=0,0,ROUND(N(내역서!$P107)*$O107/$J107,0)))))</f>
+        <v/>
+      </c>
+      <c r="T107" s="20">
+        <f>IF($B107="","",N($O107)-N($R107)-N($S107))</f>
+        <v/>
+      </c>
+      <c r="U107" s="20">
+        <f>IF($B107="","",ROUND(N($K107)*N($R107),0))</f>
+        <v/>
+      </c>
+      <c r="V107" s="20">
+        <f>IF($B107="","",ROUND(N($K107)*N($S107),0))</f>
+        <v/>
+      </c>
+      <c r="W107" s="20">
+        <f>IF($B107="","",N($P107)-N($U107)-N($V107))</f>
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="18">
@@ -9351,6 +11883,30 @@
         <f>IF($B108="","",IF($L108="감소","감소분 → 계약단가",IF(AND($M108="Y",OR($L108="증가",$L108="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L108="증가",IF(AND($N108&lt;&gt;"",$G108&gt;$N108),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L108="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R108" s="20">
+        <f>IF($B108="","",IF(N($O108)=0,0,IF(OR($L108="감소",AND($L108="증가",$M108&lt;&gt;"Y")),IF(N($G108)=0,0,ROUND(N(내역서!$G108)*$O108/$G108,0)),IF(N($J108)=0,0,ROUND(N(내역서!$O108)*$O108/$J108,0)))))</f>
+        <v/>
+      </c>
+      <c r="S108" s="20">
+        <f>IF($B108="","",IF(N($O108)=0,0,IF(OR($L108="감소",AND($L108="증가",$M108&lt;&gt;"Y")),IF(N($G108)=0,0,ROUND(N(내역서!$H108)*$O108/$G108,0)),IF(N($J108)=0,0,ROUND(N(내역서!$P108)*$O108/$J108,0)))))</f>
+        <v/>
+      </c>
+      <c r="T108" s="20">
+        <f>IF($B108="","",N($O108)-N($R108)-N($S108))</f>
+        <v/>
+      </c>
+      <c r="U108" s="20">
+        <f>IF($B108="","",ROUND(N($K108)*N($R108),0))</f>
+        <v/>
+      </c>
+      <c r="V108" s="20">
+        <f>IF($B108="","",ROUND(N($K108)*N($S108),0))</f>
+        <v/>
+      </c>
+      <c r="W108" s="20">
+        <f>IF($B108="","",N($P108)-N($U108)-N($V108))</f>
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="18">
@@ -9415,6 +11971,30 @@
         <f>IF($B109="","",IF($L109="감소","감소분 → 계약단가",IF(AND($M109="Y",OR($L109="증가",$L109="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L109="증가",IF(AND($N109&lt;&gt;"",$G109&gt;$N109),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L109="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R109" s="20">
+        <f>IF($B109="","",IF(N($O109)=0,0,IF(OR($L109="감소",AND($L109="증가",$M109&lt;&gt;"Y")),IF(N($G109)=0,0,ROUND(N(내역서!$G109)*$O109/$G109,0)),IF(N($J109)=0,0,ROUND(N(내역서!$O109)*$O109/$J109,0)))))</f>
+        <v/>
+      </c>
+      <c r="S109" s="20">
+        <f>IF($B109="","",IF(N($O109)=0,0,IF(OR($L109="감소",AND($L109="증가",$M109&lt;&gt;"Y")),IF(N($G109)=0,0,ROUND(N(내역서!$H109)*$O109/$G109,0)),IF(N($J109)=0,0,ROUND(N(내역서!$P109)*$O109/$J109,0)))))</f>
+        <v/>
+      </c>
+      <c r="T109" s="20">
+        <f>IF($B109="","",N($O109)-N($R109)-N($S109))</f>
+        <v/>
+      </c>
+      <c r="U109" s="20">
+        <f>IF($B109="","",ROUND(N($K109)*N($R109),0))</f>
+        <v/>
+      </c>
+      <c r="V109" s="20">
+        <f>IF($B109="","",ROUND(N($K109)*N($S109),0))</f>
+        <v/>
+      </c>
+      <c r="W109" s="20">
+        <f>IF($B109="","",N($P109)-N($U109)-N($V109))</f>
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="18">
@@ -9479,6 +12059,30 @@
         <f>IF($B110="","",IF($L110="감소","감소분 → 계약단가",IF(AND($M110="Y",OR($L110="증가",$L110="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L110="증가",IF(AND($N110&lt;&gt;"",$G110&gt;$N110),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L110="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R110" s="20">
+        <f>IF($B110="","",IF(N($O110)=0,0,IF(OR($L110="감소",AND($L110="증가",$M110&lt;&gt;"Y")),IF(N($G110)=0,0,ROUND(N(내역서!$G110)*$O110/$G110,0)),IF(N($J110)=0,0,ROUND(N(내역서!$O110)*$O110/$J110,0)))))</f>
+        <v/>
+      </c>
+      <c r="S110" s="20">
+        <f>IF($B110="","",IF(N($O110)=0,0,IF(OR($L110="감소",AND($L110="증가",$M110&lt;&gt;"Y")),IF(N($G110)=0,0,ROUND(N(내역서!$H110)*$O110/$G110,0)),IF(N($J110)=0,0,ROUND(N(내역서!$P110)*$O110/$J110,0)))))</f>
+        <v/>
+      </c>
+      <c r="T110" s="20">
+        <f>IF($B110="","",N($O110)-N($R110)-N($S110))</f>
+        <v/>
+      </c>
+      <c r="U110" s="20">
+        <f>IF($B110="","",ROUND(N($K110)*N($R110),0))</f>
+        <v/>
+      </c>
+      <c r="V110" s="20">
+        <f>IF($B110="","",ROUND(N($K110)*N($S110),0))</f>
+        <v/>
+      </c>
+      <c r="W110" s="20">
+        <f>IF($B110="","",N($P110)-N($U110)-N($V110))</f>
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="18">
@@ -9543,6 +12147,30 @@
         <f>IF($B111="","",IF($L111="감소","감소분 → 계약단가",IF(AND($M111="Y",OR($L111="증가",$L111="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L111="증가",IF(AND($N111&lt;&gt;"",$G111&gt;$N111),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L111="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R111" s="20">
+        <f>IF($B111="","",IF(N($O111)=0,0,IF(OR($L111="감소",AND($L111="증가",$M111&lt;&gt;"Y")),IF(N($G111)=0,0,ROUND(N(내역서!$G111)*$O111/$G111,0)),IF(N($J111)=0,0,ROUND(N(내역서!$O111)*$O111/$J111,0)))))</f>
+        <v/>
+      </c>
+      <c r="S111" s="20">
+        <f>IF($B111="","",IF(N($O111)=0,0,IF(OR($L111="감소",AND($L111="증가",$M111&lt;&gt;"Y")),IF(N($G111)=0,0,ROUND(N(내역서!$H111)*$O111/$G111,0)),IF(N($J111)=0,0,ROUND(N(내역서!$P111)*$O111/$J111,0)))))</f>
+        <v/>
+      </c>
+      <c r="T111" s="20">
+        <f>IF($B111="","",N($O111)-N($R111)-N($S111))</f>
+        <v/>
+      </c>
+      <c r="U111" s="20">
+        <f>IF($B111="","",ROUND(N($K111)*N($R111),0))</f>
+        <v/>
+      </c>
+      <c r="V111" s="20">
+        <f>IF($B111="","",ROUND(N($K111)*N($S111),0))</f>
+        <v/>
+      </c>
+      <c r="W111" s="20">
+        <f>IF($B111="","",N($P111)-N($U111)-N($V111))</f>
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="18">
@@ -9607,6 +12235,30 @@
         <f>IF($B112="","",IF($L112="감소","감소분 → 계약단가",IF(AND($M112="Y",OR($L112="증가",$L112="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L112="증가",IF(AND($N112&lt;&gt;"",$G112&gt;$N112),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L112="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R112" s="20">
+        <f>IF($B112="","",IF(N($O112)=0,0,IF(OR($L112="감소",AND($L112="증가",$M112&lt;&gt;"Y")),IF(N($G112)=0,0,ROUND(N(내역서!$G112)*$O112/$G112,0)),IF(N($J112)=0,0,ROUND(N(내역서!$O112)*$O112/$J112,0)))))</f>
+        <v/>
+      </c>
+      <c r="S112" s="20">
+        <f>IF($B112="","",IF(N($O112)=0,0,IF(OR($L112="감소",AND($L112="증가",$M112&lt;&gt;"Y")),IF(N($G112)=0,0,ROUND(N(내역서!$H112)*$O112/$G112,0)),IF(N($J112)=0,0,ROUND(N(내역서!$P112)*$O112/$J112,0)))))</f>
+        <v/>
+      </c>
+      <c r="T112" s="20">
+        <f>IF($B112="","",N($O112)-N($R112)-N($S112))</f>
+        <v/>
+      </c>
+      <c r="U112" s="20">
+        <f>IF($B112="","",ROUND(N($K112)*N($R112),0))</f>
+        <v/>
+      </c>
+      <c r="V112" s="20">
+        <f>IF($B112="","",ROUND(N($K112)*N($S112),0))</f>
+        <v/>
+      </c>
+      <c r="W112" s="20">
+        <f>IF($B112="","",N($P112)-N($U112)-N($V112))</f>
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="18">
@@ -9671,6 +12323,30 @@
         <f>IF($B113="","",IF($L113="감소","감소분 → 계약단가",IF(AND($M113="Y",OR($L113="증가",$L113="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L113="증가",IF(AND($N113&lt;&gt;"",$G113&gt;$N113),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L113="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R113" s="20">
+        <f>IF($B113="","",IF(N($O113)=0,0,IF(OR($L113="감소",AND($L113="증가",$M113&lt;&gt;"Y")),IF(N($G113)=0,0,ROUND(N(내역서!$G113)*$O113/$G113,0)),IF(N($J113)=0,0,ROUND(N(내역서!$O113)*$O113/$J113,0)))))</f>
+        <v/>
+      </c>
+      <c r="S113" s="20">
+        <f>IF($B113="","",IF(N($O113)=0,0,IF(OR($L113="감소",AND($L113="증가",$M113&lt;&gt;"Y")),IF(N($G113)=0,0,ROUND(N(내역서!$H113)*$O113/$G113,0)),IF(N($J113)=0,0,ROUND(N(내역서!$P113)*$O113/$J113,0)))))</f>
+        <v/>
+      </c>
+      <c r="T113" s="20">
+        <f>IF($B113="","",N($O113)-N($R113)-N($S113))</f>
+        <v/>
+      </c>
+      <c r="U113" s="20">
+        <f>IF($B113="","",ROUND(N($K113)*N($R113),0))</f>
+        <v/>
+      </c>
+      <c r="V113" s="20">
+        <f>IF($B113="","",ROUND(N($K113)*N($S113),0))</f>
+        <v/>
+      </c>
+      <c r="W113" s="20">
+        <f>IF($B113="","",N($P113)-N($U113)-N($V113))</f>
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="18">
@@ -9735,6 +12411,30 @@
         <f>IF($B114="","",IF($L114="감소","감소분 → 계약단가",IF(AND($M114="Y",OR($L114="증가",$L114="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L114="증가",IF(AND($N114&lt;&gt;"",$G114&gt;$N114),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L114="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R114" s="20">
+        <f>IF($B114="","",IF(N($O114)=0,0,IF(OR($L114="감소",AND($L114="증가",$M114&lt;&gt;"Y")),IF(N($G114)=0,0,ROUND(N(내역서!$G114)*$O114/$G114,0)),IF(N($J114)=0,0,ROUND(N(내역서!$O114)*$O114/$J114,0)))))</f>
+        <v/>
+      </c>
+      <c r="S114" s="20">
+        <f>IF($B114="","",IF(N($O114)=0,0,IF(OR($L114="감소",AND($L114="증가",$M114&lt;&gt;"Y")),IF(N($G114)=0,0,ROUND(N(내역서!$H114)*$O114/$G114,0)),IF(N($J114)=0,0,ROUND(N(내역서!$P114)*$O114/$J114,0)))))</f>
+        <v/>
+      </c>
+      <c r="T114" s="20">
+        <f>IF($B114="","",N($O114)-N($R114)-N($S114))</f>
+        <v/>
+      </c>
+      <c r="U114" s="20">
+        <f>IF($B114="","",ROUND(N($K114)*N($R114),0))</f>
+        <v/>
+      </c>
+      <c r="V114" s="20">
+        <f>IF($B114="","",ROUND(N($K114)*N($S114),0))</f>
+        <v/>
+      </c>
+      <c r="W114" s="20">
+        <f>IF($B114="","",N($P114)-N($U114)-N($V114))</f>
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="18">
@@ -9799,6 +12499,30 @@
         <f>IF($B115="","",IF($L115="감소","감소분 → 계약단가",IF(AND($M115="Y",OR($L115="증가",$L115="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L115="증가",IF(AND($N115&lt;&gt;"",$G115&gt;$N115),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L115="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R115" s="20">
+        <f>IF($B115="","",IF(N($O115)=0,0,IF(OR($L115="감소",AND($L115="증가",$M115&lt;&gt;"Y")),IF(N($G115)=0,0,ROUND(N(내역서!$G115)*$O115/$G115,0)),IF(N($J115)=0,0,ROUND(N(내역서!$O115)*$O115/$J115,0)))))</f>
+        <v/>
+      </c>
+      <c r="S115" s="20">
+        <f>IF($B115="","",IF(N($O115)=0,0,IF(OR($L115="감소",AND($L115="증가",$M115&lt;&gt;"Y")),IF(N($G115)=0,0,ROUND(N(내역서!$H115)*$O115/$G115,0)),IF(N($J115)=0,0,ROUND(N(내역서!$P115)*$O115/$J115,0)))))</f>
+        <v/>
+      </c>
+      <c r="T115" s="20">
+        <f>IF($B115="","",N($O115)-N($R115)-N($S115))</f>
+        <v/>
+      </c>
+      <c r="U115" s="20">
+        <f>IF($B115="","",ROUND(N($K115)*N($R115),0))</f>
+        <v/>
+      </c>
+      <c r="V115" s="20">
+        <f>IF($B115="","",ROUND(N($K115)*N($S115),0))</f>
+        <v/>
+      </c>
+      <c r="W115" s="20">
+        <f>IF($B115="","",N($P115)-N($U115)-N($V115))</f>
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="18">
@@ -9863,6 +12587,30 @@
         <f>IF($B116="","",IF($L116="감소","감소분 → 계약단가",IF(AND($M116="Y",OR($L116="증가",$L116="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L116="증가",IF(AND($N116&lt;&gt;"",$G116&gt;$N116),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L116="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R116" s="20">
+        <f>IF($B116="","",IF(N($O116)=0,0,IF(OR($L116="감소",AND($L116="증가",$M116&lt;&gt;"Y")),IF(N($G116)=0,0,ROUND(N(내역서!$G116)*$O116/$G116,0)),IF(N($J116)=0,0,ROUND(N(내역서!$O116)*$O116/$J116,0)))))</f>
+        <v/>
+      </c>
+      <c r="S116" s="20">
+        <f>IF($B116="","",IF(N($O116)=0,0,IF(OR($L116="감소",AND($L116="증가",$M116&lt;&gt;"Y")),IF(N($G116)=0,0,ROUND(N(내역서!$H116)*$O116/$G116,0)),IF(N($J116)=0,0,ROUND(N(내역서!$P116)*$O116/$J116,0)))))</f>
+        <v/>
+      </c>
+      <c r="T116" s="20">
+        <f>IF($B116="","",N($O116)-N($R116)-N($S116))</f>
+        <v/>
+      </c>
+      <c r="U116" s="20">
+        <f>IF($B116="","",ROUND(N($K116)*N($R116),0))</f>
+        <v/>
+      </c>
+      <c r="V116" s="20">
+        <f>IF($B116="","",ROUND(N($K116)*N($S116),0))</f>
+        <v/>
+      </c>
+      <c r="W116" s="20">
+        <f>IF($B116="","",N($P116)-N($U116)-N($V116))</f>
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="18">
@@ -9927,6 +12675,30 @@
         <f>IF($B117="","",IF($L117="감소","감소분 → 계약단가",IF(AND($M117="Y",OR($L117="증가",$L117="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L117="증가",IF(AND($N117&lt;&gt;"",$G117&gt;$N117),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L117="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R117" s="20">
+        <f>IF($B117="","",IF(N($O117)=0,0,IF(OR($L117="감소",AND($L117="증가",$M117&lt;&gt;"Y")),IF(N($G117)=0,0,ROUND(N(내역서!$G117)*$O117/$G117,0)),IF(N($J117)=0,0,ROUND(N(내역서!$O117)*$O117/$J117,0)))))</f>
+        <v/>
+      </c>
+      <c r="S117" s="20">
+        <f>IF($B117="","",IF(N($O117)=0,0,IF(OR($L117="감소",AND($L117="증가",$M117&lt;&gt;"Y")),IF(N($G117)=0,0,ROUND(N(내역서!$H117)*$O117/$G117,0)),IF(N($J117)=0,0,ROUND(N(내역서!$P117)*$O117/$J117,0)))))</f>
+        <v/>
+      </c>
+      <c r="T117" s="20">
+        <f>IF($B117="","",N($O117)-N($R117)-N($S117))</f>
+        <v/>
+      </c>
+      <c r="U117" s="20">
+        <f>IF($B117="","",ROUND(N($K117)*N($R117),0))</f>
+        <v/>
+      </c>
+      <c r="V117" s="20">
+        <f>IF($B117="","",ROUND(N($K117)*N($S117),0))</f>
+        <v/>
+      </c>
+      <c r="W117" s="20">
+        <f>IF($B117="","",N($P117)-N($U117)-N($V117))</f>
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="18">
@@ -9991,6 +12763,30 @@
         <f>IF($B118="","",IF($L118="감소","감소분 → 계약단가",IF(AND($M118="Y",OR($L118="증가",$L118="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L118="증가",IF(AND($N118&lt;&gt;"",$G118&gt;$N118),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L118="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R118" s="20">
+        <f>IF($B118="","",IF(N($O118)=0,0,IF(OR($L118="감소",AND($L118="증가",$M118&lt;&gt;"Y")),IF(N($G118)=0,0,ROUND(N(내역서!$G118)*$O118/$G118,0)),IF(N($J118)=0,0,ROUND(N(내역서!$O118)*$O118/$J118,0)))))</f>
+        <v/>
+      </c>
+      <c r="S118" s="20">
+        <f>IF($B118="","",IF(N($O118)=0,0,IF(OR($L118="감소",AND($L118="증가",$M118&lt;&gt;"Y")),IF(N($G118)=0,0,ROUND(N(내역서!$H118)*$O118/$G118,0)),IF(N($J118)=0,0,ROUND(N(내역서!$P118)*$O118/$J118,0)))))</f>
+        <v/>
+      </c>
+      <c r="T118" s="20">
+        <f>IF($B118="","",N($O118)-N($R118)-N($S118))</f>
+        <v/>
+      </c>
+      <c r="U118" s="20">
+        <f>IF($B118="","",ROUND(N($K118)*N($R118),0))</f>
+        <v/>
+      </c>
+      <c r="V118" s="20">
+        <f>IF($B118="","",ROUND(N($K118)*N($S118),0))</f>
+        <v/>
+      </c>
+      <c r="W118" s="20">
+        <f>IF($B118="","",N($P118)-N($U118)-N($V118))</f>
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="18">
@@ -10055,6 +12851,30 @@
         <f>IF($B119="","",IF($L119="감소","감소분 → 계약단가",IF(AND($M119="Y",OR($L119="증가",$L119="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L119="증가",IF(AND($N119&lt;&gt;"",$G119&gt;$N119),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L119="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R119" s="20">
+        <f>IF($B119="","",IF(N($O119)=0,0,IF(OR($L119="감소",AND($L119="증가",$M119&lt;&gt;"Y")),IF(N($G119)=0,0,ROUND(N(내역서!$G119)*$O119/$G119,0)),IF(N($J119)=0,0,ROUND(N(내역서!$O119)*$O119/$J119,0)))))</f>
+        <v/>
+      </c>
+      <c r="S119" s="20">
+        <f>IF($B119="","",IF(N($O119)=0,0,IF(OR($L119="감소",AND($L119="증가",$M119&lt;&gt;"Y")),IF(N($G119)=0,0,ROUND(N(내역서!$H119)*$O119/$G119,0)),IF(N($J119)=0,0,ROUND(N(내역서!$P119)*$O119/$J119,0)))))</f>
+        <v/>
+      </c>
+      <c r="T119" s="20">
+        <f>IF($B119="","",N($O119)-N($R119)-N($S119))</f>
+        <v/>
+      </c>
+      <c r="U119" s="20">
+        <f>IF($B119="","",ROUND(N($K119)*N($R119),0))</f>
+        <v/>
+      </c>
+      <c r="V119" s="20">
+        <f>IF($B119="","",ROUND(N($K119)*N($S119),0))</f>
+        <v/>
+      </c>
+      <c r="W119" s="20">
+        <f>IF($B119="","",N($P119)-N($U119)-N($V119))</f>
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="18">
@@ -10119,6 +12939,30 @@
         <f>IF($B120="","",IF($L120="감소","감소분 → 계약단가",IF(AND($M120="Y",OR($L120="증가",$L120="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L120="증가",IF(AND($N120&lt;&gt;"",$G120&gt;$N120),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L120="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R120" s="20">
+        <f>IF($B120="","",IF(N($O120)=0,0,IF(OR($L120="감소",AND($L120="증가",$M120&lt;&gt;"Y")),IF(N($G120)=0,0,ROUND(N(내역서!$G120)*$O120/$G120,0)),IF(N($J120)=0,0,ROUND(N(내역서!$O120)*$O120/$J120,0)))))</f>
+        <v/>
+      </c>
+      <c r="S120" s="20">
+        <f>IF($B120="","",IF(N($O120)=0,0,IF(OR($L120="감소",AND($L120="증가",$M120&lt;&gt;"Y")),IF(N($G120)=0,0,ROUND(N(내역서!$H120)*$O120/$G120,0)),IF(N($J120)=0,0,ROUND(N(내역서!$P120)*$O120/$J120,0)))))</f>
+        <v/>
+      </c>
+      <c r="T120" s="20">
+        <f>IF($B120="","",N($O120)-N($R120)-N($S120))</f>
+        <v/>
+      </c>
+      <c r="U120" s="20">
+        <f>IF($B120="","",ROUND(N($K120)*N($R120),0))</f>
+        <v/>
+      </c>
+      <c r="V120" s="20">
+        <f>IF($B120="","",ROUND(N($K120)*N($S120),0))</f>
+        <v/>
+      </c>
+      <c r="W120" s="20">
+        <f>IF($B120="","",N($P120)-N($U120)-N($V120))</f>
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="18">
@@ -10183,6 +13027,30 @@
         <f>IF($B121="","",IF($L121="감소","감소분 → 계약단가",IF(AND($M121="Y",OR($L121="증가",$L121="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L121="증가",IF(AND($N121&lt;&gt;"",$G121&gt;$N121),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L121="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R121" s="20">
+        <f>IF($B121="","",IF(N($O121)=0,0,IF(OR($L121="감소",AND($L121="증가",$M121&lt;&gt;"Y")),IF(N($G121)=0,0,ROUND(N(내역서!$G121)*$O121/$G121,0)),IF(N($J121)=0,0,ROUND(N(내역서!$O121)*$O121/$J121,0)))))</f>
+        <v/>
+      </c>
+      <c r="S121" s="20">
+        <f>IF($B121="","",IF(N($O121)=0,0,IF(OR($L121="감소",AND($L121="증가",$M121&lt;&gt;"Y")),IF(N($G121)=0,0,ROUND(N(내역서!$H121)*$O121/$G121,0)),IF(N($J121)=0,0,ROUND(N(내역서!$P121)*$O121/$J121,0)))))</f>
+        <v/>
+      </c>
+      <c r="T121" s="20">
+        <f>IF($B121="","",N($O121)-N($R121)-N($S121))</f>
+        <v/>
+      </c>
+      <c r="U121" s="20">
+        <f>IF($B121="","",ROUND(N($K121)*N($R121),0))</f>
+        <v/>
+      </c>
+      <c r="V121" s="20">
+        <f>IF($B121="","",ROUND(N($K121)*N($S121),0))</f>
+        <v/>
+      </c>
+      <c r="W121" s="20">
+        <f>IF($B121="","",N($P121)-N($U121)-N($V121))</f>
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="18">
@@ -10247,6 +13115,30 @@
         <f>IF($B122="","",IF($L122="감소","감소분 → 계약단가",IF(AND($M122="Y",OR($L122="증가",$L122="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L122="증가",IF(AND($N122&lt;&gt;"",$G122&gt;$N122),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L122="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R122" s="20">
+        <f>IF($B122="","",IF(N($O122)=0,0,IF(OR($L122="감소",AND($L122="증가",$M122&lt;&gt;"Y")),IF(N($G122)=0,0,ROUND(N(내역서!$G122)*$O122/$G122,0)),IF(N($J122)=0,0,ROUND(N(내역서!$O122)*$O122/$J122,0)))))</f>
+        <v/>
+      </c>
+      <c r="S122" s="20">
+        <f>IF($B122="","",IF(N($O122)=0,0,IF(OR($L122="감소",AND($L122="증가",$M122&lt;&gt;"Y")),IF(N($G122)=0,0,ROUND(N(내역서!$H122)*$O122/$G122,0)),IF(N($J122)=0,0,ROUND(N(내역서!$P122)*$O122/$J122,0)))))</f>
+        <v/>
+      </c>
+      <c r="T122" s="20">
+        <f>IF($B122="","",N($O122)-N($R122)-N($S122))</f>
+        <v/>
+      </c>
+      <c r="U122" s="20">
+        <f>IF($B122="","",ROUND(N($K122)*N($R122),0))</f>
+        <v/>
+      </c>
+      <c r="V122" s="20">
+        <f>IF($B122="","",ROUND(N($K122)*N($S122),0))</f>
+        <v/>
+      </c>
+      <c r="W122" s="20">
+        <f>IF($B122="","",N($P122)-N($U122)-N($V122))</f>
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="18">
@@ -10311,6 +13203,30 @@
         <f>IF($B123="","",IF($L123="감소","감소분 → 계약단가",IF(AND($M123="Y",OR($L123="증가",$L123="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L123="증가",IF(AND($N123&lt;&gt;"",$G123&gt;$N123),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L123="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R123" s="20">
+        <f>IF($B123="","",IF(N($O123)=0,0,IF(OR($L123="감소",AND($L123="증가",$M123&lt;&gt;"Y")),IF(N($G123)=0,0,ROUND(N(내역서!$G123)*$O123/$G123,0)),IF(N($J123)=0,0,ROUND(N(내역서!$O123)*$O123/$J123,0)))))</f>
+        <v/>
+      </c>
+      <c r="S123" s="20">
+        <f>IF($B123="","",IF(N($O123)=0,0,IF(OR($L123="감소",AND($L123="증가",$M123&lt;&gt;"Y")),IF(N($G123)=0,0,ROUND(N(내역서!$H123)*$O123/$G123,0)),IF(N($J123)=0,0,ROUND(N(내역서!$P123)*$O123/$J123,0)))))</f>
+        <v/>
+      </c>
+      <c r="T123" s="20">
+        <f>IF($B123="","",N($O123)-N($R123)-N($S123))</f>
+        <v/>
+      </c>
+      <c r="U123" s="20">
+        <f>IF($B123="","",ROUND(N($K123)*N($R123),0))</f>
+        <v/>
+      </c>
+      <c r="V123" s="20">
+        <f>IF($B123="","",ROUND(N($K123)*N($S123),0))</f>
+        <v/>
+      </c>
+      <c r="W123" s="20">
+        <f>IF($B123="","",N($P123)-N($U123)-N($V123))</f>
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="18">
@@ -10375,6 +13291,30 @@
         <f>IF($B124="","",IF($L124="감소","감소분 → 계약단가",IF(AND($M124="Y",OR($L124="증가",$L124="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L124="증가",IF(AND($N124&lt;&gt;"",$G124&gt;$N124),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L124="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R124" s="20">
+        <f>IF($B124="","",IF(N($O124)=0,0,IF(OR($L124="감소",AND($L124="증가",$M124&lt;&gt;"Y")),IF(N($G124)=0,0,ROUND(N(내역서!$G124)*$O124/$G124,0)),IF(N($J124)=0,0,ROUND(N(내역서!$O124)*$O124/$J124,0)))))</f>
+        <v/>
+      </c>
+      <c r="S124" s="20">
+        <f>IF($B124="","",IF(N($O124)=0,0,IF(OR($L124="감소",AND($L124="증가",$M124&lt;&gt;"Y")),IF(N($G124)=0,0,ROUND(N(내역서!$H124)*$O124/$G124,0)),IF(N($J124)=0,0,ROUND(N(내역서!$P124)*$O124/$J124,0)))))</f>
+        <v/>
+      </c>
+      <c r="T124" s="20">
+        <f>IF($B124="","",N($O124)-N($R124)-N($S124))</f>
+        <v/>
+      </c>
+      <c r="U124" s="20">
+        <f>IF($B124="","",ROUND(N($K124)*N($R124),0))</f>
+        <v/>
+      </c>
+      <c r="V124" s="20">
+        <f>IF($B124="","",ROUND(N($K124)*N($S124),0))</f>
+        <v/>
+      </c>
+      <c r="W124" s="20">
+        <f>IF($B124="","",N($P124)-N($U124)-N($V124))</f>
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="18">
@@ -10439,6 +13379,30 @@
         <f>IF($B125="","",IF($L125="감소","감소분 → 계약단가",IF(AND($M125="Y",OR($L125="증가",$L125="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L125="증가",IF(AND($N125&lt;&gt;"",$G125&gt;$N125),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L125="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R125" s="20">
+        <f>IF($B125="","",IF(N($O125)=0,0,IF(OR($L125="감소",AND($L125="증가",$M125&lt;&gt;"Y")),IF(N($G125)=0,0,ROUND(N(내역서!$G125)*$O125/$G125,0)),IF(N($J125)=0,0,ROUND(N(내역서!$O125)*$O125/$J125,0)))))</f>
+        <v/>
+      </c>
+      <c r="S125" s="20">
+        <f>IF($B125="","",IF(N($O125)=0,0,IF(OR($L125="감소",AND($L125="증가",$M125&lt;&gt;"Y")),IF(N($G125)=0,0,ROUND(N(내역서!$H125)*$O125/$G125,0)),IF(N($J125)=0,0,ROUND(N(내역서!$P125)*$O125/$J125,0)))))</f>
+        <v/>
+      </c>
+      <c r="T125" s="20">
+        <f>IF($B125="","",N($O125)-N($R125)-N($S125))</f>
+        <v/>
+      </c>
+      <c r="U125" s="20">
+        <f>IF($B125="","",ROUND(N($K125)*N($R125),0))</f>
+        <v/>
+      </c>
+      <c r="V125" s="20">
+        <f>IF($B125="","",ROUND(N($K125)*N($S125),0))</f>
+        <v/>
+      </c>
+      <c r="W125" s="20">
+        <f>IF($B125="","",N($P125)-N($U125)-N($V125))</f>
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="18">
@@ -10503,6 +13467,30 @@
         <f>IF($B126="","",IF($L126="감소","감소분 → 계약단가",IF(AND($M126="Y",OR($L126="증가",$L126="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L126="증가",IF(AND($N126&lt;&gt;"",$G126&gt;$N126),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L126="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R126" s="20">
+        <f>IF($B126="","",IF(N($O126)=0,0,IF(OR($L126="감소",AND($L126="증가",$M126&lt;&gt;"Y")),IF(N($G126)=0,0,ROUND(N(내역서!$G126)*$O126/$G126,0)),IF(N($J126)=0,0,ROUND(N(내역서!$O126)*$O126/$J126,0)))))</f>
+        <v/>
+      </c>
+      <c r="S126" s="20">
+        <f>IF($B126="","",IF(N($O126)=0,0,IF(OR($L126="감소",AND($L126="증가",$M126&lt;&gt;"Y")),IF(N($G126)=0,0,ROUND(N(내역서!$H126)*$O126/$G126,0)),IF(N($J126)=0,0,ROUND(N(내역서!$P126)*$O126/$J126,0)))))</f>
+        <v/>
+      </c>
+      <c r="T126" s="20">
+        <f>IF($B126="","",N($O126)-N($R126)-N($S126))</f>
+        <v/>
+      </c>
+      <c r="U126" s="20">
+        <f>IF($B126="","",ROUND(N($K126)*N($R126),0))</f>
+        <v/>
+      </c>
+      <c r="V126" s="20">
+        <f>IF($B126="","",ROUND(N($K126)*N($S126),0))</f>
+        <v/>
+      </c>
+      <c r="W126" s="20">
+        <f>IF($B126="","",N($P126)-N($U126)-N($V126))</f>
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="18">
@@ -10567,6 +13555,30 @@
         <f>IF($B127="","",IF($L127="감소","감소분 → 계약단가",IF(AND($M127="Y",OR($L127="증가",$L127="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L127="증가",IF(AND($N127&lt;&gt;"",$G127&gt;$N127),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L127="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R127" s="20">
+        <f>IF($B127="","",IF(N($O127)=0,0,IF(OR($L127="감소",AND($L127="증가",$M127&lt;&gt;"Y")),IF(N($G127)=0,0,ROUND(N(내역서!$G127)*$O127/$G127,0)),IF(N($J127)=0,0,ROUND(N(내역서!$O127)*$O127/$J127,0)))))</f>
+        <v/>
+      </c>
+      <c r="S127" s="20">
+        <f>IF($B127="","",IF(N($O127)=0,0,IF(OR($L127="감소",AND($L127="증가",$M127&lt;&gt;"Y")),IF(N($G127)=0,0,ROUND(N(내역서!$H127)*$O127/$G127,0)),IF(N($J127)=0,0,ROUND(N(내역서!$P127)*$O127/$J127,0)))))</f>
+        <v/>
+      </c>
+      <c r="T127" s="20">
+        <f>IF($B127="","",N($O127)-N($R127)-N($S127))</f>
+        <v/>
+      </c>
+      <c r="U127" s="20">
+        <f>IF($B127="","",ROUND(N($K127)*N($R127),0))</f>
+        <v/>
+      </c>
+      <c r="V127" s="20">
+        <f>IF($B127="","",ROUND(N($K127)*N($S127),0))</f>
+        <v/>
+      </c>
+      <c r="W127" s="20">
+        <f>IF($B127="","",N($P127)-N($U127)-N($V127))</f>
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="18">
@@ -10631,6 +13643,30 @@
         <f>IF($B128="","",IF($L128="감소","감소분 → 계약단가",IF(AND($M128="Y",OR($L128="증가",$L128="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L128="증가",IF(AND($N128&lt;&gt;"",$G128&gt;$N128),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L128="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R128" s="20">
+        <f>IF($B128="","",IF(N($O128)=0,0,IF(OR($L128="감소",AND($L128="증가",$M128&lt;&gt;"Y")),IF(N($G128)=0,0,ROUND(N(내역서!$G128)*$O128/$G128,0)),IF(N($J128)=0,0,ROUND(N(내역서!$O128)*$O128/$J128,0)))))</f>
+        <v/>
+      </c>
+      <c r="S128" s="20">
+        <f>IF($B128="","",IF(N($O128)=0,0,IF(OR($L128="감소",AND($L128="증가",$M128&lt;&gt;"Y")),IF(N($G128)=0,0,ROUND(N(내역서!$H128)*$O128/$G128,0)),IF(N($J128)=0,0,ROUND(N(내역서!$P128)*$O128/$J128,0)))))</f>
+        <v/>
+      </c>
+      <c r="T128" s="20">
+        <f>IF($B128="","",N($O128)-N($R128)-N($S128))</f>
+        <v/>
+      </c>
+      <c r="U128" s="20">
+        <f>IF($B128="","",ROUND(N($K128)*N($R128),0))</f>
+        <v/>
+      </c>
+      <c r="V128" s="20">
+        <f>IF($B128="","",ROUND(N($K128)*N($S128),0))</f>
+        <v/>
+      </c>
+      <c r="W128" s="20">
+        <f>IF($B128="","",N($P128)-N($U128)-N($V128))</f>
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="18">
@@ -10695,6 +13731,30 @@
         <f>IF($B129="","",IF($L129="감소","감소분 → 계약단가",IF(AND($M129="Y",OR($L129="증가",$L129="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L129="증가",IF(AND($N129&lt;&gt;"",$G129&gt;$N129),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L129="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R129" s="20">
+        <f>IF($B129="","",IF(N($O129)=0,0,IF(OR($L129="감소",AND($L129="증가",$M129&lt;&gt;"Y")),IF(N($G129)=0,0,ROUND(N(내역서!$G129)*$O129/$G129,0)),IF(N($J129)=0,0,ROUND(N(내역서!$O129)*$O129/$J129,0)))))</f>
+        <v/>
+      </c>
+      <c r="S129" s="20">
+        <f>IF($B129="","",IF(N($O129)=0,0,IF(OR($L129="감소",AND($L129="증가",$M129&lt;&gt;"Y")),IF(N($G129)=0,0,ROUND(N(내역서!$H129)*$O129/$G129,0)),IF(N($J129)=0,0,ROUND(N(내역서!$P129)*$O129/$J129,0)))))</f>
+        <v/>
+      </c>
+      <c r="T129" s="20">
+        <f>IF($B129="","",N($O129)-N($R129)-N($S129))</f>
+        <v/>
+      </c>
+      <c r="U129" s="20">
+        <f>IF($B129="","",ROUND(N($K129)*N($R129),0))</f>
+        <v/>
+      </c>
+      <c r="V129" s="20">
+        <f>IF($B129="","",ROUND(N($K129)*N($S129),0))</f>
+        <v/>
+      </c>
+      <c r="W129" s="20">
+        <f>IF($B129="","",N($P129)-N($U129)-N($V129))</f>
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="18">
@@ -10759,6 +13819,30 @@
         <f>IF($B130="","",IF($L130="감소","감소분 → 계약단가",IF(AND($M130="Y",OR($L130="증가",$L130="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L130="증가",IF(AND($N130&lt;&gt;"",$G130&gt;$N130),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L130="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R130" s="20">
+        <f>IF($B130="","",IF(N($O130)=0,0,IF(OR($L130="감소",AND($L130="증가",$M130&lt;&gt;"Y")),IF(N($G130)=0,0,ROUND(N(내역서!$G130)*$O130/$G130,0)),IF(N($J130)=0,0,ROUND(N(내역서!$O130)*$O130/$J130,0)))))</f>
+        <v/>
+      </c>
+      <c r="S130" s="20">
+        <f>IF($B130="","",IF(N($O130)=0,0,IF(OR($L130="감소",AND($L130="증가",$M130&lt;&gt;"Y")),IF(N($G130)=0,0,ROUND(N(내역서!$H130)*$O130/$G130,0)),IF(N($J130)=0,0,ROUND(N(내역서!$P130)*$O130/$J130,0)))))</f>
+        <v/>
+      </c>
+      <c r="T130" s="20">
+        <f>IF($B130="","",N($O130)-N($R130)-N($S130))</f>
+        <v/>
+      </c>
+      <c r="U130" s="20">
+        <f>IF($B130="","",ROUND(N($K130)*N($R130),0))</f>
+        <v/>
+      </c>
+      <c r="V130" s="20">
+        <f>IF($B130="","",ROUND(N($K130)*N($S130),0))</f>
+        <v/>
+      </c>
+      <c r="W130" s="20">
+        <f>IF($B130="","",N($P130)-N($U130)-N($V130))</f>
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="18">
@@ -10823,6 +13907,30 @@
         <f>IF($B131="","",IF($L131="감소","감소분 → 계약단가",IF(AND($M131="Y",OR($L131="증가",$L131="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L131="증가",IF(AND($N131&lt;&gt;"",$G131&gt;$N131),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L131="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R131" s="20">
+        <f>IF($B131="","",IF(N($O131)=0,0,IF(OR($L131="감소",AND($L131="증가",$M131&lt;&gt;"Y")),IF(N($G131)=0,0,ROUND(N(내역서!$G131)*$O131/$G131,0)),IF(N($J131)=0,0,ROUND(N(내역서!$O131)*$O131/$J131,0)))))</f>
+        <v/>
+      </c>
+      <c r="S131" s="20">
+        <f>IF($B131="","",IF(N($O131)=0,0,IF(OR($L131="감소",AND($L131="증가",$M131&lt;&gt;"Y")),IF(N($G131)=0,0,ROUND(N(내역서!$H131)*$O131/$G131,0)),IF(N($J131)=0,0,ROUND(N(내역서!$P131)*$O131/$J131,0)))))</f>
+        <v/>
+      </c>
+      <c r="T131" s="20">
+        <f>IF($B131="","",N($O131)-N($R131)-N($S131))</f>
+        <v/>
+      </c>
+      <c r="U131" s="20">
+        <f>IF($B131="","",ROUND(N($K131)*N($R131),0))</f>
+        <v/>
+      </c>
+      <c r="V131" s="20">
+        <f>IF($B131="","",ROUND(N($K131)*N($S131),0))</f>
+        <v/>
+      </c>
+      <c r="W131" s="20">
+        <f>IF($B131="","",N($P131)-N($U131)-N($V131))</f>
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="18">
@@ -10887,6 +13995,30 @@
         <f>IF($B132="","",IF($L132="감소","감소분 → 계약단가",IF(AND($M132="Y",OR($L132="증가",$L132="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L132="증가",IF(AND($N132&lt;&gt;"",$G132&gt;$N132),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L132="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R132" s="20">
+        <f>IF($B132="","",IF(N($O132)=0,0,IF(OR($L132="감소",AND($L132="증가",$M132&lt;&gt;"Y")),IF(N($G132)=0,0,ROUND(N(내역서!$G132)*$O132/$G132,0)),IF(N($J132)=0,0,ROUND(N(내역서!$O132)*$O132/$J132,0)))))</f>
+        <v/>
+      </c>
+      <c r="S132" s="20">
+        <f>IF($B132="","",IF(N($O132)=0,0,IF(OR($L132="감소",AND($L132="증가",$M132&lt;&gt;"Y")),IF(N($G132)=0,0,ROUND(N(내역서!$H132)*$O132/$G132,0)),IF(N($J132)=0,0,ROUND(N(내역서!$P132)*$O132/$J132,0)))))</f>
+        <v/>
+      </c>
+      <c r="T132" s="20">
+        <f>IF($B132="","",N($O132)-N($R132)-N($S132))</f>
+        <v/>
+      </c>
+      <c r="U132" s="20">
+        <f>IF($B132="","",ROUND(N($K132)*N($R132),0))</f>
+        <v/>
+      </c>
+      <c r="V132" s="20">
+        <f>IF($B132="","",ROUND(N($K132)*N($S132),0))</f>
+        <v/>
+      </c>
+      <c r="W132" s="20">
+        <f>IF($B132="","",N($P132)-N($U132)-N($V132))</f>
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="18">
@@ -10951,6 +14083,30 @@
         <f>IF($B133="","",IF($L133="감소","감소분 → 계약단가",IF(AND($M133="Y",OR($L133="증가",$L133="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L133="증가",IF(AND($N133&lt;&gt;"",$G133&gt;$N133),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L133="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R133" s="20">
+        <f>IF($B133="","",IF(N($O133)=0,0,IF(OR($L133="감소",AND($L133="증가",$M133&lt;&gt;"Y")),IF(N($G133)=0,0,ROUND(N(내역서!$G133)*$O133/$G133,0)),IF(N($J133)=0,0,ROUND(N(내역서!$O133)*$O133/$J133,0)))))</f>
+        <v/>
+      </c>
+      <c r="S133" s="20">
+        <f>IF($B133="","",IF(N($O133)=0,0,IF(OR($L133="감소",AND($L133="증가",$M133&lt;&gt;"Y")),IF(N($G133)=0,0,ROUND(N(내역서!$H133)*$O133/$G133,0)),IF(N($J133)=0,0,ROUND(N(내역서!$P133)*$O133/$J133,0)))))</f>
+        <v/>
+      </c>
+      <c r="T133" s="20">
+        <f>IF($B133="","",N($O133)-N($R133)-N($S133))</f>
+        <v/>
+      </c>
+      <c r="U133" s="20">
+        <f>IF($B133="","",ROUND(N($K133)*N($R133),0))</f>
+        <v/>
+      </c>
+      <c r="V133" s="20">
+        <f>IF($B133="","",ROUND(N($K133)*N($S133),0))</f>
+        <v/>
+      </c>
+      <c r="W133" s="20">
+        <f>IF($B133="","",N($P133)-N($U133)-N($V133))</f>
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="18">
@@ -11015,6 +14171,30 @@
         <f>IF($B134="","",IF($L134="감소","감소분 → 계약단가",IF(AND($M134="Y",OR($L134="증가",$L134="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L134="증가",IF(AND($N134&lt;&gt;"",$G134&gt;$N134),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L134="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R134" s="20">
+        <f>IF($B134="","",IF(N($O134)=0,0,IF(OR($L134="감소",AND($L134="증가",$M134&lt;&gt;"Y")),IF(N($G134)=0,0,ROUND(N(내역서!$G134)*$O134/$G134,0)),IF(N($J134)=0,0,ROUND(N(내역서!$O134)*$O134/$J134,0)))))</f>
+        <v/>
+      </c>
+      <c r="S134" s="20">
+        <f>IF($B134="","",IF(N($O134)=0,0,IF(OR($L134="감소",AND($L134="증가",$M134&lt;&gt;"Y")),IF(N($G134)=0,0,ROUND(N(내역서!$H134)*$O134/$G134,0)),IF(N($J134)=0,0,ROUND(N(내역서!$P134)*$O134/$J134,0)))))</f>
+        <v/>
+      </c>
+      <c r="T134" s="20">
+        <f>IF($B134="","",N($O134)-N($R134)-N($S134))</f>
+        <v/>
+      </c>
+      <c r="U134" s="20">
+        <f>IF($B134="","",ROUND(N($K134)*N($R134),0))</f>
+        <v/>
+      </c>
+      <c r="V134" s="20">
+        <f>IF($B134="","",ROUND(N($K134)*N($S134),0))</f>
+        <v/>
+      </c>
+      <c r="W134" s="20">
+        <f>IF($B134="","",N($P134)-N($U134)-N($V134))</f>
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="18">
@@ -11079,6 +14259,30 @@
         <f>IF($B135="","",IF($L135="감소","감소분 → 계약단가",IF(AND($M135="Y",OR($L135="증가",$L135="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L135="증가",IF(AND($N135&lt;&gt;"",$G135&gt;$N135),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L135="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R135" s="20">
+        <f>IF($B135="","",IF(N($O135)=0,0,IF(OR($L135="감소",AND($L135="증가",$M135&lt;&gt;"Y")),IF(N($G135)=0,0,ROUND(N(내역서!$G135)*$O135/$G135,0)),IF(N($J135)=0,0,ROUND(N(내역서!$O135)*$O135/$J135,0)))))</f>
+        <v/>
+      </c>
+      <c r="S135" s="20">
+        <f>IF($B135="","",IF(N($O135)=0,0,IF(OR($L135="감소",AND($L135="증가",$M135&lt;&gt;"Y")),IF(N($G135)=0,0,ROUND(N(내역서!$H135)*$O135/$G135,0)),IF(N($J135)=0,0,ROUND(N(내역서!$P135)*$O135/$J135,0)))))</f>
+        <v/>
+      </c>
+      <c r="T135" s="20">
+        <f>IF($B135="","",N($O135)-N($R135)-N($S135))</f>
+        <v/>
+      </c>
+      <c r="U135" s="20">
+        <f>IF($B135="","",ROUND(N($K135)*N($R135),0))</f>
+        <v/>
+      </c>
+      <c r="V135" s="20">
+        <f>IF($B135="","",ROUND(N($K135)*N($S135),0))</f>
+        <v/>
+      </c>
+      <c r="W135" s="20">
+        <f>IF($B135="","",N($P135)-N($U135)-N($V135))</f>
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="18">
@@ -11143,6 +14347,30 @@
         <f>IF($B136="","",IF($L136="감소","감소분 → 계약단가",IF(AND($M136="Y",OR($L136="증가",$L136="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L136="증가",IF(AND($N136&lt;&gt;"",$G136&gt;$N136),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L136="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R136" s="20">
+        <f>IF($B136="","",IF(N($O136)=0,0,IF(OR($L136="감소",AND($L136="증가",$M136&lt;&gt;"Y")),IF(N($G136)=0,0,ROUND(N(내역서!$G136)*$O136/$G136,0)),IF(N($J136)=0,0,ROUND(N(내역서!$O136)*$O136/$J136,0)))))</f>
+        <v/>
+      </c>
+      <c r="S136" s="20">
+        <f>IF($B136="","",IF(N($O136)=0,0,IF(OR($L136="감소",AND($L136="증가",$M136&lt;&gt;"Y")),IF(N($G136)=0,0,ROUND(N(내역서!$H136)*$O136/$G136,0)),IF(N($J136)=0,0,ROUND(N(내역서!$P136)*$O136/$J136,0)))))</f>
+        <v/>
+      </c>
+      <c r="T136" s="20">
+        <f>IF($B136="","",N($O136)-N($R136)-N($S136))</f>
+        <v/>
+      </c>
+      <c r="U136" s="20">
+        <f>IF($B136="","",ROUND(N($K136)*N($R136),0))</f>
+        <v/>
+      </c>
+      <c r="V136" s="20">
+        <f>IF($B136="","",ROUND(N($K136)*N($S136),0))</f>
+        <v/>
+      </c>
+      <c r="W136" s="20">
+        <f>IF($B136="","",N($P136)-N($U136)-N($V136))</f>
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="18">
@@ -11207,6 +14435,30 @@
         <f>IF($B137="","",IF($L137="감소","감소분 → 계약단가",IF(AND($M137="Y",OR($L137="증가",$L137="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L137="증가",IF(AND($N137&lt;&gt;"",$G137&gt;$N137),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L137="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R137" s="20">
+        <f>IF($B137="","",IF(N($O137)=0,0,IF(OR($L137="감소",AND($L137="증가",$M137&lt;&gt;"Y")),IF(N($G137)=0,0,ROUND(N(내역서!$G137)*$O137/$G137,0)),IF(N($J137)=0,0,ROUND(N(내역서!$O137)*$O137/$J137,0)))))</f>
+        <v/>
+      </c>
+      <c r="S137" s="20">
+        <f>IF($B137="","",IF(N($O137)=0,0,IF(OR($L137="감소",AND($L137="증가",$M137&lt;&gt;"Y")),IF(N($G137)=0,0,ROUND(N(내역서!$H137)*$O137/$G137,0)),IF(N($J137)=0,0,ROUND(N(내역서!$P137)*$O137/$J137,0)))))</f>
+        <v/>
+      </c>
+      <c r="T137" s="20">
+        <f>IF($B137="","",N($O137)-N($R137)-N($S137))</f>
+        <v/>
+      </c>
+      <c r="U137" s="20">
+        <f>IF($B137="","",ROUND(N($K137)*N($R137),0))</f>
+        <v/>
+      </c>
+      <c r="V137" s="20">
+        <f>IF($B137="","",ROUND(N($K137)*N($S137),0))</f>
+        <v/>
+      </c>
+      <c r="W137" s="20">
+        <f>IF($B137="","",N($P137)-N($U137)-N($V137))</f>
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="18">
@@ -11271,6 +14523,30 @@
         <f>IF($B138="","",IF($L138="감소","감소분 → 계약단가",IF(AND($M138="Y",OR($L138="증가",$L138="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L138="증가",IF(AND($N138&lt;&gt;"",$G138&gt;$N138),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L138="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R138" s="20">
+        <f>IF($B138="","",IF(N($O138)=0,0,IF(OR($L138="감소",AND($L138="증가",$M138&lt;&gt;"Y")),IF(N($G138)=0,0,ROUND(N(내역서!$G138)*$O138/$G138,0)),IF(N($J138)=0,0,ROUND(N(내역서!$O138)*$O138/$J138,0)))))</f>
+        <v/>
+      </c>
+      <c r="S138" s="20">
+        <f>IF($B138="","",IF(N($O138)=0,0,IF(OR($L138="감소",AND($L138="증가",$M138&lt;&gt;"Y")),IF(N($G138)=0,0,ROUND(N(내역서!$H138)*$O138/$G138,0)),IF(N($J138)=0,0,ROUND(N(내역서!$P138)*$O138/$J138,0)))))</f>
+        <v/>
+      </c>
+      <c r="T138" s="20">
+        <f>IF($B138="","",N($O138)-N($R138)-N($S138))</f>
+        <v/>
+      </c>
+      <c r="U138" s="20">
+        <f>IF($B138="","",ROUND(N($K138)*N($R138),0))</f>
+        <v/>
+      </c>
+      <c r="V138" s="20">
+        <f>IF($B138="","",ROUND(N($K138)*N($S138),0))</f>
+        <v/>
+      </c>
+      <c r="W138" s="20">
+        <f>IF($B138="","",N($P138)-N($U138)-N($V138))</f>
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="18">
@@ -11335,6 +14611,30 @@
         <f>IF($B139="","",IF($L139="감소","감소분 → 계약단가",IF(AND($M139="Y",OR($L139="증가",$L139="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L139="증가",IF(AND($N139&lt;&gt;"",$G139&gt;$N139),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L139="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R139" s="20">
+        <f>IF($B139="","",IF(N($O139)=0,0,IF(OR($L139="감소",AND($L139="증가",$M139&lt;&gt;"Y")),IF(N($G139)=0,0,ROUND(N(내역서!$G139)*$O139/$G139,0)),IF(N($J139)=0,0,ROUND(N(내역서!$O139)*$O139/$J139,0)))))</f>
+        <v/>
+      </c>
+      <c r="S139" s="20">
+        <f>IF($B139="","",IF(N($O139)=0,0,IF(OR($L139="감소",AND($L139="증가",$M139&lt;&gt;"Y")),IF(N($G139)=0,0,ROUND(N(내역서!$H139)*$O139/$G139,0)),IF(N($J139)=0,0,ROUND(N(내역서!$P139)*$O139/$J139,0)))))</f>
+        <v/>
+      </c>
+      <c r="T139" s="20">
+        <f>IF($B139="","",N($O139)-N($R139)-N($S139))</f>
+        <v/>
+      </c>
+      <c r="U139" s="20">
+        <f>IF($B139="","",ROUND(N($K139)*N($R139),0))</f>
+        <v/>
+      </c>
+      <c r="V139" s="20">
+        <f>IF($B139="","",ROUND(N($K139)*N($S139),0))</f>
+        <v/>
+      </c>
+      <c r="W139" s="20">
+        <f>IF($B139="","",N($P139)-N($U139)-N($V139))</f>
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="18">
@@ -11399,6 +14699,30 @@
         <f>IF($B140="","",IF($L140="감소","감소분 → 계약단가",IF(AND($M140="Y",OR($L140="증가",$L140="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L140="증가",IF(AND($N140&lt;&gt;"",$G140&gt;$N140),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L140="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R140" s="20">
+        <f>IF($B140="","",IF(N($O140)=0,0,IF(OR($L140="감소",AND($L140="증가",$M140&lt;&gt;"Y")),IF(N($G140)=0,0,ROUND(N(내역서!$G140)*$O140/$G140,0)),IF(N($J140)=0,0,ROUND(N(내역서!$O140)*$O140/$J140,0)))))</f>
+        <v/>
+      </c>
+      <c r="S140" s="20">
+        <f>IF($B140="","",IF(N($O140)=0,0,IF(OR($L140="감소",AND($L140="증가",$M140&lt;&gt;"Y")),IF(N($G140)=0,0,ROUND(N(내역서!$H140)*$O140/$G140,0)),IF(N($J140)=0,0,ROUND(N(내역서!$P140)*$O140/$J140,0)))))</f>
+        <v/>
+      </c>
+      <c r="T140" s="20">
+        <f>IF($B140="","",N($O140)-N($R140)-N($S140))</f>
+        <v/>
+      </c>
+      <c r="U140" s="20">
+        <f>IF($B140="","",ROUND(N($K140)*N($R140),0))</f>
+        <v/>
+      </c>
+      <c r="V140" s="20">
+        <f>IF($B140="","",ROUND(N($K140)*N($S140),0))</f>
+        <v/>
+      </c>
+      <c r="W140" s="20">
+        <f>IF($B140="","",N($P140)-N($U140)-N($V140))</f>
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="18">
@@ -11463,6 +14787,30 @@
         <f>IF($B141="","",IF($L141="감소","감소분 → 계약단가",IF(AND($M141="Y",OR($L141="증가",$L141="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L141="증가",IF(AND($N141&lt;&gt;"",$G141&gt;$N141),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L141="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R141" s="20">
+        <f>IF($B141="","",IF(N($O141)=0,0,IF(OR($L141="감소",AND($L141="증가",$M141&lt;&gt;"Y")),IF(N($G141)=0,0,ROUND(N(내역서!$G141)*$O141/$G141,0)),IF(N($J141)=0,0,ROUND(N(내역서!$O141)*$O141/$J141,0)))))</f>
+        <v/>
+      </c>
+      <c r="S141" s="20">
+        <f>IF($B141="","",IF(N($O141)=0,0,IF(OR($L141="감소",AND($L141="증가",$M141&lt;&gt;"Y")),IF(N($G141)=0,0,ROUND(N(내역서!$H141)*$O141/$G141,0)),IF(N($J141)=0,0,ROUND(N(내역서!$P141)*$O141/$J141,0)))))</f>
+        <v/>
+      </c>
+      <c r="T141" s="20">
+        <f>IF($B141="","",N($O141)-N($R141)-N($S141))</f>
+        <v/>
+      </c>
+      <c r="U141" s="20">
+        <f>IF($B141="","",ROUND(N($K141)*N($R141),0))</f>
+        <v/>
+      </c>
+      <c r="V141" s="20">
+        <f>IF($B141="","",ROUND(N($K141)*N($S141),0))</f>
+        <v/>
+      </c>
+      <c r="W141" s="20">
+        <f>IF($B141="","",N($P141)-N($U141)-N($V141))</f>
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="18">
@@ -11527,6 +14875,30 @@
         <f>IF($B142="","",IF($L142="감소","감소분 → 계약단가",IF(AND($M142="Y",OR($L142="증가",$L142="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L142="증가",IF(AND($N142&lt;&gt;"",$G142&gt;$N142),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L142="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R142" s="20">
+        <f>IF($B142="","",IF(N($O142)=0,0,IF(OR($L142="감소",AND($L142="증가",$M142&lt;&gt;"Y")),IF(N($G142)=0,0,ROUND(N(내역서!$G142)*$O142/$G142,0)),IF(N($J142)=0,0,ROUND(N(내역서!$O142)*$O142/$J142,0)))))</f>
+        <v/>
+      </c>
+      <c r="S142" s="20">
+        <f>IF($B142="","",IF(N($O142)=0,0,IF(OR($L142="감소",AND($L142="증가",$M142&lt;&gt;"Y")),IF(N($G142)=0,0,ROUND(N(내역서!$H142)*$O142/$G142,0)),IF(N($J142)=0,0,ROUND(N(내역서!$P142)*$O142/$J142,0)))))</f>
+        <v/>
+      </c>
+      <c r="T142" s="20">
+        <f>IF($B142="","",N($O142)-N($R142)-N($S142))</f>
+        <v/>
+      </c>
+      <c r="U142" s="20">
+        <f>IF($B142="","",ROUND(N($K142)*N($R142),0))</f>
+        <v/>
+      </c>
+      <c r="V142" s="20">
+        <f>IF($B142="","",ROUND(N($K142)*N($S142),0))</f>
+        <v/>
+      </c>
+      <c r="W142" s="20">
+        <f>IF($B142="","",N($P142)-N($U142)-N($V142))</f>
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="18">
@@ -11591,6 +14963,30 @@
         <f>IF($B143="","",IF($L143="감소","감소분 → 계약단가",IF(AND($M143="Y",OR($L143="증가",$L143="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L143="증가",IF(AND($N143&lt;&gt;"",$G143&gt;$N143),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L143="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R143" s="20">
+        <f>IF($B143="","",IF(N($O143)=0,0,IF(OR($L143="감소",AND($L143="증가",$M143&lt;&gt;"Y")),IF(N($G143)=0,0,ROUND(N(내역서!$G143)*$O143/$G143,0)),IF(N($J143)=0,0,ROUND(N(내역서!$O143)*$O143/$J143,0)))))</f>
+        <v/>
+      </c>
+      <c r="S143" s="20">
+        <f>IF($B143="","",IF(N($O143)=0,0,IF(OR($L143="감소",AND($L143="증가",$M143&lt;&gt;"Y")),IF(N($G143)=0,0,ROUND(N(내역서!$H143)*$O143/$G143,0)),IF(N($J143)=0,0,ROUND(N(내역서!$P143)*$O143/$J143,0)))))</f>
+        <v/>
+      </c>
+      <c r="T143" s="20">
+        <f>IF($B143="","",N($O143)-N($R143)-N($S143))</f>
+        <v/>
+      </c>
+      <c r="U143" s="20">
+        <f>IF($B143="","",ROUND(N($K143)*N($R143),0))</f>
+        <v/>
+      </c>
+      <c r="V143" s="20">
+        <f>IF($B143="","",ROUND(N($K143)*N($S143),0))</f>
+        <v/>
+      </c>
+      <c r="W143" s="20">
+        <f>IF($B143="","",N($P143)-N($U143)-N($V143))</f>
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="18">
@@ -11655,6 +15051,30 @@
         <f>IF($B144="","",IF($L144="감소","감소분 → 계약단가",IF(AND($M144="Y",OR($L144="증가",$L144="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L144="증가",IF(AND($N144&lt;&gt;"",$G144&gt;$N144),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L144="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R144" s="20">
+        <f>IF($B144="","",IF(N($O144)=0,0,IF(OR($L144="감소",AND($L144="증가",$M144&lt;&gt;"Y")),IF(N($G144)=0,0,ROUND(N(내역서!$G144)*$O144/$G144,0)),IF(N($J144)=0,0,ROUND(N(내역서!$O144)*$O144/$J144,0)))))</f>
+        <v/>
+      </c>
+      <c r="S144" s="20">
+        <f>IF($B144="","",IF(N($O144)=0,0,IF(OR($L144="감소",AND($L144="증가",$M144&lt;&gt;"Y")),IF(N($G144)=0,0,ROUND(N(내역서!$H144)*$O144/$G144,0)),IF(N($J144)=0,0,ROUND(N(내역서!$P144)*$O144/$J144,0)))))</f>
+        <v/>
+      </c>
+      <c r="T144" s="20">
+        <f>IF($B144="","",N($O144)-N($R144)-N($S144))</f>
+        <v/>
+      </c>
+      <c r="U144" s="20">
+        <f>IF($B144="","",ROUND(N($K144)*N($R144),0))</f>
+        <v/>
+      </c>
+      <c r="V144" s="20">
+        <f>IF($B144="","",ROUND(N($K144)*N($S144),0))</f>
+        <v/>
+      </c>
+      <c r="W144" s="20">
+        <f>IF($B144="","",N($P144)-N($U144)-N($V144))</f>
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="18">
@@ -11719,6 +15139,30 @@
         <f>IF($B145="","",IF($L145="감소","감소분 → 계약단가",IF(AND($M145="Y",OR($L145="증가",$L145="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L145="증가",IF(AND($N145&lt;&gt;"",$G145&gt;$N145),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L145="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R145" s="20">
+        <f>IF($B145="","",IF(N($O145)=0,0,IF(OR($L145="감소",AND($L145="증가",$M145&lt;&gt;"Y")),IF(N($G145)=0,0,ROUND(N(내역서!$G145)*$O145/$G145,0)),IF(N($J145)=0,0,ROUND(N(내역서!$O145)*$O145/$J145,0)))))</f>
+        <v/>
+      </c>
+      <c r="S145" s="20">
+        <f>IF($B145="","",IF(N($O145)=0,0,IF(OR($L145="감소",AND($L145="증가",$M145&lt;&gt;"Y")),IF(N($G145)=0,0,ROUND(N(내역서!$H145)*$O145/$G145,0)),IF(N($J145)=0,0,ROUND(N(내역서!$P145)*$O145/$J145,0)))))</f>
+        <v/>
+      </c>
+      <c r="T145" s="20">
+        <f>IF($B145="","",N($O145)-N($R145)-N($S145))</f>
+        <v/>
+      </c>
+      <c r="U145" s="20">
+        <f>IF($B145="","",ROUND(N($K145)*N($R145),0))</f>
+        <v/>
+      </c>
+      <c r="V145" s="20">
+        <f>IF($B145="","",ROUND(N($K145)*N($S145),0))</f>
+        <v/>
+      </c>
+      <c r="W145" s="20">
+        <f>IF($B145="","",N($P145)-N($U145)-N($V145))</f>
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="18">
@@ -11783,6 +15227,30 @@
         <f>IF($B146="","",IF($L146="감소","감소분 → 계약단가",IF(AND($M146="Y",OR($L146="증가",$L146="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L146="증가",IF(AND($N146&lt;&gt;"",$G146&gt;$N146),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L146="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R146" s="20">
+        <f>IF($B146="","",IF(N($O146)=0,0,IF(OR($L146="감소",AND($L146="증가",$M146&lt;&gt;"Y")),IF(N($G146)=0,0,ROUND(N(내역서!$G146)*$O146/$G146,0)),IF(N($J146)=0,0,ROUND(N(내역서!$O146)*$O146/$J146,0)))))</f>
+        <v/>
+      </c>
+      <c r="S146" s="20">
+        <f>IF($B146="","",IF(N($O146)=0,0,IF(OR($L146="감소",AND($L146="증가",$M146&lt;&gt;"Y")),IF(N($G146)=0,0,ROUND(N(내역서!$H146)*$O146/$G146,0)),IF(N($J146)=0,0,ROUND(N(내역서!$P146)*$O146/$J146,0)))))</f>
+        <v/>
+      </c>
+      <c r="T146" s="20">
+        <f>IF($B146="","",N($O146)-N($R146)-N($S146))</f>
+        <v/>
+      </c>
+      <c r="U146" s="20">
+        <f>IF($B146="","",ROUND(N($K146)*N($R146),0))</f>
+        <v/>
+      </c>
+      <c r="V146" s="20">
+        <f>IF($B146="","",ROUND(N($K146)*N($S146),0))</f>
+        <v/>
+      </c>
+      <c r="W146" s="20">
+        <f>IF($B146="","",N($P146)-N($U146)-N($V146))</f>
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="18">
@@ -11847,6 +15315,30 @@
         <f>IF($B147="","",IF($L147="감소","감소분 → 계약단가",IF(AND($M147="Y",OR($L147="증가",$L147="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L147="증가",IF(AND($N147&lt;&gt;"",$G147&gt;$N147),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L147="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R147" s="20">
+        <f>IF($B147="","",IF(N($O147)=0,0,IF(OR($L147="감소",AND($L147="증가",$M147&lt;&gt;"Y")),IF(N($G147)=0,0,ROUND(N(내역서!$G147)*$O147/$G147,0)),IF(N($J147)=0,0,ROUND(N(내역서!$O147)*$O147/$J147,0)))))</f>
+        <v/>
+      </c>
+      <c r="S147" s="20">
+        <f>IF($B147="","",IF(N($O147)=0,0,IF(OR($L147="감소",AND($L147="증가",$M147&lt;&gt;"Y")),IF(N($G147)=0,0,ROUND(N(내역서!$H147)*$O147/$G147,0)),IF(N($J147)=0,0,ROUND(N(내역서!$P147)*$O147/$J147,0)))))</f>
+        <v/>
+      </c>
+      <c r="T147" s="20">
+        <f>IF($B147="","",N($O147)-N($R147)-N($S147))</f>
+        <v/>
+      </c>
+      <c r="U147" s="20">
+        <f>IF($B147="","",ROUND(N($K147)*N($R147),0))</f>
+        <v/>
+      </c>
+      <c r="V147" s="20">
+        <f>IF($B147="","",ROUND(N($K147)*N($S147),0))</f>
+        <v/>
+      </c>
+      <c r="W147" s="20">
+        <f>IF($B147="","",N($P147)-N($U147)-N($V147))</f>
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="18">
@@ -11911,6 +15403,30 @@
         <f>IF($B148="","",IF($L148="감소","감소분 → 계약단가",IF(AND($M148="Y",OR($L148="증가",$L148="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L148="증가",IF(AND($N148&lt;&gt;"",$G148&gt;$N148),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L148="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R148" s="20">
+        <f>IF($B148="","",IF(N($O148)=0,0,IF(OR($L148="감소",AND($L148="증가",$M148&lt;&gt;"Y")),IF(N($G148)=0,0,ROUND(N(내역서!$G148)*$O148/$G148,0)),IF(N($J148)=0,0,ROUND(N(내역서!$O148)*$O148/$J148,0)))))</f>
+        <v/>
+      </c>
+      <c r="S148" s="20">
+        <f>IF($B148="","",IF(N($O148)=0,0,IF(OR($L148="감소",AND($L148="증가",$M148&lt;&gt;"Y")),IF(N($G148)=0,0,ROUND(N(내역서!$H148)*$O148/$G148,0)),IF(N($J148)=0,0,ROUND(N(내역서!$P148)*$O148/$J148,0)))))</f>
+        <v/>
+      </c>
+      <c r="T148" s="20">
+        <f>IF($B148="","",N($O148)-N($R148)-N($S148))</f>
+        <v/>
+      </c>
+      <c r="U148" s="20">
+        <f>IF($B148="","",ROUND(N($K148)*N($R148),0))</f>
+        <v/>
+      </c>
+      <c r="V148" s="20">
+        <f>IF($B148="","",ROUND(N($K148)*N($S148),0))</f>
+        <v/>
+      </c>
+      <c r="W148" s="20">
+        <f>IF($B148="","",N($P148)-N($U148)-N($V148))</f>
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="18">
@@ -11975,6 +15491,30 @@
         <f>IF($B149="","",IF($L149="감소","감소분 → 계약단가",IF(AND($M149="Y",OR($L149="증가",$L149="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L149="증가",IF(AND($N149&lt;&gt;"",$G149&gt;$N149),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L149="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R149" s="20">
+        <f>IF($B149="","",IF(N($O149)=0,0,IF(OR($L149="감소",AND($L149="증가",$M149&lt;&gt;"Y")),IF(N($G149)=0,0,ROUND(N(내역서!$G149)*$O149/$G149,0)),IF(N($J149)=0,0,ROUND(N(내역서!$O149)*$O149/$J149,0)))))</f>
+        <v/>
+      </c>
+      <c r="S149" s="20">
+        <f>IF($B149="","",IF(N($O149)=0,0,IF(OR($L149="감소",AND($L149="증가",$M149&lt;&gt;"Y")),IF(N($G149)=0,0,ROUND(N(내역서!$H149)*$O149/$G149,0)),IF(N($J149)=0,0,ROUND(N(내역서!$P149)*$O149/$J149,0)))))</f>
+        <v/>
+      </c>
+      <c r="T149" s="20">
+        <f>IF($B149="","",N($O149)-N($R149)-N($S149))</f>
+        <v/>
+      </c>
+      <c r="U149" s="20">
+        <f>IF($B149="","",ROUND(N($K149)*N($R149),0))</f>
+        <v/>
+      </c>
+      <c r="V149" s="20">
+        <f>IF($B149="","",ROUND(N($K149)*N($S149),0))</f>
+        <v/>
+      </c>
+      <c r="W149" s="20">
+        <f>IF($B149="","",N($P149)-N($U149)-N($V149))</f>
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="18">
@@ -12039,6 +15579,30 @@
         <f>IF($B150="","",IF($L150="감소","감소분 → 계약단가",IF(AND($M150="Y",OR($L150="증가",$L150="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L150="증가",IF(AND($N150&lt;&gt;"",$G150&gt;$N150),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L150="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R150" s="20">
+        <f>IF($B150="","",IF(N($O150)=0,0,IF(OR($L150="감소",AND($L150="증가",$M150&lt;&gt;"Y")),IF(N($G150)=0,0,ROUND(N(내역서!$G150)*$O150/$G150,0)),IF(N($J150)=0,0,ROUND(N(내역서!$O150)*$O150/$J150,0)))))</f>
+        <v/>
+      </c>
+      <c r="S150" s="20">
+        <f>IF($B150="","",IF(N($O150)=0,0,IF(OR($L150="감소",AND($L150="증가",$M150&lt;&gt;"Y")),IF(N($G150)=0,0,ROUND(N(내역서!$H150)*$O150/$G150,0)),IF(N($J150)=0,0,ROUND(N(내역서!$P150)*$O150/$J150,0)))))</f>
+        <v/>
+      </c>
+      <c r="T150" s="20">
+        <f>IF($B150="","",N($O150)-N($R150)-N($S150))</f>
+        <v/>
+      </c>
+      <c r="U150" s="20">
+        <f>IF($B150="","",ROUND(N($K150)*N($R150),0))</f>
+        <v/>
+      </c>
+      <c r="V150" s="20">
+        <f>IF($B150="","",ROUND(N($K150)*N($S150),0))</f>
+        <v/>
+      </c>
+      <c r="W150" s="20">
+        <f>IF($B150="","",N($P150)-N($U150)-N($V150))</f>
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="18">
@@ -12103,6 +15667,30 @@
         <f>IF($B151="","",IF($L151="감소","감소분 → 계약단가",IF(AND($M151="Y",OR($L151="증가",$L151="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L151="증가",IF(AND($N151&lt;&gt;"",$G151&gt;$N151),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L151="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R151" s="20">
+        <f>IF($B151="","",IF(N($O151)=0,0,IF(OR($L151="감소",AND($L151="증가",$M151&lt;&gt;"Y")),IF(N($G151)=0,0,ROUND(N(내역서!$G151)*$O151/$G151,0)),IF(N($J151)=0,0,ROUND(N(내역서!$O151)*$O151/$J151,0)))))</f>
+        <v/>
+      </c>
+      <c r="S151" s="20">
+        <f>IF($B151="","",IF(N($O151)=0,0,IF(OR($L151="감소",AND($L151="증가",$M151&lt;&gt;"Y")),IF(N($G151)=0,0,ROUND(N(내역서!$H151)*$O151/$G151,0)),IF(N($J151)=0,0,ROUND(N(내역서!$P151)*$O151/$J151,0)))))</f>
+        <v/>
+      </c>
+      <c r="T151" s="20">
+        <f>IF($B151="","",N($O151)-N($R151)-N($S151))</f>
+        <v/>
+      </c>
+      <c r="U151" s="20">
+        <f>IF($B151="","",ROUND(N($K151)*N($R151),0))</f>
+        <v/>
+      </c>
+      <c r="V151" s="20">
+        <f>IF($B151="","",ROUND(N($K151)*N($S151),0))</f>
+        <v/>
+      </c>
+      <c r="W151" s="20">
+        <f>IF($B151="","",N($P151)-N($U151)-N($V151))</f>
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="18">
@@ -12167,6 +15755,30 @@
         <f>IF($B152="","",IF($L152="감소","감소분 → 계약단가",IF(AND($M152="Y",OR($L152="증가",$L152="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L152="증가",IF(AND($N152&lt;&gt;"",$G152&gt;$N152),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L152="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R152" s="20">
+        <f>IF($B152="","",IF(N($O152)=0,0,IF(OR($L152="감소",AND($L152="증가",$M152&lt;&gt;"Y")),IF(N($G152)=0,0,ROUND(N(내역서!$G152)*$O152/$G152,0)),IF(N($J152)=0,0,ROUND(N(내역서!$O152)*$O152/$J152,0)))))</f>
+        <v/>
+      </c>
+      <c r="S152" s="20">
+        <f>IF($B152="","",IF(N($O152)=0,0,IF(OR($L152="감소",AND($L152="증가",$M152&lt;&gt;"Y")),IF(N($G152)=0,0,ROUND(N(내역서!$H152)*$O152/$G152,0)),IF(N($J152)=0,0,ROUND(N(내역서!$P152)*$O152/$J152,0)))))</f>
+        <v/>
+      </c>
+      <c r="T152" s="20">
+        <f>IF($B152="","",N($O152)-N($R152)-N($S152))</f>
+        <v/>
+      </c>
+      <c r="U152" s="20">
+        <f>IF($B152="","",ROUND(N($K152)*N($R152),0))</f>
+        <v/>
+      </c>
+      <c r="V152" s="20">
+        <f>IF($B152="","",ROUND(N($K152)*N($S152),0))</f>
+        <v/>
+      </c>
+      <c r="W152" s="20">
+        <f>IF($B152="","",N($P152)-N($U152)-N($V152))</f>
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="18">
@@ -12231,6 +15843,30 @@
         <f>IF($B153="","",IF($L153="감소","감소분 → 계약단가",IF(AND($M153="Y",OR($L153="증가",$L153="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L153="증가",IF(AND($N153&lt;&gt;"",$G153&gt;$N153),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L153="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R153" s="20">
+        <f>IF($B153="","",IF(N($O153)=0,0,IF(OR($L153="감소",AND($L153="증가",$M153&lt;&gt;"Y")),IF(N($G153)=0,0,ROUND(N(내역서!$G153)*$O153/$G153,0)),IF(N($J153)=0,0,ROUND(N(내역서!$O153)*$O153/$J153,0)))))</f>
+        <v/>
+      </c>
+      <c r="S153" s="20">
+        <f>IF($B153="","",IF(N($O153)=0,0,IF(OR($L153="감소",AND($L153="증가",$M153&lt;&gt;"Y")),IF(N($G153)=0,0,ROUND(N(내역서!$H153)*$O153/$G153,0)),IF(N($J153)=0,0,ROUND(N(내역서!$P153)*$O153/$J153,0)))))</f>
+        <v/>
+      </c>
+      <c r="T153" s="20">
+        <f>IF($B153="","",N($O153)-N($R153)-N($S153))</f>
+        <v/>
+      </c>
+      <c r="U153" s="20">
+        <f>IF($B153="","",ROUND(N($K153)*N($R153),0))</f>
+        <v/>
+      </c>
+      <c r="V153" s="20">
+        <f>IF($B153="","",ROUND(N($K153)*N($S153),0))</f>
+        <v/>
+      </c>
+      <c r="W153" s="20">
+        <f>IF($B153="","",N($P153)-N($U153)-N($V153))</f>
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="18">
@@ -12295,6 +15931,30 @@
         <f>IF($B154="","",IF($L154="감소","감소분 → 계약단가",IF(AND($M154="Y",OR($L154="증가",$L154="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L154="증가",IF(AND($N154&lt;&gt;"",$G154&gt;$N154),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L154="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R154" s="20">
+        <f>IF($B154="","",IF(N($O154)=0,0,IF(OR($L154="감소",AND($L154="증가",$M154&lt;&gt;"Y")),IF(N($G154)=0,0,ROUND(N(내역서!$G154)*$O154/$G154,0)),IF(N($J154)=0,0,ROUND(N(내역서!$O154)*$O154/$J154,0)))))</f>
+        <v/>
+      </c>
+      <c r="S154" s="20">
+        <f>IF($B154="","",IF(N($O154)=0,0,IF(OR($L154="감소",AND($L154="증가",$M154&lt;&gt;"Y")),IF(N($G154)=0,0,ROUND(N(내역서!$H154)*$O154/$G154,0)),IF(N($J154)=0,0,ROUND(N(내역서!$P154)*$O154/$J154,0)))))</f>
+        <v/>
+      </c>
+      <c r="T154" s="20">
+        <f>IF($B154="","",N($O154)-N($R154)-N($S154))</f>
+        <v/>
+      </c>
+      <c r="U154" s="20">
+        <f>IF($B154="","",ROUND(N($K154)*N($R154),0))</f>
+        <v/>
+      </c>
+      <c r="V154" s="20">
+        <f>IF($B154="","",ROUND(N($K154)*N($S154),0))</f>
+        <v/>
+      </c>
+      <c r="W154" s="20">
+        <f>IF($B154="","",N($P154)-N($U154)-N($V154))</f>
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="18">
@@ -12359,6 +16019,30 @@
         <f>IF($B155="","",IF($L155="감소","감소분 → 계약단가",IF(AND($M155="Y",OR($L155="증가",$L155="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L155="증가",IF(AND($N155&lt;&gt;"",$G155&gt;$N155),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L155="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R155" s="20">
+        <f>IF($B155="","",IF(N($O155)=0,0,IF(OR($L155="감소",AND($L155="증가",$M155&lt;&gt;"Y")),IF(N($G155)=0,0,ROUND(N(내역서!$G155)*$O155/$G155,0)),IF(N($J155)=0,0,ROUND(N(내역서!$O155)*$O155/$J155,0)))))</f>
+        <v/>
+      </c>
+      <c r="S155" s="20">
+        <f>IF($B155="","",IF(N($O155)=0,0,IF(OR($L155="감소",AND($L155="증가",$M155&lt;&gt;"Y")),IF(N($G155)=0,0,ROUND(N(내역서!$H155)*$O155/$G155,0)),IF(N($J155)=0,0,ROUND(N(내역서!$P155)*$O155/$J155,0)))))</f>
+        <v/>
+      </c>
+      <c r="T155" s="20">
+        <f>IF($B155="","",N($O155)-N($R155)-N($S155))</f>
+        <v/>
+      </c>
+      <c r="U155" s="20">
+        <f>IF($B155="","",ROUND(N($K155)*N($R155),0))</f>
+        <v/>
+      </c>
+      <c r="V155" s="20">
+        <f>IF($B155="","",ROUND(N($K155)*N($S155),0))</f>
+        <v/>
+      </c>
+      <c r="W155" s="20">
+        <f>IF($B155="","",N($P155)-N($U155)-N($V155))</f>
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="18">
@@ -12423,6 +16107,30 @@
         <f>IF($B156="","",IF($L156="감소","감소분 → 계약단가",IF(AND($M156="Y",OR($L156="증가",$L156="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L156="증가",IF(AND($N156&lt;&gt;"",$G156&gt;$N156),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L156="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R156" s="20">
+        <f>IF($B156="","",IF(N($O156)=0,0,IF(OR($L156="감소",AND($L156="증가",$M156&lt;&gt;"Y")),IF(N($G156)=0,0,ROUND(N(내역서!$G156)*$O156/$G156,0)),IF(N($J156)=0,0,ROUND(N(내역서!$O156)*$O156/$J156,0)))))</f>
+        <v/>
+      </c>
+      <c r="S156" s="20">
+        <f>IF($B156="","",IF(N($O156)=0,0,IF(OR($L156="감소",AND($L156="증가",$M156&lt;&gt;"Y")),IF(N($G156)=0,0,ROUND(N(내역서!$H156)*$O156/$G156,0)),IF(N($J156)=0,0,ROUND(N(내역서!$P156)*$O156/$J156,0)))))</f>
+        <v/>
+      </c>
+      <c r="T156" s="20">
+        <f>IF($B156="","",N($O156)-N($R156)-N($S156))</f>
+        <v/>
+      </c>
+      <c r="U156" s="20">
+        <f>IF($B156="","",ROUND(N($K156)*N($R156),0))</f>
+        <v/>
+      </c>
+      <c r="V156" s="20">
+        <f>IF($B156="","",ROUND(N($K156)*N($S156),0))</f>
+        <v/>
+      </c>
+      <c r="W156" s="20">
+        <f>IF($B156="","",N($P156)-N($U156)-N($V156))</f>
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="18">
@@ -12487,6 +16195,30 @@
         <f>IF($B157="","",IF($L157="감소","감소분 → 계약단가",IF(AND($M157="Y",OR($L157="증가",$L157="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L157="증가",IF(AND($N157&lt;&gt;"",$G157&gt;$N157),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L157="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R157" s="20">
+        <f>IF($B157="","",IF(N($O157)=0,0,IF(OR($L157="감소",AND($L157="증가",$M157&lt;&gt;"Y")),IF(N($G157)=0,0,ROUND(N(내역서!$G157)*$O157/$G157,0)),IF(N($J157)=0,0,ROUND(N(내역서!$O157)*$O157/$J157,0)))))</f>
+        <v/>
+      </c>
+      <c r="S157" s="20">
+        <f>IF($B157="","",IF(N($O157)=0,0,IF(OR($L157="감소",AND($L157="증가",$M157&lt;&gt;"Y")),IF(N($G157)=0,0,ROUND(N(내역서!$H157)*$O157/$G157,0)),IF(N($J157)=0,0,ROUND(N(내역서!$P157)*$O157/$J157,0)))))</f>
+        <v/>
+      </c>
+      <c r="T157" s="20">
+        <f>IF($B157="","",N($O157)-N($R157)-N($S157))</f>
+        <v/>
+      </c>
+      <c r="U157" s="20">
+        <f>IF($B157="","",ROUND(N($K157)*N($R157),0))</f>
+        <v/>
+      </c>
+      <c r="V157" s="20">
+        <f>IF($B157="","",ROUND(N($K157)*N($S157),0))</f>
+        <v/>
+      </c>
+      <c r="W157" s="20">
+        <f>IF($B157="","",N($P157)-N($U157)-N($V157))</f>
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="18">
@@ -12551,6 +16283,30 @@
         <f>IF($B158="","",IF($L158="감소","감소분 → 계약단가",IF(AND($M158="Y",OR($L158="증가",$L158="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L158="증가",IF(AND($N158&lt;&gt;"",$G158&gt;$N158),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L158="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R158" s="20">
+        <f>IF($B158="","",IF(N($O158)=0,0,IF(OR($L158="감소",AND($L158="증가",$M158&lt;&gt;"Y")),IF(N($G158)=0,0,ROUND(N(내역서!$G158)*$O158/$G158,0)),IF(N($J158)=0,0,ROUND(N(내역서!$O158)*$O158/$J158,0)))))</f>
+        <v/>
+      </c>
+      <c r="S158" s="20">
+        <f>IF($B158="","",IF(N($O158)=0,0,IF(OR($L158="감소",AND($L158="증가",$M158&lt;&gt;"Y")),IF(N($G158)=0,0,ROUND(N(내역서!$H158)*$O158/$G158,0)),IF(N($J158)=0,0,ROUND(N(내역서!$P158)*$O158/$J158,0)))))</f>
+        <v/>
+      </c>
+      <c r="T158" s="20">
+        <f>IF($B158="","",N($O158)-N($R158)-N($S158))</f>
+        <v/>
+      </c>
+      <c r="U158" s="20">
+        <f>IF($B158="","",ROUND(N($K158)*N($R158),0))</f>
+        <v/>
+      </c>
+      <c r="V158" s="20">
+        <f>IF($B158="","",ROUND(N($K158)*N($S158),0))</f>
+        <v/>
+      </c>
+      <c r="W158" s="20">
+        <f>IF($B158="","",N($P158)-N($U158)-N($V158))</f>
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="18">
@@ -12615,6 +16371,30 @@
         <f>IF($B159="","",IF($L159="감소","감소분 → 계약단가",IF(AND($M159="Y",OR($L159="증가",$L159="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L159="증가",IF(AND($N159&lt;&gt;"",$G159&gt;$N159),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L159="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R159" s="20">
+        <f>IF($B159="","",IF(N($O159)=0,0,IF(OR($L159="감소",AND($L159="증가",$M159&lt;&gt;"Y")),IF(N($G159)=0,0,ROUND(N(내역서!$G159)*$O159/$G159,0)),IF(N($J159)=0,0,ROUND(N(내역서!$O159)*$O159/$J159,0)))))</f>
+        <v/>
+      </c>
+      <c r="S159" s="20">
+        <f>IF($B159="","",IF(N($O159)=0,0,IF(OR($L159="감소",AND($L159="증가",$M159&lt;&gt;"Y")),IF(N($G159)=0,0,ROUND(N(내역서!$H159)*$O159/$G159,0)),IF(N($J159)=0,0,ROUND(N(내역서!$P159)*$O159/$J159,0)))))</f>
+        <v/>
+      </c>
+      <c r="T159" s="20">
+        <f>IF($B159="","",N($O159)-N($R159)-N($S159))</f>
+        <v/>
+      </c>
+      <c r="U159" s="20">
+        <f>IF($B159="","",ROUND(N($K159)*N($R159),0))</f>
+        <v/>
+      </c>
+      <c r="V159" s="20">
+        <f>IF($B159="","",ROUND(N($K159)*N($S159),0))</f>
+        <v/>
+      </c>
+      <c r="W159" s="20">
+        <f>IF($B159="","",N($P159)-N($U159)-N($V159))</f>
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="18">
@@ -12679,6 +16459,30 @@
         <f>IF($B160="","",IF($L160="감소","감소분 → 계약단가",IF(AND($M160="Y",OR($L160="증가",$L160="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L160="증가",IF(AND($N160&lt;&gt;"",$G160&gt;$N160),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L160="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R160" s="20">
+        <f>IF($B160="","",IF(N($O160)=0,0,IF(OR($L160="감소",AND($L160="증가",$M160&lt;&gt;"Y")),IF(N($G160)=0,0,ROUND(N(내역서!$G160)*$O160/$G160,0)),IF(N($J160)=0,0,ROUND(N(내역서!$O160)*$O160/$J160,0)))))</f>
+        <v/>
+      </c>
+      <c r="S160" s="20">
+        <f>IF($B160="","",IF(N($O160)=0,0,IF(OR($L160="감소",AND($L160="증가",$M160&lt;&gt;"Y")),IF(N($G160)=0,0,ROUND(N(내역서!$H160)*$O160/$G160,0)),IF(N($J160)=0,0,ROUND(N(내역서!$P160)*$O160/$J160,0)))))</f>
+        <v/>
+      </c>
+      <c r="T160" s="20">
+        <f>IF($B160="","",N($O160)-N($R160)-N($S160))</f>
+        <v/>
+      </c>
+      <c r="U160" s="20">
+        <f>IF($B160="","",ROUND(N($K160)*N($R160),0))</f>
+        <v/>
+      </c>
+      <c r="V160" s="20">
+        <f>IF($B160="","",ROUND(N($K160)*N($S160),0))</f>
+        <v/>
+      </c>
+      <c r="W160" s="20">
+        <f>IF($B160="","",N($P160)-N($U160)-N($V160))</f>
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="18">
@@ -12743,6 +16547,30 @@
         <f>IF($B161="","",IF($L161="감소","감소분 → 계약단가",IF(AND($M161="Y",OR($L161="증가",$L161="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L161="증가",IF(AND($N161&lt;&gt;"",$G161&gt;$N161),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L161="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R161" s="20">
+        <f>IF($B161="","",IF(N($O161)=0,0,IF(OR($L161="감소",AND($L161="증가",$M161&lt;&gt;"Y")),IF(N($G161)=0,0,ROUND(N(내역서!$G161)*$O161/$G161,0)),IF(N($J161)=0,0,ROUND(N(내역서!$O161)*$O161/$J161,0)))))</f>
+        <v/>
+      </c>
+      <c r="S161" s="20">
+        <f>IF($B161="","",IF(N($O161)=0,0,IF(OR($L161="감소",AND($L161="증가",$M161&lt;&gt;"Y")),IF(N($G161)=0,0,ROUND(N(내역서!$H161)*$O161/$G161,0)),IF(N($J161)=0,0,ROUND(N(내역서!$P161)*$O161/$J161,0)))))</f>
+        <v/>
+      </c>
+      <c r="T161" s="20">
+        <f>IF($B161="","",N($O161)-N($R161)-N($S161))</f>
+        <v/>
+      </c>
+      <c r="U161" s="20">
+        <f>IF($B161="","",ROUND(N($K161)*N($R161),0))</f>
+        <v/>
+      </c>
+      <c r="V161" s="20">
+        <f>IF($B161="","",ROUND(N($K161)*N($S161),0))</f>
+        <v/>
+      </c>
+      <c r="W161" s="20">
+        <f>IF($B161="","",N($P161)-N($U161)-N($V161))</f>
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="18">
@@ -12807,6 +16635,30 @@
         <f>IF($B162="","",IF($L162="감소","감소분 → 계약단가",IF(AND($M162="Y",OR($L162="증가",$L162="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L162="증가",IF(AND($N162&lt;&gt;"",$G162&gt;$N162),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L162="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R162" s="20">
+        <f>IF($B162="","",IF(N($O162)=0,0,IF(OR($L162="감소",AND($L162="증가",$M162&lt;&gt;"Y")),IF(N($G162)=0,0,ROUND(N(내역서!$G162)*$O162/$G162,0)),IF(N($J162)=0,0,ROUND(N(내역서!$O162)*$O162/$J162,0)))))</f>
+        <v/>
+      </c>
+      <c r="S162" s="20">
+        <f>IF($B162="","",IF(N($O162)=0,0,IF(OR($L162="감소",AND($L162="증가",$M162&lt;&gt;"Y")),IF(N($G162)=0,0,ROUND(N(내역서!$H162)*$O162/$G162,0)),IF(N($J162)=0,0,ROUND(N(내역서!$P162)*$O162/$J162,0)))))</f>
+        <v/>
+      </c>
+      <c r="T162" s="20">
+        <f>IF($B162="","",N($O162)-N($R162)-N($S162))</f>
+        <v/>
+      </c>
+      <c r="U162" s="20">
+        <f>IF($B162="","",ROUND(N($K162)*N($R162),0))</f>
+        <v/>
+      </c>
+      <c r="V162" s="20">
+        <f>IF($B162="","",ROUND(N($K162)*N($S162),0))</f>
+        <v/>
+      </c>
+      <c r="W162" s="20">
+        <f>IF($B162="","",N($P162)-N($U162)-N($V162))</f>
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="18">
@@ -12871,6 +16723,30 @@
         <f>IF($B163="","",IF($L163="감소","감소분 → 계약단가",IF(AND($M163="Y",OR($L163="증가",$L163="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L163="증가",IF(AND($N163&lt;&gt;"",$G163&gt;$N163),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L163="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R163" s="20">
+        <f>IF($B163="","",IF(N($O163)=0,0,IF(OR($L163="감소",AND($L163="증가",$M163&lt;&gt;"Y")),IF(N($G163)=0,0,ROUND(N(내역서!$G163)*$O163/$G163,0)),IF(N($J163)=0,0,ROUND(N(내역서!$O163)*$O163/$J163,0)))))</f>
+        <v/>
+      </c>
+      <c r="S163" s="20">
+        <f>IF($B163="","",IF(N($O163)=0,0,IF(OR($L163="감소",AND($L163="증가",$M163&lt;&gt;"Y")),IF(N($G163)=0,0,ROUND(N(내역서!$H163)*$O163/$G163,0)),IF(N($J163)=0,0,ROUND(N(내역서!$P163)*$O163/$J163,0)))))</f>
+        <v/>
+      </c>
+      <c r="T163" s="20">
+        <f>IF($B163="","",N($O163)-N($R163)-N($S163))</f>
+        <v/>
+      </c>
+      <c r="U163" s="20">
+        <f>IF($B163="","",ROUND(N($K163)*N($R163),0))</f>
+        <v/>
+      </c>
+      <c r="V163" s="20">
+        <f>IF($B163="","",ROUND(N($K163)*N($S163),0))</f>
+        <v/>
+      </c>
+      <c r="W163" s="20">
+        <f>IF($B163="","",N($P163)-N($U163)-N($V163))</f>
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="18">
@@ -12935,6 +16811,30 @@
         <f>IF($B164="","",IF($L164="감소","감소분 → 계약단가",IF(AND($M164="Y",OR($L164="증가",$L164="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L164="증가",IF(AND($N164&lt;&gt;"",$G164&gt;$N164),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L164="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R164" s="20">
+        <f>IF($B164="","",IF(N($O164)=0,0,IF(OR($L164="감소",AND($L164="증가",$M164&lt;&gt;"Y")),IF(N($G164)=0,0,ROUND(N(내역서!$G164)*$O164/$G164,0)),IF(N($J164)=0,0,ROUND(N(내역서!$O164)*$O164/$J164,0)))))</f>
+        <v/>
+      </c>
+      <c r="S164" s="20">
+        <f>IF($B164="","",IF(N($O164)=0,0,IF(OR($L164="감소",AND($L164="증가",$M164&lt;&gt;"Y")),IF(N($G164)=0,0,ROUND(N(내역서!$H164)*$O164/$G164,0)),IF(N($J164)=0,0,ROUND(N(내역서!$P164)*$O164/$J164,0)))))</f>
+        <v/>
+      </c>
+      <c r="T164" s="20">
+        <f>IF($B164="","",N($O164)-N($R164)-N($S164))</f>
+        <v/>
+      </c>
+      <c r="U164" s="20">
+        <f>IF($B164="","",ROUND(N($K164)*N($R164),0))</f>
+        <v/>
+      </c>
+      <c r="V164" s="20">
+        <f>IF($B164="","",ROUND(N($K164)*N($S164),0))</f>
+        <v/>
+      </c>
+      <c r="W164" s="20">
+        <f>IF($B164="","",N($P164)-N($U164)-N($V164))</f>
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="18">
@@ -12999,6 +16899,30 @@
         <f>IF($B165="","",IF($L165="감소","감소분 → 계약단가",IF(AND($M165="Y",OR($L165="증가",$L165="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L165="증가",IF(AND($N165&lt;&gt;"",$G165&gt;$N165),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L165="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R165" s="20">
+        <f>IF($B165="","",IF(N($O165)=0,0,IF(OR($L165="감소",AND($L165="증가",$M165&lt;&gt;"Y")),IF(N($G165)=0,0,ROUND(N(내역서!$G165)*$O165/$G165,0)),IF(N($J165)=0,0,ROUND(N(내역서!$O165)*$O165/$J165,0)))))</f>
+        <v/>
+      </c>
+      <c r="S165" s="20">
+        <f>IF($B165="","",IF(N($O165)=0,0,IF(OR($L165="감소",AND($L165="증가",$M165&lt;&gt;"Y")),IF(N($G165)=0,0,ROUND(N(내역서!$H165)*$O165/$G165,0)),IF(N($J165)=0,0,ROUND(N(내역서!$P165)*$O165/$J165,0)))))</f>
+        <v/>
+      </c>
+      <c r="T165" s="20">
+        <f>IF($B165="","",N($O165)-N($R165)-N($S165))</f>
+        <v/>
+      </c>
+      <c r="U165" s="20">
+        <f>IF($B165="","",ROUND(N($K165)*N($R165),0))</f>
+        <v/>
+      </c>
+      <c r="V165" s="20">
+        <f>IF($B165="","",ROUND(N($K165)*N($S165),0))</f>
+        <v/>
+      </c>
+      <c r="W165" s="20">
+        <f>IF($B165="","",N($P165)-N($U165)-N($V165))</f>
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="18">
@@ -13063,6 +16987,30 @@
         <f>IF($B166="","",IF($L166="감소","감소분 → 계약단가",IF(AND($M166="Y",OR($L166="증가",$L166="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L166="증가",IF(AND($N166&lt;&gt;"",$G166&gt;$N166),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L166="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R166" s="20">
+        <f>IF($B166="","",IF(N($O166)=0,0,IF(OR($L166="감소",AND($L166="증가",$M166&lt;&gt;"Y")),IF(N($G166)=0,0,ROUND(N(내역서!$G166)*$O166/$G166,0)),IF(N($J166)=0,0,ROUND(N(내역서!$O166)*$O166/$J166,0)))))</f>
+        <v/>
+      </c>
+      <c r="S166" s="20">
+        <f>IF($B166="","",IF(N($O166)=0,0,IF(OR($L166="감소",AND($L166="증가",$M166&lt;&gt;"Y")),IF(N($G166)=0,0,ROUND(N(내역서!$H166)*$O166/$G166,0)),IF(N($J166)=0,0,ROUND(N(내역서!$P166)*$O166/$J166,0)))))</f>
+        <v/>
+      </c>
+      <c r="T166" s="20">
+        <f>IF($B166="","",N($O166)-N($R166)-N($S166))</f>
+        <v/>
+      </c>
+      <c r="U166" s="20">
+        <f>IF($B166="","",ROUND(N($K166)*N($R166),0))</f>
+        <v/>
+      </c>
+      <c r="V166" s="20">
+        <f>IF($B166="","",ROUND(N($K166)*N($S166),0))</f>
+        <v/>
+      </c>
+      <c r="W166" s="20">
+        <f>IF($B166="","",N($P166)-N($U166)-N($V166))</f>
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="18">
@@ -13127,6 +17075,30 @@
         <f>IF($B167="","",IF($L167="감소","감소분 → 계약단가",IF(AND($M167="Y",OR($L167="증가",$L167="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L167="증가",IF(AND($N167&lt;&gt;"",$G167&gt;$N167),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L167="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R167" s="20">
+        <f>IF($B167="","",IF(N($O167)=0,0,IF(OR($L167="감소",AND($L167="증가",$M167&lt;&gt;"Y")),IF(N($G167)=0,0,ROUND(N(내역서!$G167)*$O167/$G167,0)),IF(N($J167)=0,0,ROUND(N(내역서!$O167)*$O167/$J167,0)))))</f>
+        <v/>
+      </c>
+      <c r="S167" s="20">
+        <f>IF($B167="","",IF(N($O167)=0,0,IF(OR($L167="감소",AND($L167="증가",$M167&lt;&gt;"Y")),IF(N($G167)=0,0,ROUND(N(내역서!$H167)*$O167/$G167,0)),IF(N($J167)=0,0,ROUND(N(내역서!$P167)*$O167/$J167,0)))))</f>
+        <v/>
+      </c>
+      <c r="T167" s="20">
+        <f>IF($B167="","",N($O167)-N($R167)-N($S167))</f>
+        <v/>
+      </c>
+      <c r="U167" s="20">
+        <f>IF($B167="","",ROUND(N($K167)*N($R167),0))</f>
+        <v/>
+      </c>
+      <c r="V167" s="20">
+        <f>IF($B167="","",ROUND(N($K167)*N($S167),0))</f>
+        <v/>
+      </c>
+      <c r="W167" s="20">
+        <f>IF($B167="","",N($P167)-N($U167)-N($V167))</f>
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="18">
@@ -13191,6 +17163,30 @@
         <f>IF($B168="","",IF($L168="감소","감소분 → 계약단가",IF(AND($M168="Y",OR($L168="증가",$L168="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L168="증가",IF(AND($N168&lt;&gt;"",$G168&gt;$N168),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L168="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R168" s="20">
+        <f>IF($B168="","",IF(N($O168)=0,0,IF(OR($L168="감소",AND($L168="증가",$M168&lt;&gt;"Y")),IF(N($G168)=0,0,ROUND(N(내역서!$G168)*$O168/$G168,0)),IF(N($J168)=0,0,ROUND(N(내역서!$O168)*$O168/$J168,0)))))</f>
+        <v/>
+      </c>
+      <c r="S168" s="20">
+        <f>IF($B168="","",IF(N($O168)=0,0,IF(OR($L168="감소",AND($L168="증가",$M168&lt;&gt;"Y")),IF(N($G168)=0,0,ROUND(N(내역서!$H168)*$O168/$G168,0)),IF(N($J168)=0,0,ROUND(N(내역서!$P168)*$O168/$J168,0)))))</f>
+        <v/>
+      </c>
+      <c r="T168" s="20">
+        <f>IF($B168="","",N($O168)-N($R168)-N($S168))</f>
+        <v/>
+      </c>
+      <c r="U168" s="20">
+        <f>IF($B168="","",ROUND(N($K168)*N($R168),0))</f>
+        <v/>
+      </c>
+      <c r="V168" s="20">
+        <f>IF($B168="","",ROUND(N($K168)*N($S168),0))</f>
+        <v/>
+      </c>
+      <c r="W168" s="20">
+        <f>IF($B168="","",N($P168)-N($U168)-N($V168))</f>
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="18">
@@ -13255,6 +17251,30 @@
         <f>IF($B169="","",IF($L169="감소","감소분 → 계약단가",IF(AND($M169="Y",OR($L169="증가",$L169="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L169="증가",IF(AND($N169&lt;&gt;"",$G169&gt;$N169),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L169="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R169" s="20">
+        <f>IF($B169="","",IF(N($O169)=0,0,IF(OR($L169="감소",AND($L169="증가",$M169&lt;&gt;"Y")),IF(N($G169)=0,0,ROUND(N(내역서!$G169)*$O169/$G169,0)),IF(N($J169)=0,0,ROUND(N(내역서!$O169)*$O169/$J169,0)))))</f>
+        <v/>
+      </c>
+      <c r="S169" s="20">
+        <f>IF($B169="","",IF(N($O169)=0,0,IF(OR($L169="감소",AND($L169="증가",$M169&lt;&gt;"Y")),IF(N($G169)=0,0,ROUND(N(내역서!$H169)*$O169/$G169,0)),IF(N($J169)=0,0,ROUND(N(내역서!$P169)*$O169/$J169,0)))))</f>
+        <v/>
+      </c>
+      <c r="T169" s="20">
+        <f>IF($B169="","",N($O169)-N($R169)-N($S169))</f>
+        <v/>
+      </c>
+      <c r="U169" s="20">
+        <f>IF($B169="","",ROUND(N($K169)*N($R169),0))</f>
+        <v/>
+      </c>
+      <c r="V169" s="20">
+        <f>IF($B169="","",ROUND(N($K169)*N($S169),0))</f>
+        <v/>
+      </c>
+      <c r="W169" s="20">
+        <f>IF($B169="","",N($P169)-N($U169)-N($V169))</f>
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="18">
@@ -13319,6 +17339,30 @@
         <f>IF($B170="","",IF($L170="감소","감소분 → 계약단가",IF(AND($M170="Y",OR($L170="증가",$L170="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L170="증가",IF(AND($N170&lt;&gt;"",$G170&gt;$N170),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L170="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R170" s="20">
+        <f>IF($B170="","",IF(N($O170)=0,0,IF(OR($L170="감소",AND($L170="증가",$M170&lt;&gt;"Y")),IF(N($G170)=0,0,ROUND(N(내역서!$G170)*$O170/$G170,0)),IF(N($J170)=0,0,ROUND(N(내역서!$O170)*$O170/$J170,0)))))</f>
+        <v/>
+      </c>
+      <c r="S170" s="20">
+        <f>IF($B170="","",IF(N($O170)=0,0,IF(OR($L170="감소",AND($L170="증가",$M170&lt;&gt;"Y")),IF(N($G170)=0,0,ROUND(N(내역서!$H170)*$O170/$G170,0)),IF(N($J170)=0,0,ROUND(N(내역서!$P170)*$O170/$J170,0)))))</f>
+        <v/>
+      </c>
+      <c r="T170" s="20">
+        <f>IF($B170="","",N($O170)-N($R170)-N($S170))</f>
+        <v/>
+      </c>
+      <c r="U170" s="20">
+        <f>IF($B170="","",ROUND(N($K170)*N($R170),0))</f>
+        <v/>
+      </c>
+      <c r="V170" s="20">
+        <f>IF($B170="","",ROUND(N($K170)*N($S170),0))</f>
+        <v/>
+      </c>
+      <c r="W170" s="20">
+        <f>IF($B170="","",N($P170)-N($U170)-N($V170))</f>
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="18">
@@ -13383,6 +17427,30 @@
         <f>IF($B171="","",IF($L171="감소","감소분 → 계약단가",IF(AND($M171="Y",OR($L171="증가",$L171="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L171="증가",IF(AND($N171&lt;&gt;"",$G171&gt;$N171),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L171="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R171" s="20">
+        <f>IF($B171="","",IF(N($O171)=0,0,IF(OR($L171="감소",AND($L171="증가",$M171&lt;&gt;"Y")),IF(N($G171)=0,0,ROUND(N(내역서!$G171)*$O171/$G171,0)),IF(N($J171)=0,0,ROUND(N(내역서!$O171)*$O171/$J171,0)))))</f>
+        <v/>
+      </c>
+      <c r="S171" s="20">
+        <f>IF($B171="","",IF(N($O171)=0,0,IF(OR($L171="감소",AND($L171="증가",$M171&lt;&gt;"Y")),IF(N($G171)=0,0,ROUND(N(내역서!$H171)*$O171/$G171,0)),IF(N($J171)=0,0,ROUND(N(내역서!$P171)*$O171/$J171,0)))))</f>
+        <v/>
+      </c>
+      <c r="T171" s="20">
+        <f>IF($B171="","",N($O171)-N($R171)-N($S171))</f>
+        <v/>
+      </c>
+      <c r="U171" s="20">
+        <f>IF($B171="","",ROUND(N($K171)*N($R171),0))</f>
+        <v/>
+      </c>
+      <c r="V171" s="20">
+        <f>IF($B171="","",ROUND(N($K171)*N($S171),0))</f>
+        <v/>
+      </c>
+      <c r="W171" s="20">
+        <f>IF($B171="","",N($P171)-N($U171)-N($V171))</f>
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="18">
@@ -13447,6 +17515,30 @@
         <f>IF($B172="","",IF($L172="감소","감소분 → 계약단가",IF(AND($M172="Y",OR($L172="증가",$L172="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L172="증가",IF(AND($N172&lt;&gt;"",$G172&gt;$N172),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L172="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R172" s="20">
+        <f>IF($B172="","",IF(N($O172)=0,0,IF(OR($L172="감소",AND($L172="증가",$M172&lt;&gt;"Y")),IF(N($G172)=0,0,ROUND(N(내역서!$G172)*$O172/$G172,0)),IF(N($J172)=0,0,ROUND(N(내역서!$O172)*$O172/$J172,0)))))</f>
+        <v/>
+      </c>
+      <c r="S172" s="20">
+        <f>IF($B172="","",IF(N($O172)=0,0,IF(OR($L172="감소",AND($L172="증가",$M172&lt;&gt;"Y")),IF(N($G172)=0,0,ROUND(N(내역서!$H172)*$O172/$G172,0)),IF(N($J172)=0,0,ROUND(N(내역서!$P172)*$O172/$J172,0)))))</f>
+        <v/>
+      </c>
+      <c r="T172" s="20">
+        <f>IF($B172="","",N($O172)-N($R172)-N($S172))</f>
+        <v/>
+      </c>
+      <c r="U172" s="20">
+        <f>IF($B172="","",ROUND(N($K172)*N($R172),0))</f>
+        <v/>
+      </c>
+      <c r="V172" s="20">
+        <f>IF($B172="","",ROUND(N($K172)*N($S172),0))</f>
+        <v/>
+      </c>
+      <c r="W172" s="20">
+        <f>IF($B172="","",N($P172)-N($U172)-N($V172))</f>
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="18">
@@ -13511,6 +17603,30 @@
         <f>IF($B173="","",IF($L173="감소","감소분 → 계약단가",IF(AND($M173="Y",OR($L173="증가",$L173="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L173="증가",IF(AND($N173&lt;&gt;"",$G173&gt;$N173),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L173="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R173" s="20">
+        <f>IF($B173="","",IF(N($O173)=0,0,IF(OR($L173="감소",AND($L173="증가",$M173&lt;&gt;"Y")),IF(N($G173)=0,0,ROUND(N(내역서!$G173)*$O173/$G173,0)),IF(N($J173)=0,0,ROUND(N(내역서!$O173)*$O173/$J173,0)))))</f>
+        <v/>
+      </c>
+      <c r="S173" s="20">
+        <f>IF($B173="","",IF(N($O173)=0,0,IF(OR($L173="감소",AND($L173="증가",$M173&lt;&gt;"Y")),IF(N($G173)=0,0,ROUND(N(내역서!$H173)*$O173/$G173,0)),IF(N($J173)=0,0,ROUND(N(내역서!$P173)*$O173/$J173,0)))))</f>
+        <v/>
+      </c>
+      <c r="T173" s="20">
+        <f>IF($B173="","",N($O173)-N($R173)-N($S173))</f>
+        <v/>
+      </c>
+      <c r="U173" s="20">
+        <f>IF($B173="","",ROUND(N($K173)*N($R173),0))</f>
+        <v/>
+      </c>
+      <c r="V173" s="20">
+        <f>IF($B173="","",ROUND(N($K173)*N($S173),0))</f>
+        <v/>
+      </c>
+      <c r="W173" s="20">
+        <f>IF($B173="","",N($P173)-N($U173)-N($V173))</f>
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="18">
@@ -13575,6 +17691,30 @@
         <f>IF($B174="","",IF($L174="감소","감소분 → 계약단가",IF(AND($M174="Y",OR($L174="증가",$L174="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L174="증가",IF(AND($N174&lt;&gt;"",$G174&gt;$N174),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L174="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R174" s="20">
+        <f>IF($B174="","",IF(N($O174)=0,0,IF(OR($L174="감소",AND($L174="증가",$M174&lt;&gt;"Y")),IF(N($G174)=0,0,ROUND(N(내역서!$G174)*$O174/$G174,0)),IF(N($J174)=0,0,ROUND(N(내역서!$O174)*$O174/$J174,0)))))</f>
+        <v/>
+      </c>
+      <c r="S174" s="20">
+        <f>IF($B174="","",IF(N($O174)=0,0,IF(OR($L174="감소",AND($L174="증가",$M174&lt;&gt;"Y")),IF(N($G174)=0,0,ROUND(N(내역서!$H174)*$O174/$G174,0)),IF(N($J174)=0,0,ROUND(N(내역서!$P174)*$O174/$J174,0)))))</f>
+        <v/>
+      </c>
+      <c r="T174" s="20">
+        <f>IF($B174="","",N($O174)-N($R174)-N($S174))</f>
+        <v/>
+      </c>
+      <c r="U174" s="20">
+        <f>IF($B174="","",ROUND(N($K174)*N($R174),0))</f>
+        <v/>
+      </c>
+      <c r="V174" s="20">
+        <f>IF($B174="","",ROUND(N($K174)*N($S174),0))</f>
+        <v/>
+      </c>
+      <c r="W174" s="20">
+        <f>IF($B174="","",N($P174)-N($U174)-N($V174))</f>
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="18">
@@ -13639,6 +17779,30 @@
         <f>IF($B175="","",IF($L175="감소","감소분 → 계약단가",IF(AND($M175="Y",OR($L175="증가",$L175="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L175="증가",IF(AND($N175&lt;&gt;"",$G175&gt;$N175),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L175="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R175" s="20">
+        <f>IF($B175="","",IF(N($O175)=0,0,IF(OR($L175="감소",AND($L175="증가",$M175&lt;&gt;"Y")),IF(N($G175)=0,0,ROUND(N(내역서!$G175)*$O175/$G175,0)),IF(N($J175)=0,0,ROUND(N(내역서!$O175)*$O175/$J175,0)))))</f>
+        <v/>
+      </c>
+      <c r="S175" s="20">
+        <f>IF($B175="","",IF(N($O175)=0,0,IF(OR($L175="감소",AND($L175="증가",$M175&lt;&gt;"Y")),IF(N($G175)=0,0,ROUND(N(내역서!$H175)*$O175/$G175,0)),IF(N($J175)=0,0,ROUND(N(내역서!$P175)*$O175/$J175,0)))))</f>
+        <v/>
+      </c>
+      <c r="T175" s="20">
+        <f>IF($B175="","",N($O175)-N($R175)-N($S175))</f>
+        <v/>
+      </c>
+      <c r="U175" s="20">
+        <f>IF($B175="","",ROUND(N($K175)*N($R175),0))</f>
+        <v/>
+      </c>
+      <c r="V175" s="20">
+        <f>IF($B175="","",ROUND(N($K175)*N($S175),0))</f>
+        <v/>
+      </c>
+      <c r="W175" s="20">
+        <f>IF($B175="","",N($P175)-N($U175)-N($V175))</f>
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="18">
@@ -13703,6 +17867,30 @@
         <f>IF($B176="","",IF($L176="감소","감소분 → 계약단가",IF(AND($M176="Y",OR($L176="증가",$L176="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L176="증가",IF(AND($N176&lt;&gt;"",$G176&gt;$N176),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L176="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R176" s="20">
+        <f>IF($B176="","",IF(N($O176)=0,0,IF(OR($L176="감소",AND($L176="증가",$M176&lt;&gt;"Y")),IF(N($G176)=0,0,ROUND(N(내역서!$G176)*$O176/$G176,0)),IF(N($J176)=0,0,ROUND(N(내역서!$O176)*$O176/$J176,0)))))</f>
+        <v/>
+      </c>
+      <c r="S176" s="20">
+        <f>IF($B176="","",IF(N($O176)=0,0,IF(OR($L176="감소",AND($L176="증가",$M176&lt;&gt;"Y")),IF(N($G176)=0,0,ROUND(N(내역서!$H176)*$O176/$G176,0)),IF(N($J176)=0,0,ROUND(N(내역서!$P176)*$O176/$J176,0)))))</f>
+        <v/>
+      </c>
+      <c r="T176" s="20">
+        <f>IF($B176="","",N($O176)-N($R176)-N($S176))</f>
+        <v/>
+      </c>
+      <c r="U176" s="20">
+        <f>IF($B176="","",ROUND(N($K176)*N($R176),0))</f>
+        <v/>
+      </c>
+      <c r="V176" s="20">
+        <f>IF($B176="","",ROUND(N($K176)*N($S176),0))</f>
+        <v/>
+      </c>
+      <c r="W176" s="20">
+        <f>IF($B176="","",N($P176)-N($U176)-N($V176))</f>
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="18">
@@ -13767,6 +17955,30 @@
         <f>IF($B177="","",IF($L177="감소","감소분 → 계약단가",IF(AND($M177="Y",OR($L177="증가",$L177="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L177="증가",IF(AND($N177&lt;&gt;"",$G177&gt;$N177),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L177="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R177" s="20">
+        <f>IF($B177="","",IF(N($O177)=0,0,IF(OR($L177="감소",AND($L177="증가",$M177&lt;&gt;"Y")),IF(N($G177)=0,0,ROUND(N(내역서!$G177)*$O177/$G177,0)),IF(N($J177)=0,0,ROUND(N(내역서!$O177)*$O177/$J177,0)))))</f>
+        <v/>
+      </c>
+      <c r="S177" s="20">
+        <f>IF($B177="","",IF(N($O177)=0,0,IF(OR($L177="감소",AND($L177="증가",$M177&lt;&gt;"Y")),IF(N($G177)=0,0,ROUND(N(내역서!$H177)*$O177/$G177,0)),IF(N($J177)=0,0,ROUND(N(내역서!$P177)*$O177/$J177,0)))))</f>
+        <v/>
+      </c>
+      <c r="T177" s="20">
+        <f>IF($B177="","",N($O177)-N($R177)-N($S177))</f>
+        <v/>
+      </c>
+      <c r="U177" s="20">
+        <f>IF($B177="","",ROUND(N($K177)*N($R177),0))</f>
+        <v/>
+      </c>
+      <c r="V177" s="20">
+        <f>IF($B177="","",ROUND(N($K177)*N($S177),0))</f>
+        <v/>
+      </c>
+      <c r="W177" s="20">
+        <f>IF($B177="","",N($P177)-N($U177)-N($V177))</f>
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="18">
@@ -13831,6 +18043,30 @@
         <f>IF($B178="","",IF($L178="감소","감소분 → 계약단가",IF(AND($M178="Y",OR($L178="증가",$L178="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L178="증가",IF(AND($N178&lt;&gt;"",$G178&gt;$N178),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L178="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R178" s="20">
+        <f>IF($B178="","",IF(N($O178)=0,0,IF(OR($L178="감소",AND($L178="증가",$M178&lt;&gt;"Y")),IF(N($G178)=0,0,ROUND(N(내역서!$G178)*$O178/$G178,0)),IF(N($J178)=0,0,ROUND(N(내역서!$O178)*$O178/$J178,0)))))</f>
+        <v/>
+      </c>
+      <c r="S178" s="20">
+        <f>IF($B178="","",IF(N($O178)=0,0,IF(OR($L178="감소",AND($L178="증가",$M178&lt;&gt;"Y")),IF(N($G178)=0,0,ROUND(N(내역서!$H178)*$O178/$G178,0)),IF(N($J178)=0,0,ROUND(N(내역서!$P178)*$O178/$J178,0)))))</f>
+        <v/>
+      </c>
+      <c r="T178" s="20">
+        <f>IF($B178="","",N($O178)-N($R178)-N($S178))</f>
+        <v/>
+      </c>
+      <c r="U178" s="20">
+        <f>IF($B178="","",ROUND(N($K178)*N($R178),0))</f>
+        <v/>
+      </c>
+      <c r="V178" s="20">
+        <f>IF($B178="","",ROUND(N($K178)*N($S178),0))</f>
+        <v/>
+      </c>
+      <c r="W178" s="20">
+        <f>IF($B178="","",N($P178)-N($U178)-N($V178))</f>
+        <v/>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="18">
@@ -13895,6 +18131,30 @@
         <f>IF($B179="","",IF($L179="감소","감소분 → 계약단가",IF(AND($M179="Y",OR($L179="증가",$L179="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L179="증가",IF(AND($N179&lt;&gt;"",$G179&gt;$N179),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L179="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R179" s="20">
+        <f>IF($B179="","",IF(N($O179)=0,0,IF(OR($L179="감소",AND($L179="증가",$M179&lt;&gt;"Y")),IF(N($G179)=0,0,ROUND(N(내역서!$G179)*$O179/$G179,0)),IF(N($J179)=0,0,ROUND(N(내역서!$O179)*$O179/$J179,0)))))</f>
+        <v/>
+      </c>
+      <c r="S179" s="20">
+        <f>IF($B179="","",IF(N($O179)=0,0,IF(OR($L179="감소",AND($L179="증가",$M179&lt;&gt;"Y")),IF(N($G179)=0,0,ROUND(N(내역서!$H179)*$O179/$G179,0)),IF(N($J179)=0,0,ROUND(N(내역서!$P179)*$O179/$J179,0)))))</f>
+        <v/>
+      </c>
+      <c r="T179" s="20">
+        <f>IF($B179="","",N($O179)-N($R179)-N($S179))</f>
+        <v/>
+      </c>
+      <c r="U179" s="20">
+        <f>IF($B179="","",ROUND(N($K179)*N($R179),0))</f>
+        <v/>
+      </c>
+      <c r="V179" s="20">
+        <f>IF($B179="","",ROUND(N($K179)*N($S179),0))</f>
+        <v/>
+      </c>
+      <c r="W179" s="20">
+        <f>IF($B179="","",N($P179)-N($U179)-N($V179))</f>
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="18">
@@ -13959,6 +18219,30 @@
         <f>IF($B180="","",IF($L180="감소","감소분 → 계약단가",IF(AND($M180="Y",OR($L180="증가",$L180="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L180="증가",IF(AND($N180&lt;&gt;"",$G180&gt;$N180),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L180="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R180" s="20">
+        <f>IF($B180="","",IF(N($O180)=0,0,IF(OR($L180="감소",AND($L180="증가",$M180&lt;&gt;"Y")),IF(N($G180)=0,0,ROUND(N(내역서!$G180)*$O180/$G180,0)),IF(N($J180)=0,0,ROUND(N(내역서!$O180)*$O180/$J180,0)))))</f>
+        <v/>
+      </c>
+      <c r="S180" s="20">
+        <f>IF($B180="","",IF(N($O180)=0,0,IF(OR($L180="감소",AND($L180="증가",$M180&lt;&gt;"Y")),IF(N($G180)=0,0,ROUND(N(내역서!$H180)*$O180/$G180,0)),IF(N($J180)=0,0,ROUND(N(내역서!$P180)*$O180/$J180,0)))))</f>
+        <v/>
+      </c>
+      <c r="T180" s="20">
+        <f>IF($B180="","",N($O180)-N($R180)-N($S180))</f>
+        <v/>
+      </c>
+      <c r="U180" s="20">
+        <f>IF($B180="","",ROUND(N($K180)*N($R180),0))</f>
+        <v/>
+      </c>
+      <c r="V180" s="20">
+        <f>IF($B180="","",ROUND(N($K180)*N($S180),0))</f>
+        <v/>
+      </c>
+      <c r="W180" s="20">
+        <f>IF($B180="","",N($P180)-N($U180)-N($V180))</f>
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="18">
@@ -14023,6 +18307,30 @@
         <f>IF($B181="","",IF($L181="감소","감소분 → 계약단가",IF(AND($M181="Y",OR($L181="증가",$L181="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L181="증가",IF(AND($N181&lt;&gt;"",$G181&gt;$N181),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L181="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R181" s="20">
+        <f>IF($B181="","",IF(N($O181)=0,0,IF(OR($L181="감소",AND($L181="증가",$M181&lt;&gt;"Y")),IF(N($G181)=0,0,ROUND(N(내역서!$G181)*$O181/$G181,0)),IF(N($J181)=0,0,ROUND(N(내역서!$O181)*$O181/$J181,0)))))</f>
+        <v/>
+      </c>
+      <c r="S181" s="20">
+        <f>IF($B181="","",IF(N($O181)=0,0,IF(OR($L181="감소",AND($L181="증가",$M181&lt;&gt;"Y")),IF(N($G181)=0,0,ROUND(N(내역서!$H181)*$O181/$G181,0)),IF(N($J181)=0,0,ROUND(N(내역서!$P181)*$O181/$J181,0)))))</f>
+        <v/>
+      </c>
+      <c r="T181" s="20">
+        <f>IF($B181="","",N($O181)-N($R181)-N($S181))</f>
+        <v/>
+      </c>
+      <c r="U181" s="20">
+        <f>IF($B181="","",ROUND(N($K181)*N($R181),0))</f>
+        <v/>
+      </c>
+      <c r="V181" s="20">
+        <f>IF($B181="","",ROUND(N($K181)*N($S181),0))</f>
+        <v/>
+      </c>
+      <c r="W181" s="20">
+        <f>IF($B181="","",N($P181)-N($U181)-N($V181))</f>
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="18">
@@ -14087,6 +18395,30 @@
         <f>IF($B182="","",IF($L182="감소","감소분 → 계약단가",IF(AND($M182="Y",OR($L182="증가",$L182="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L182="증가",IF(AND($N182&lt;&gt;"",$G182&gt;$N182),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L182="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R182" s="20">
+        <f>IF($B182="","",IF(N($O182)=0,0,IF(OR($L182="감소",AND($L182="증가",$M182&lt;&gt;"Y")),IF(N($G182)=0,0,ROUND(N(내역서!$G182)*$O182/$G182,0)),IF(N($J182)=0,0,ROUND(N(내역서!$O182)*$O182/$J182,0)))))</f>
+        <v/>
+      </c>
+      <c r="S182" s="20">
+        <f>IF($B182="","",IF(N($O182)=0,0,IF(OR($L182="감소",AND($L182="증가",$M182&lt;&gt;"Y")),IF(N($G182)=0,0,ROUND(N(내역서!$H182)*$O182/$G182,0)),IF(N($J182)=0,0,ROUND(N(내역서!$P182)*$O182/$J182,0)))))</f>
+        <v/>
+      </c>
+      <c r="T182" s="20">
+        <f>IF($B182="","",N($O182)-N($R182)-N($S182))</f>
+        <v/>
+      </c>
+      <c r="U182" s="20">
+        <f>IF($B182="","",ROUND(N($K182)*N($R182),0))</f>
+        <v/>
+      </c>
+      <c r="V182" s="20">
+        <f>IF($B182="","",ROUND(N($K182)*N($S182),0))</f>
+        <v/>
+      </c>
+      <c r="W182" s="20">
+        <f>IF($B182="","",N($P182)-N($U182)-N($V182))</f>
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="18">
@@ -14151,6 +18483,30 @@
         <f>IF($B183="","",IF($L183="감소","감소분 → 계약단가",IF(AND($M183="Y",OR($L183="증가",$L183="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L183="증가",IF(AND($N183&lt;&gt;"",$G183&gt;$N183),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L183="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R183" s="20">
+        <f>IF($B183="","",IF(N($O183)=0,0,IF(OR($L183="감소",AND($L183="증가",$M183&lt;&gt;"Y")),IF(N($G183)=0,0,ROUND(N(내역서!$G183)*$O183/$G183,0)),IF(N($J183)=0,0,ROUND(N(내역서!$O183)*$O183/$J183,0)))))</f>
+        <v/>
+      </c>
+      <c r="S183" s="20">
+        <f>IF($B183="","",IF(N($O183)=0,0,IF(OR($L183="감소",AND($L183="증가",$M183&lt;&gt;"Y")),IF(N($G183)=0,0,ROUND(N(내역서!$H183)*$O183/$G183,0)),IF(N($J183)=0,0,ROUND(N(내역서!$P183)*$O183/$J183,0)))))</f>
+        <v/>
+      </c>
+      <c r="T183" s="20">
+        <f>IF($B183="","",N($O183)-N($R183)-N($S183))</f>
+        <v/>
+      </c>
+      <c r="U183" s="20">
+        <f>IF($B183="","",ROUND(N($K183)*N($R183),0))</f>
+        <v/>
+      </c>
+      <c r="V183" s="20">
+        <f>IF($B183="","",ROUND(N($K183)*N($S183),0))</f>
+        <v/>
+      </c>
+      <c r="W183" s="20">
+        <f>IF($B183="","",N($P183)-N($U183)-N($V183))</f>
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="18">
@@ -14215,6 +18571,30 @@
         <f>IF($B184="","",IF($L184="감소","감소분 → 계약단가",IF(AND($M184="Y",OR($L184="증가",$L184="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L184="증가",IF(AND($N184&lt;&gt;"",$G184&gt;$N184),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L184="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R184" s="20">
+        <f>IF($B184="","",IF(N($O184)=0,0,IF(OR($L184="감소",AND($L184="증가",$M184&lt;&gt;"Y")),IF(N($G184)=0,0,ROUND(N(내역서!$G184)*$O184/$G184,0)),IF(N($J184)=0,0,ROUND(N(내역서!$O184)*$O184/$J184,0)))))</f>
+        <v/>
+      </c>
+      <c r="S184" s="20">
+        <f>IF($B184="","",IF(N($O184)=0,0,IF(OR($L184="감소",AND($L184="증가",$M184&lt;&gt;"Y")),IF(N($G184)=0,0,ROUND(N(내역서!$H184)*$O184/$G184,0)),IF(N($J184)=0,0,ROUND(N(내역서!$P184)*$O184/$J184,0)))))</f>
+        <v/>
+      </c>
+      <c r="T184" s="20">
+        <f>IF($B184="","",N($O184)-N($R184)-N($S184))</f>
+        <v/>
+      </c>
+      <c r="U184" s="20">
+        <f>IF($B184="","",ROUND(N($K184)*N($R184),0))</f>
+        <v/>
+      </c>
+      <c r="V184" s="20">
+        <f>IF($B184="","",ROUND(N($K184)*N($S184),0))</f>
+        <v/>
+      </c>
+      <c r="W184" s="20">
+        <f>IF($B184="","",N($P184)-N($U184)-N($V184))</f>
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="18">
@@ -14279,6 +18659,30 @@
         <f>IF($B185="","",IF($L185="감소","감소분 → 계약단가",IF(AND($M185="Y",OR($L185="증가",$L185="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L185="증가",IF(AND($N185&lt;&gt;"",$G185&gt;$N185),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L185="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R185" s="20">
+        <f>IF($B185="","",IF(N($O185)=0,0,IF(OR($L185="감소",AND($L185="증가",$M185&lt;&gt;"Y")),IF(N($G185)=0,0,ROUND(N(내역서!$G185)*$O185/$G185,0)),IF(N($J185)=0,0,ROUND(N(내역서!$O185)*$O185/$J185,0)))))</f>
+        <v/>
+      </c>
+      <c r="S185" s="20">
+        <f>IF($B185="","",IF(N($O185)=0,0,IF(OR($L185="감소",AND($L185="증가",$M185&lt;&gt;"Y")),IF(N($G185)=0,0,ROUND(N(내역서!$H185)*$O185/$G185,0)),IF(N($J185)=0,0,ROUND(N(내역서!$P185)*$O185/$J185,0)))))</f>
+        <v/>
+      </c>
+      <c r="T185" s="20">
+        <f>IF($B185="","",N($O185)-N($R185)-N($S185))</f>
+        <v/>
+      </c>
+      <c r="U185" s="20">
+        <f>IF($B185="","",ROUND(N($K185)*N($R185),0))</f>
+        <v/>
+      </c>
+      <c r="V185" s="20">
+        <f>IF($B185="","",ROUND(N($K185)*N($S185),0))</f>
+        <v/>
+      </c>
+      <c r="W185" s="20">
+        <f>IF($B185="","",N($P185)-N($U185)-N($V185))</f>
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="18">
@@ -14343,6 +18747,30 @@
         <f>IF($B186="","",IF($L186="감소","감소분 → 계약단가",IF(AND($M186="Y",OR($L186="증가",$L186="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L186="증가",IF(AND($N186&lt;&gt;"",$G186&gt;$N186),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L186="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R186" s="20">
+        <f>IF($B186="","",IF(N($O186)=0,0,IF(OR($L186="감소",AND($L186="증가",$M186&lt;&gt;"Y")),IF(N($G186)=0,0,ROUND(N(내역서!$G186)*$O186/$G186,0)),IF(N($J186)=0,0,ROUND(N(내역서!$O186)*$O186/$J186,0)))))</f>
+        <v/>
+      </c>
+      <c r="S186" s="20">
+        <f>IF($B186="","",IF(N($O186)=0,0,IF(OR($L186="감소",AND($L186="증가",$M186&lt;&gt;"Y")),IF(N($G186)=0,0,ROUND(N(내역서!$H186)*$O186/$G186,0)),IF(N($J186)=0,0,ROUND(N(내역서!$P186)*$O186/$J186,0)))))</f>
+        <v/>
+      </c>
+      <c r="T186" s="20">
+        <f>IF($B186="","",N($O186)-N($R186)-N($S186))</f>
+        <v/>
+      </c>
+      <c r="U186" s="20">
+        <f>IF($B186="","",ROUND(N($K186)*N($R186),0))</f>
+        <v/>
+      </c>
+      <c r="V186" s="20">
+        <f>IF($B186="","",ROUND(N($K186)*N($S186),0))</f>
+        <v/>
+      </c>
+      <c r="W186" s="20">
+        <f>IF($B186="","",N($P186)-N($U186)-N($V186))</f>
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="18">
@@ -14407,6 +18835,30 @@
         <f>IF($B187="","",IF($L187="감소","감소분 → 계약단가",IF(AND($M187="Y",OR($L187="증가",$L187="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L187="증가",IF(AND($N187&lt;&gt;"",$G187&gt;$N187),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L187="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R187" s="20">
+        <f>IF($B187="","",IF(N($O187)=0,0,IF(OR($L187="감소",AND($L187="증가",$M187&lt;&gt;"Y")),IF(N($G187)=0,0,ROUND(N(내역서!$G187)*$O187/$G187,0)),IF(N($J187)=0,0,ROUND(N(내역서!$O187)*$O187/$J187,0)))))</f>
+        <v/>
+      </c>
+      <c r="S187" s="20">
+        <f>IF($B187="","",IF(N($O187)=0,0,IF(OR($L187="감소",AND($L187="증가",$M187&lt;&gt;"Y")),IF(N($G187)=0,0,ROUND(N(내역서!$H187)*$O187/$G187,0)),IF(N($J187)=0,0,ROUND(N(내역서!$P187)*$O187/$J187,0)))))</f>
+        <v/>
+      </c>
+      <c r="T187" s="20">
+        <f>IF($B187="","",N($O187)-N($R187)-N($S187))</f>
+        <v/>
+      </c>
+      <c r="U187" s="20">
+        <f>IF($B187="","",ROUND(N($K187)*N($R187),0))</f>
+        <v/>
+      </c>
+      <c r="V187" s="20">
+        <f>IF($B187="","",ROUND(N($K187)*N($S187),0))</f>
+        <v/>
+      </c>
+      <c r="W187" s="20">
+        <f>IF($B187="","",N($P187)-N($U187)-N($V187))</f>
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="18">
@@ -14471,6 +18923,30 @@
         <f>IF($B188="","",IF($L188="감소","감소분 → 계약단가",IF(AND($M188="Y",OR($L188="증가",$L188="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L188="증가",IF(AND($N188&lt;&gt;"",$G188&gt;$N188),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L188="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R188" s="20">
+        <f>IF($B188="","",IF(N($O188)=0,0,IF(OR($L188="감소",AND($L188="증가",$M188&lt;&gt;"Y")),IF(N($G188)=0,0,ROUND(N(내역서!$G188)*$O188/$G188,0)),IF(N($J188)=0,0,ROUND(N(내역서!$O188)*$O188/$J188,0)))))</f>
+        <v/>
+      </c>
+      <c r="S188" s="20">
+        <f>IF($B188="","",IF(N($O188)=0,0,IF(OR($L188="감소",AND($L188="증가",$M188&lt;&gt;"Y")),IF(N($G188)=0,0,ROUND(N(내역서!$H188)*$O188/$G188,0)),IF(N($J188)=0,0,ROUND(N(내역서!$P188)*$O188/$J188,0)))))</f>
+        <v/>
+      </c>
+      <c r="T188" s="20">
+        <f>IF($B188="","",N($O188)-N($R188)-N($S188))</f>
+        <v/>
+      </c>
+      <c r="U188" s="20">
+        <f>IF($B188="","",ROUND(N($K188)*N($R188),0))</f>
+        <v/>
+      </c>
+      <c r="V188" s="20">
+        <f>IF($B188="","",ROUND(N($K188)*N($S188),0))</f>
+        <v/>
+      </c>
+      <c r="W188" s="20">
+        <f>IF($B188="","",N($P188)-N($U188)-N($V188))</f>
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="18">
@@ -14535,6 +19011,30 @@
         <f>IF($B189="","",IF($L189="감소","감소분 → 계약단가",IF(AND($M189="Y",OR($L189="증가",$L189="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L189="증가",IF(AND($N189&lt;&gt;"",$G189&gt;$N189),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L189="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R189" s="20">
+        <f>IF($B189="","",IF(N($O189)=0,0,IF(OR($L189="감소",AND($L189="증가",$M189&lt;&gt;"Y")),IF(N($G189)=0,0,ROUND(N(내역서!$G189)*$O189/$G189,0)),IF(N($J189)=0,0,ROUND(N(내역서!$O189)*$O189/$J189,0)))))</f>
+        <v/>
+      </c>
+      <c r="S189" s="20">
+        <f>IF($B189="","",IF(N($O189)=0,0,IF(OR($L189="감소",AND($L189="증가",$M189&lt;&gt;"Y")),IF(N($G189)=0,0,ROUND(N(내역서!$H189)*$O189/$G189,0)),IF(N($J189)=0,0,ROUND(N(내역서!$P189)*$O189/$J189,0)))))</f>
+        <v/>
+      </c>
+      <c r="T189" s="20">
+        <f>IF($B189="","",N($O189)-N($R189)-N($S189))</f>
+        <v/>
+      </c>
+      <c r="U189" s="20">
+        <f>IF($B189="","",ROUND(N($K189)*N($R189),0))</f>
+        <v/>
+      </c>
+      <c r="V189" s="20">
+        <f>IF($B189="","",ROUND(N($K189)*N($S189),0))</f>
+        <v/>
+      </c>
+      <c r="W189" s="20">
+        <f>IF($B189="","",N($P189)-N($U189)-N($V189))</f>
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="18">
@@ -14599,6 +19099,30 @@
         <f>IF($B190="","",IF($L190="감소","감소분 → 계약단가",IF(AND($M190="Y",OR($L190="증가",$L190="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L190="증가",IF(AND($N190&lt;&gt;"",$G190&gt;$N190),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L190="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R190" s="20">
+        <f>IF($B190="","",IF(N($O190)=0,0,IF(OR($L190="감소",AND($L190="증가",$M190&lt;&gt;"Y")),IF(N($G190)=0,0,ROUND(N(내역서!$G190)*$O190/$G190,0)),IF(N($J190)=0,0,ROUND(N(내역서!$O190)*$O190/$J190,0)))))</f>
+        <v/>
+      </c>
+      <c r="S190" s="20">
+        <f>IF($B190="","",IF(N($O190)=0,0,IF(OR($L190="감소",AND($L190="증가",$M190&lt;&gt;"Y")),IF(N($G190)=0,0,ROUND(N(내역서!$H190)*$O190/$G190,0)),IF(N($J190)=0,0,ROUND(N(내역서!$P190)*$O190/$J190,0)))))</f>
+        <v/>
+      </c>
+      <c r="T190" s="20">
+        <f>IF($B190="","",N($O190)-N($R190)-N($S190))</f>
+        <v/>
+      </c>
+      <c r="U190" s="20">
+        <f>IF($B190="","",ROUND(N($K190)*N($R190),0))</f>
+        <v/>
+      </c>
+      <c r="V190" s="20">
+        <f>IF($B190="","",ROUND(N($K190)*N($S190),0))</f>
+        <v/>
+      </c>
+      <c r="W190" s="20">
+        <f>IF($B190="","",N($P190)-N($U190)-N($V190))</f>
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="18">
@@ -14663,6 +19187,30 @@
         <f>IF($B191="","",IF($L191="감소","감소분 → 계약단가",IF(AND($M191="Y",OR($L191="증가",$L191="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L191="증가",IF(AND($N191&lt;&gt;"",$G191&gt;$N191),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L191="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R191" s="20">
+        <f>IF($B191="","",IF(N($O191)=0,0,IF(OR($L191="감소",AND($L191="증가",$M191&lt;&gt;"Y")),IF(N($G191)=0,0,ROUND(N(내역서!$G191)*$O191/$G191,0)),IF(N($J191)=0,0,ROUND(N(내역서!$O191)*$O191/$J191,0)))))</f>
+        <v/>
+      </c>
+      <c r="S191" s="20">
+        <f>IF($B191="","",IF(N($O191)=0,0,IF(OR($L191="감소",AND($L191="증가",$M191&lt;&gt;"Y")),IF(N($G191)=0,0,ROUND(N(내역서!$H191)*$O191/$G191,0)),IF(N($J191)=0,0,ROUND(N(내역서!$P191)*$O191/$J191,0)))))</f>
+        <v/>
+      </c>
+      <c r="T191" s="20">
+        <f>IF($B191="","",N($O191)-N($R191)-N($S191))</f>
+        <v/>
+      </c>
+      <c r="U191" s="20">
+        <f>IF($B191="","",ROUND(N($K191)*N($R191),0))</f>
+        <v/>
+      </c>
+      <c r="V191" s="20">
+        <f>IF($B191="","",ROUND(N($K191)*N($S191),0))</f>
+        <v/>
+      </c>
+      <c r="W191" s="20">
+        <f>IF($B191="","",N($P191)-N($U191)-N($V191))</f>
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="18">
@@ -14727,6 +19275,30 @@
         <f>IF($B192="","",IF($L192="감소","감소분 → 계약단가",IF(AND($M192="Y",OR($L192="증가",$L192="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L192="증가",IF(AND($N192&lt;&gt;"",$G192&gt;$N192),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L192="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R192" s="20">
+        <f>IF($B192="","",IF(N($O192)=0,0,IF(OR($L192="감소",AND($L192="증가",$M192&lt;&gt;"Y")),IF(N($G192)=0,0,ROUND(N(내역서!$G192)*$O192/$G192,0)),IF(N($J192)=0,0,ROUND(N(내역서!$O192)*$O192/$J192,0)))))</f>
+        <v/>
+      </c>
+      <c r="S192" s="20">
+        <f>IF($B192="","",IF(N($O192)=0,0,IF(OR($L192="감소",AND($L192="증가",$M192&lt;&gt;"Y")),IF(N($G192)=0,0,ROUND(N(내역서!$H192)*$O192/$G192,0)),IF(N($J192)=0,0,ROUND(N(내역서!$P192)*$O192/$J192,0)))))</f>
+        <v/>
+      </c>
+      <c r="T192" s="20">
+        <f>IF($B192="","",N($O192)-N($R192)-N($S192))</f>
+        <v/>
+      </c>
+      <c r="U192" s="20">
+        <f>IF($B192="","",ROUND(N($K192)*N($R192),0))</f>
+        <v/>
+      </c>
+      <c r="V192" s="20">
+        <f>IF($B192="","",ROUND(N($K192)*N($S192),0))</f>
+        <v/>
+      </c>
+      <c r="W192" s="20">
+        <f>IF($B192="","",N($P192)-N($U192)-N($V192))</f>
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="18">
@@ -14791,6 +19363,30 @@
         <f>IF($B193="","",IF($L193="감소","감소분 → 계약단가",IF(AND($M193="Y",OR($L193="증가",$L193="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L193="증가",IF(AND($N193&lt;&gt;"",$G193&gt;$N193),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L193="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R193" s="20">
+        <f>IF($B193="","",IF(N($O193)=0,0,IF(OR($L193="감소",AND($L193="증가",$M193&lt;&gt;"Y")),IF(N($G193)=0,0,ROUND(N(내역서!$G193)*$O193/$G193,0)),IF(N($J193)=0,0,ROUND(N(내역서!$O193)*$O193/$J193,0)))))</f>
+        <v/>
+      </c>
+      <c r="S193" s="20">
+        <f>IF($B193="","",IF(N($O193)=0,0,IF(OR($L193="감소",AND($L193="증가",$M193&lt;&gt;"Y")),IF(N($G193)=0,0,ROUND(N(내역서!$H193)*$O193/$G193,0)),IF(N($J193)=0,0,ROUND(N(내역서!$P193)*$O193/$J193,0)))))</f>
+        <v/>
+      </c>
+      <c r="T193" s="20">
+        <f>IF($B193="","",N($O193)-N($R193)-N($S193))</f>
+        <v/>
+      </c>
+      <c r="U193" s="20">
+        <f>IF($B193="","",ROUND(N($K193)*N($R193),0))</f>
+        <v/>
+      </c>
+      <c r="V193" s="20">
+        <f>IF($B193="","",ROUND(N($K193)*N($S193),0))</f>
+        <v/>
+      </c>
+      <c r="W193" s="20">
+        <f>IF($B193="","",N($P193)-N($U193)-N($V193))</f>
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="18">
@@ -14855,6 +19451,30 @@
         <f>IF($B194="","",IF($L194="감소","감소분 → 계약단가",IF(AND($M194="Y",OR($L194="증가",$L194="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L194="증가",IF(AND($N194&lt;&gt;"",$G194&gt;$N194),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L194="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R194" s="20">
+        <f>IF($B194="","",IF(N($O194)=0,0,IF(OR($L194="감소",AND($L194="증가",$M194&lt;&gt;"Y")),IF(N($G194)=0,0,ROUND(N(내역서!$G194)*$O194/$G194,0)),IF(N($J194)=0,0,ROUND(N(내역서!$O194)*$O194/$J194,0)))))</f>
+        <v/>
+      </c>
+      <c r="S194" s="20">
+        <f>IF($B194="","",IF(N($O194)=0,0,IF(OR($L194="감소",AND($L194="증가",$M194&lt;&gt;"Y")),IF(N($G194)=0,0,ROUND(N(내역서!$H194)*$O194/$G194,0)),IF(N($J194)=0,0,ROUND(N(내역서!$P194)*$O194/$J194,0)))))</f>
+        <v/>
+      </c>
+      <c r="T194" s="20">
+        <f>IF($B194="","",N($O194)-N($R194)-N($S194))</f>
+        <v/>
+      </c>
+      <c r="U194" s="20">
+        <f>IF($B194="","",ROUND(N($K194)*N($R194),0))</f>
+        <v/>
+      </c>
+      <c r="V194" s="20">
+        <f>IF($B194="","",ROUND(N($K194)*N($S194),0))</f>
+        <v/>
+      </c>
+      <c r="W194" s="20">
+        <f>IF($B194="","",N($P194)-N($U194)-N($V194))</f>
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="18">
@@ -14919,6 +19539,30 @@
         <f>IF($B195="","",IF($L195="감소","감소분 → 계약단가",IF(AND($M195="Y",OR($L195="증가",$L195="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L195="증가",IF(AND($N195&lt;&gt;"",$G195&gt;$N195),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L195="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R195" s="20">
+        <f>IF($B195="","",IF(N($O195)=0,0,IF(OR($L195="감소",AND($L195="증가",$M195&lt;&gt;"Y")),IF(N($G195)=0,0,ROUND(N(내역서!$G195)*$O195/$G195,0)),IF(N($J195)=0,0,ROUND(N(내역서!$O195)*$O195/$J195,0)))))</f>
+        <v/>
+      </c>
+      <c r="S195" s="20">
+        <f>IF($B195="","",IF(N($O195)=0,0,IF(OR($L195="감소",AND($L195="증가",$M195&lt;&gt;"Y")),IF(N($G195)=0,0,ROUND(N(내역서!$H195)*$O195/$G195,0)),IF(N($J195)=0,0,ROUND(N(내역서!$P195)*$O195/$J195,0)))))</f>
+        <v/>
+      </c>
+      <c r="T195" s="20">
+        <f>IF($B195="","",N($O195)-N($R195)-N($S195))</f>
+        <v/>
+      </c>
+      <c r="U195" s="20">
+        <f>IF($B195="","",ROUND(N($K195)*N($R195),0))</f>
+        <v/>
+      </c>
+      <c r="V195" s="20">
+        <f>IF($B195="","",ROUND(N($K195)*N($S195),0))</f>
+        <v/>
+      </c>
+      <c r="W195" s="20">
+        <f>IF($B195="","",N($P195)-N($U195)-N($V195))</f>
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="18">
@@ -14983,6 +19627,30 @@
         <f>IF($B196="","",IF($L196="감소","감소분 → 계약단가",IF(AND($M196="Y",OR($L196="증가",$L196="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L196="증가",IF(AND($N196&lt;&gt;"",$G196&gt;$N196),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L196="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R196" s="20">
+        <f>IF($B196="","",IF(N($O196)=0,0,IF(OR($L196="감소",AND($L196="증가",$M196&lt;&gt;"Y")),IF(N($G196)=0,0,ROUND(N(내역서!$G196)*$O196/$G196,0)),IF(N($J196)=0,0,ROUND(N(내역서!$O196)*$O196/$J196,0)))))</f>
+        <v/>
+      </c>
+      <c r="S196" s="20">
+        <f>IF($B196="","",IF(N($O196)=0,0,IF(OR($L196="감소",AND($L196="증가",$M196&lt;&gt;"Y")),IF(N($G196)=0,0,ROUND(N(내역서!$H196)*$O196/$G196,0)),IF(N($J196)=0,0,ROUND(N(내역서!$P196)*$O196/$J196,0)))))</f>
+        <v/>
+      </c>
+      <c r="T196" s="20">
+        <f>IF($B196="","",N($O196)-N($R196)-N($S196))</f>
+        <v/>
+      </c>
+      <c r="U196" s="20">
+        <f>IF($B196="","",ROUND(N($K196)*N($R196),0))</f>
+        <v/>
+      </c>
+      <c r="V196" s="20">
+        <f>IF($B196="","",ROUND(N($K196)*N($S196),0))</f>
+        <v/>
+      </c>
+      <c r="W196" s="20">
+        <f>IF($B196="","",N($P196)-N($U196)-N($V196))</f>
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="18">
@@ -15047,6 +19715,30 @@
         <f>IF($B197="","",IF($L197="감소","감소분 → 계약단가",IF(AND($M197="Y",OR($L197="증가",$L197="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L197="증가",IF(AND($N197&lt;&gt;"",$G197&gt;$N197),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L197="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R197" s="20">
+        <f>IF($B197="","",IF(N($O197)=0,0,IF(OR($L197="감소",AND($L197="증가",$M197&lt;&gt;"Y")),IF(N($G197)=0,0,ROUND(N(내역서!$G197)*$O197/$G197,0)),IF(N($J197)=0,0,ROUND(N(내역서!$O197)*$O197/$J197,0)))))</f>
+        <v/>
+      </c>
+      <c r="S197" s="20">
+        <f>IF($B197="","",IF(N($O197)=0,0,IF(OR($L197="감소",AND($L197="증가",$M197&lt;&gt;"Y")),IF(N($G197)=0,0,ROUND(N(내역서!$H197)*$O197/$G197,0)),IF(N($J197)=0,0,ROUND(N(내역서!$P197)*$O197/$J197,0)))))</f>
+        <v/>
+      </c>
+      <c r="T197" s="20">
+        <f>IF($B197="","",N($O197)-N($R197)-N($S197))</f>
+        <v/>
+      </c>
+      <c r="U197" s="20">
+        <f>IF($B197="","",ROUND(N($K197)*N($R197),0))</f>
+        <v/>
+      </c>
+      <c r="V197" s="20">
+        <f>IF($B197="","",ROUND(N($K197)*N($S197),0))</f>
+        <v/>
+      </c>
+      <c r="W197" s="20">
+        <f>IF($B197="","",N($P197)-N($U197)-N($V197))</f>
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="18">
@@ -15111,6 +19803,30 @@
         <f>IF($B198="","",IF($L198="감소","감소분 → 계약단가",IF(AND($M198="Y",OR($L198="증가",$L198="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L198="증가",IF(AND($N198&lt;&gt;"",$G198&gt;$N198),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L198="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R198" s="20">
+        <f>IF($B198="","",IF(N($O198)=0,0,IF(OR($L198="감소",AND($L198="증가",$M198&lt;&gt;"Y")),IF(N($G198)=0,0,ROUND(N(내역서!$G198)*$O198/$G198,0)),IF(N($J198)=0,0,ROUND(N(내역서!$O198)*$O198/$J198,0)))))</f>
+        <v/>
+      </c>
+      <c r="S198" s="20">
+        <f>IF($B198="","",IF(N($O198)=0,0,IF(OR($L198="감소",AND($L198="증가",$M198&lt;&gt;"Y")),IF(N($G198)=0,0,ROUND(N(내역서!$H198)*$O198/$G198,0)),IF(N($J198)=0,0,ROUND(N(내역서!$P198)*$O198/$J198,0)))))</f>
+        <v/>
+      </c>
+      <c r="T198" s="20">
+        <f>IF($B198="","",N($O198)-N($R198)-N($S198))</f>
+        <v/>
+      </c>
+      <c r="U198" s="20">
+        <f>IF($B198="","",ROUND(N($K198)*N($R198),0))</f>
+        <v/>
+      </c>
+      <c r="V198" s="20">
+        <f>IF($B198="","",ROUND(N($K198)*N($S198),0))</f>
+        <v/>
+      </c>
+      <c r="W198" s="20">
+        <f>IF($B198="","",N($P198)-N($U198)-N($V198))</f>
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="18">
@@ -15175,6 +19891,30 @@
         <f>IF($B199="","",IF($L199="감소","감소분 → 계약단가",IF(AND($M199="Y",OR($L199="증가",$L199="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L199="증가",IF(AND($N199&lt;&gt;"",$G199&gt;$N199),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L199="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R199" s="20">
+        <f>IF($B199="","",IF(N($O199)=0,0,IF(OR($L199="감소",AND($L199="증가",$M199&lt;&gt;"Y")),IF(N($G199)=0,0,ROUND(N(내역서!$G199)*$O199/$G199,0)),IF(N($J199)=0,0,ROUND(N(내역서!$O199)*$O199/$J199,0)))))</f>
+        <v/>
+      </c>
+      <c r="S199" s="20">
+        <f>IF($B199="","",IF(N($O199)=0,0,IF(OR($L199="감소",AND($L199="증가",$M199&lt;&gt;"Y")),IF(N($G199)=0,0,ROUND(N(내역서!$H199)*$O199/$G199,0)),IF(N($J199)=0,0,ROUND(N(내역서!$P199)*$O199/$J199,0)))))</f>
+        <v/>
+      </c>
+      <c r="T199" s="20">
+        <f>IF($B199="","",N($O199)-N($R199)-N($S199))</f>
+        <v/>
+      </c>
+      <c r="U199" s="20">
+        <f>IF($B199="","",ROUND(N($K199)*N($R199),0))</f>
+        <v/>
+      </c>
+      <c r="V199" s="20">
+        <f>IF($B199="","",ROUND(N($K199)*N($S199),0))</f>
+        <v/>
+      </c>
+      <c r="W199" s="20">
+        <f>IF($B199="","",N($P199)-N($U199)-N($V199))</f>
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="18">
@@ -15239,6 +19979,30 @@
         <f>IF($B200="","",IF($L200="감소","감소분 → 계약단가",IF(AND($M200="Y",OR($L200="증가",$L200="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L200="증가",IF(AND($N200&lt;&gt;"",$G200&gt;$N200),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L200="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R200" s="20">
+        <f>IF($B200="","",IF(N($O200)=0,0,IF(OR($L200="감소",AND($L200="증가",$M200&lt;&gt;"Y")),IF(N($G200)=0,0,ROUND(N(내역서!$G200)*$O200/$G200,0)),IF(N($J200)=0,0,ROUND(N(내역서!$O200)*$O200/$J200,0)))))</f>
+        <v/>
+      </c>
+      <c r="S200" s="20">
+        <f>IF($B200="","",IF(N($O200)=0,0,IF(OR($L200="감소",AND($L200="증가",$M200&lt;&gt;"Y")),IF(N($G200)=0,0,ROUND(N(내역서!$H200)*$O200/$G200,0)),IF(N($J200)=0,0,ROUND(N(내역서!$P200)*$O200/$J200,0)))))</f>
+        <v/>
+      </c>
+      <c r="T200" s="20">
+        <f>IF($B200="","",N($O200)-N($R200)-N($S200))</f>
+        <v/>
+      </c>
+      <c r="U200" s="20">
+        <f>IF($B200="","",ROUND(N($K200)*N($R200),0))</f>
+        <v/>
+      </c>
+      <c r="V200" s="20">
+        <f>IF($B200="","",ROUND(N($K200)*N($S200),0))</f>
+        <v/>
+      </c>
+      <c r="W200" s="20">
+        <f>IF($B200="","",N($P200)-N($U200)-N($V200))</f>
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="18">
@@ -15303,6 +20067,30 @@
         <f>IF($B201="","",IF($L201="감소","감소분 → 계약단가",IF(AND($M201="Y",OR($L201="증가",$L201="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L201="증가",IF(AND($N201&lt;&gt;"",$G201&gt;$N201),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L201="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R201" s="20">
+        <f>IF($B201="","",IF(N($O201)=0,0,IF(OR($L201="감소",AND($L201="증가",$M201&lt;&gt;"Y")),IF(N($G201)=0,0,ROUND(N(내역서!$G201)*$O201/$G201,0)),IF(N($J201)=0,0,ROUND(N(내역서!$O201)*$O201/$J201,0)))))</f>
+        <v/>
+      </c>
+      <c r="S201" s="20">
+        <f>IF($B201="","",IF(N($O201)=0,0,IF(OR($L201="감소",AND($L201="증가",$M201&lt;&gt;"Y")),IF(N($G201)=0,0,ROUND(N(내역서!$H201)*$O201/$G201,0)),IF(N($J201)=0,0,ROUND(N(내역서!$P201)*$O201/$J201,0)))))</f>
+        <v/>
+      </c>
+      <c r="T201" s="20">
+        <f>IF($B201="","",N($O201)-N($R201)-N($S201))</f>
+        <v/>
+      </c>
+      <c r="U201" s="20">
+        <f>IF($B201="","",ROUND(N($K201)*N($R201),0))</f>
+        <v/>
+      </c>
+      <c r="V201" s="20">
+        <f>IF($B201="","",ROUND(N($K201)*N($S201),0))</f>
+        <v/>
+      </c>
+      <c r="W201" s="20">
+        <f>IF($B201="","",N($P201)-N($U201)-N($V201))</f>
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="18">
@@ -15367,6 +20155,30 @@
         <f>IF($B202="","",IF($L202="감소","감소분 → 계약단가",IF(AND($M202="Y",OR($L202="증가",$L202="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L202="증가",IF(AND($N202&lt;&gt;"",$G202&gt;$N202),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L202="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
         <v/>
       </c>
+      <c r="R202" s="20">
+        <f>IF($B202="","",IF(N($O202)=0,0,IF(OR($L202="감소",AND($L202="증가",$M202&lt;&gt;"Y")),IF(N($G202)=0,0,ROUND(N(내역서!$G202)*$O202/$G202,0)),IF(N($J202)=0,0,ROUND(N(내역서!$O202)*$O202/$J202,0)))))</f>
+        <v/>
+      </c>
+      <c r="S202" s="20">
+        <f>IF($B202="","",IF(N($O202)=0,0,IF(OR($L202="감소",AND($L202="증가",$M202&lt;&gt;"Y")),IF(N($G202)=0,0,ROUND(N(내역서!$H202)*$O202/$G202,0)),IF(N($J202)=0,0,ROUND(N(내역서!$P202)*$O202/$J202,0)))))</f>
+        <v/>
+      </c>
+      <c r="T202" s="20">
+        <f>IF($B202="","",N($O202)-N($R202)-N($S202))</f>
+        <v/>
+      </c>
+      <c r="U202" s="20">
+        <f>IF($B202="","",ROUND(N($K202)*N($R202),0))</f>
+        <v/>
+      </c>
+      <c r="V202" s="20">
+        <f>IF($B202="","",ROUND(N($K202)*N($S202),0))</f>
+        <v/>
+      </c>
+      <c r="W202" s="20">
+        <f>IF($B202="","",N($P202)-N($U202)-N($V202))</f>
+        <v/>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="18">
@@ -15429,6 +20241,30 @@
       </c>
       <c r="Q203" s="25">
         <f>IF($B203="","",IF($L203="감소","감소분 → 계약단가",IF(AND($M203="Y",OR($L203="증가",$L203="신규")),"발주기관 요구 → 협의 (불성립 시 (당시단가+당시단가×낙찰률)÷2)",IF($L203="증가",IF(AND($N203&lt;&gt;"",$G203&gt;$N203),"증가분 → 계약단가&gt;예정가격단가 이므로 예정가격단가","증가분 → 계약단가 (낙찰률을 곱하지 않습니다)"),IF($L203="신규","신규비목 → 당시단가 × 낙찰률","")))))</f>
+        <v/>
+      </c>
+      <c r="R203" s="20">
+        <f>IF($B203="","",IF(N($O203)=0,0,IF(OR($L203="감소",AND($L203="증가",$M203&lt;&gt;"Y")),IF(N($G203)=0,0,ROUND(N(내역서!$G203)*$O203/$G203,0)),IF(N($J203)=0,0,ROUND(N(내역서!$O203)*$O203/$J203,0)))))</f>
+        <v/>
+      </c>
+      <c r="S203" s="20">
+        <f>IF($B203="","",IF(N($O203)=0,0,IF(OR($L203="감소",AND($L203="증가",$M203&lt;&gt;"Y")),IF(N($G203)=0,0,ROUND(N(내역서!$H203)*$O203/$G203,0)),IF(N($J203)=0,0,ROUND(N(내역서!$P203)*$O203/$J203,0)))))</f>
+        <v/>
+      </c>
+      <c r="T203" s="20">
+        <f>IF($B203="","",N($O203)-N($R203)-N($S203))</f>
+        <v/>
+      </c>
+      <c r="U203" s="20">
+        <f>IF($B203="","",ROUND(N($K203)*N($R203),0))</f>
+        <v/>
+      </c>
+      <c r="V203" s="20">
+        <f>IF($B203="","",ROUND(N($K203)*N($S203),0))</f>
+        <v/>
+      </c>
+      <c r="W203" s="20">
+        <f>IF($B203="","",N($P203)-N($U203)-N($V203))</f>
         <v/>
       </c>
     </row>
@@ -15468,7 +20304,7 @@
     <row r="207">
       <c r="N207" s="26" t="inlineStr">
         <is>
-          <t>증감 합계</t>
+          <t>직접공사비 증감 합계</t>
         </is>
       </c>
       <c r="P207" s="27">
@@ -15477,31 +20313,55 @@
       </c>
     </row>
     <row r="208">
-      <c r="N208" s="28" t="inlineStr">
+      <c r="N208" s="26" t="inlineStr">
+        <is>
+          <t>제비율 · 일반관리비 · 이윤 · 부가세 증감</t>
+        </is>
+      </c>
+      <c r="P208" s="27">
+        <f>원가계산서!$G$33-P207</f>
+        <v/>
+      </c>
+    </row>
+    <row r="209">
+      <c r="N209" s="26" t="inlineStr">
+        <is>
+          <t>계약금액 증감 (원가계산서 도급액)</t>
+        </is>
+      </c>
+      <c r="P209" s="27">
+        <f>원가계산서!$G$33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="210">
+      <c r="N210" s="28" t="inlineStr">
         <is>
           <t>변경 후 계약금액</t>
         </is>
       </c>
-      <c r="P208" s="29">
-        <f>'설정'!$C$13+P207</f>
-        <v/>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="17" t="inlineStr">
+      <c r="P210" s="29">
+        <f>'설정'!$C$13+P209</f>
+        <v/>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="17" t="inlineStr">
         <is>
           <t>이 표는 손으로 채우는 곳이 «협의(Y)» 와 «예정가격단가» 둘뿐입니다. 나머지는 전부 자동입니다.
 · 발주기관이 요구해서 늘어난 분이면 협의 칸에 Y 를 넣으세요 — 단가가 협의식으로 바뀝니다.
 · 예정가격단가는 «아는 경우에만» 적으세요. 계약단가가 그보다 높으면 예정가격단가가 적용됩니다.
-· 증가분에는 낙찰률을 곱하지 않습니다. 낙찰률은 «신규 비목» 에만 곱합니다.</t>
+· 증가분에는 낙찰률을 곱하지 않습니다. 낙찰률은 «신규 비목» 에만 곱합니다.
+· R~W 열은 적용단가를 재료비 · 노무비 · 경비로 가른 것입니다 — 원가계산서 «변경 후» 가 «당초 + 이 증감» 으로 셉니다.
+· 변경 후 계약금액 = 계약금액 + 원가계산서 «도급액» 증감(간접노무비 · 보험료 · 일반관리비 · 이윤 · 부가세까지 · 시행령 제65조⑥).</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A210:Q210"/>
-    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A212:W212"/>
+    <mergeCell ref="A2:W2"/>
+    <mergeCell ref="A1:W1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -52206,7 +57066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -52238,7 +57098,7 @@
         </is>
       </c>
       <c r="C4" s="40">
-        <f>'설정'!$C$5</f>
+        <f>IF('설정'!$C$5="","",'설정'!$C$5)</f>
         <v/>
       </c>
       <c r="D4" s="6" t="n"/>
@@ -52251,7 +57111,7 @@
         </is>
       </c>
       <c r="C5" s="40">
-        <f>'설정'!$C$6</f>
+        <f>IF('설정'!$C$6="","",'설정'!$C$6)</f>
         <v/>
       </c>
       <c r="D5" s="6" t="n"/>
@@ -52264,7 +57124,7 @@
         </is>
       </c>
       <c r="C6" s="40">
-        <f>'설정'!$C$7</f>
+        <f>IF('설정'!$C$7="","",'설정'!$C$7)</f>
         <v/>
       </c>
       <c r="D6" s="6" t="n"/>
@@ -52277,7 +57137,7 @@
         </is>
       </c>
       <c r="C7" s="40">
-        <f>'설정'!$C$9</f>
+        <f>IF('설정'!$C$9="","",'설정'!$C$9)</f>
         <v/>
       </c>
       <c r="D7" s="6" t="n"/>
@@ -52338,7 +57198,7 @@
     <row r="13" ht="22" customHeight="1">
       <c r="B13" s="39" t="inlineStr">
         <is>
-          <t>증감 합계</t>
+          <t>직접공사비 증감</t>
         </is>
       </c>
       <c r="C13" s="41">
@@ -52351,92 +57211,120 @@
     <row r="14" ht="22" customHeight="1">
       <c r="B14" s="39" t="inlineStr">
         <is>
+          <t>제비율 · 이윤 · 부가세 증감</t>
+        </is>
+      </c>
+      <c r="C14" s="41">
+        <f>증감대비표!$P$208</f>
+        <v/>
+      </c>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="39" t="inlineStr">
+        <is>
+          <t>계약금액 증감</t>
+        </is>
+      </c>
+      <c r="C15" s="41">
+        <f>증감대비표!$P$209</f>
+        <v/>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="B16" s="39" t="inlineStr">
+        <is>
           <t>증감률</t>
         </is>
       </c>
-      <c r="C14" s="40">
-        <f>IF(N('설정'!$C$13)=0,"",ROUND(증감대비표!$P$207/'설정'!$C$13*100,2)&amp;" %")</f>
-        <v/>
-      </c>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="B15" s="42" t="inlineStr">
+      <c r="C16" s="40">
+        <f>IF(N('설정'!$C$13)=0,"",ROUND(증감대비표!$P$209/'설정'!$C$13*100,2)&amp;" %")</f>
+        <v/>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="42" t="inlineStr">
         <is>
           <t>변경 후 계약금액</t>
         </is>
       </c>
-      <c r="C15" s="43">
-        <f>증감대비표!$P$208</f>
-        <v/>
-      </c>
-      <c r="D15" s="44" t="n"/>
-      <c r="E15" s="44" t="n"/>
-    </row>
-    <row r="17" ht="54" customHeight="1">
-      <c r="B17" s="39" t="inlineStr">
+      <c r="C17" s="43">
+        <f>증감대비표!$P$210</f>
+        <v/>
+      </c>
+      <c r="D17" s="44" t="n"/>
+      <c r="E17" s="44" t="n"/>
+    </row>
+    <row r="19" ht="54" customHeight="1">
+      <c r="B19" s="39" t="inlineStr">
         <is>
           <t>변경 사유</t>
         </is>
       </c>
-      <c r="C17" s="45" t="inlineStr"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-    </row>
-    <row r="18" ht="54" customHeight="1">
-      <c r="B18" s="39" t="inlineStr">
+      <c r="C19" s="45" t="inlineStr"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+    </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="B20" s="39" t="inlineStr">
         <is>
           <t>근거 서류</t>
         </is>
       </c>
-      <c r="C18" s="45" t="inlineStr"/>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="46" t="inlineStr">
+      <c r="C20" s="45" t="inlineStr"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="46" t="inlineStr">
         <is>
           <t>위와 같이 설계변경에 따른 계약금액 조정을 요청합니다.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="47" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="47" t="inlineStr">
         <is>
           <t>현장대리인</t>
         </is>
       </c>
-      <c r="C23" s="48" t="inlineStr">
+      <c r="C25" s="48" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
-      <c r="D23" s="47" t="inlineStr">
+      <c r="D25" s="47" t="inlineStr">
         <is>
           <t>대표자</t>
         </is>
       </c>
-      <c r="E23" s="48" t="inlineStr">
+      <c r="E25" s="48" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="17">
+    <mergeCell ref="C16:E16"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="C11:E11"/>
     <mergeCell ref="C14:E14"/>
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C19:E19"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C15:E15"/>
     <mergeCell ref="C9:E9"/>
     <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C18:E18"/>
     <mergeCell ref="C17:E17"/>
     <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C20:E20"/>
     <mergeCell ref="C12:E12"/>
     <mergeCell ref="C6:E6"/>
     <mergeCell ref="C10:E10"/>
@@ -52452,7 +57340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -52693,20 +57581,20 @@
       </c>
       <c r="B12" s="49" t="inlineStr">
         <is>
-          <t>내역서 당초 합계와 설정의 계약금액 차이</t>
+          <t>원가계산서 당초 도급액과 설정의 계약금액 차이</t>
         </is>
       </c>
       <c r="C12" s="53">
-        <f>IF(N('설정'!$C$13)=0,"",내역서!$K$204-'설정'!$C$13)</f>
+        <f>IF(N('설정'!$C$13)=0,"",원가계산서!$E$33-'설정'!$C$13)</f>
         <v/>
       </c>
       <c r="D12" s="51">
-        <f>IF(OR(C12="",ABS(N(C12))&lt;=1),"✅","⚠️")</f>
+        <f>IF(OR(C12="",ABS(N(C12))&lt;=10000),"✅","⚠️")</f>
         <v/>
       </c>
       <c r="E12" s="52" t="inlineStr">
         <is>
-          <t>내역서의 당초 합계가 계약금액과 안 맞습니다. 빠진 항목이나 부가세 처리를 확인하세요.</t>
+          <t>원가계산서 «당초» 도급액이 계약금액과 1만 원 넘게 다릅니다. 설정의 요율이 산출내역서와 같은지, 관급 · 폐기물 · 단수 조정 같은 빠진 항목이 없는지 보세요(조정액은 «증감» 으로 세므로 영향은 작습니다).</t>
         </is>
       </c>
     </row>
@@ -52716,7 +57604,7 @@
       </c>
       <c r="B13" s="49" t="inlineStr">
         <is>
-          <t>증감 합계 (규정 단가 적용)</t>
+          <t>직접공사비 증감 (규정 단가 적용)</t>
         </is>
       </c>
       <c r="C13" s="53">
@@ -52729,7 +57617,7 @@
       </c>
       <c r="E13" s="52" t="inlineStr">
         <is>
-          <t>이 값이 발주기관에 내는 조정금액입니다.</t>
+          <t>재료비 · 노무비 · 경비의 증감입니다(시행령 제65조 단가).</t>
         </is>
       </c>
     </row>
@@ -52739,48 +57627,71 @@
       </c>
       <c r="B14" s="49" t="inlineStr">
         <is>
+          <t>계약금액 증감 (제비율 · 부가세 포함)</t>
+        </is>
+      </c>
+      <c r="C14" s="53">
+        <f>증감대비표!$P$209</f>
+        <v/>
+      </c>
+      <c r="D14" s="51">
+        <f>"—"</f>
+        <v/>
+      </c>
+      <c r="E14" s="52" t="inlineStr">
+        <is>
+          <t>이 값이 발주기관에 내는 조정금액입니다 — 원가계산서 «도급액» 의 증감(시행령 제65조⑥).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="49" t="inlineStr">
+        <is>
           <t>변경 − 당초 (단순 차)</t>
         </is>
       </c>
-      <c r="C14" s="53">
+      <c r="C15" s="53">
         <f>내역서!$K$204*-1+내역서!$S$204</f>
         <v/>
       </c>
-      <c r="D14" s="51">
+      <c r="D15" s="51">
         <f>"—"</f>
         <v/>
       </c>
-      <c r="E14" s="52" t="inlineStr">
+      <c r="E15" s="52" t="inlineStr">
         <is>
           <t>위 «증감 합계» 와 다른 것이 정상입니다 — 규정 단가(증가는 계약단가, 신규는 낙찰률 적용)를 쓰기 때문입니다.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="49" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="49" t="inlineStr">
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="49" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="49" t="inlineStr">
         <is>
           <t>증감률 (%)</t>
         </is>
       </c>
-      <c r="C15" s="54">
-        <f>IF(N('설정'!$C$13)=0,"",ROUND(증감대비표!$P$207/'설정'!$C$13*100,2))</f>
-        <v/>
-      </c>
-      <c r="D15" s="51">
-        <f>IF(C15="","—",IF(ABS(N(C15))&lt;30,"✅","⚠️"))</f>
-        <v/>
-      </c>
-      <c r="E15" s="52" t="inlineStr">
+      <c r="C16" s="54">
+        <f>IF(N('설정'!$C$13)=0,"",ROUND(증감대비표!$P$209/'설정'!$C$13*100,2))</f>
+        <v/>
+      </c>
+      <c r="D16" s="51">
+        <f>IF(C16="","—",IF(ABS(N(C16))&lt;30,"✅","⚠️"))</f>
+        <v/>
+      </c>
+      <c r="E16" s="52" t="inlineStr">
         <is>
           <t>30% 를 넘으면 발주기관 내부 절차가 길어집니다. 차수를 나누는 편이 빠를 수 있습니다.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="55" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="55" t="inlineStr">
         <is>
           <t>⚠️ 가 하나라도 있으면 그 줄의 «틀렸을 때 어떻게 되나» 를 읽고 고친 뒤 제출하세요.</t>
         </is>
